--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -863,7 +863,7 @@
         <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I2" t="n">
         <v>3.3</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
         <v>1.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G3" t="n">
         <v>1.58</v>
@@ -1126,7 +1126,7 @@
         <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
         <v>2.34</v>
@@ -1377,7 +1377,7 @@
         <v>2.74</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.54</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G8" t="n">
         <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="I8" t="n">
         <v>17.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>1.84</v>
@@ -2647,7 +2647,7 @@
         <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2913,28 +2913,28 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I11" t="n">
         <v>2.06</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 01:41:52</t>
+          <t>2026-05-18 03:54:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
         <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I2" t="n">
         <v>3.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
         <v>2.74</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
         <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
         <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
         <v>2.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2922,19 +2922,19 @@
         <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I11" t="n">
         <v>2.06</v>
@@ -3158,7 +3158,7 @@
         <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,261 +3366,515 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 03:54:59</t>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-18 06:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nacional (Uru)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Universitario de Deportes</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" t="n">
         <v>1.01</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-05-18 03:54:59</t>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-18 06:08:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
         <v>5.2</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
         <v>2.86</v>
@@ -1628,10 +1628,10 @@
         <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
         <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I6" t="n">
         <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>9.6</v>
       </c>
       <c r="I7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
         <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="I8" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2913,28 +2913,28 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
         <v>5.1</v>
@@ -3412,7 +3412,7 @@
         <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 06:08:13</t>
+          <t>2026-05-18 08:24:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -860,67 +860,67 @@
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -929,43 +929,43 @@
         <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>12.5</v>
@@ -974,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -986,7 +986,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="AX2" t="n">
         <v>13.5</v>
@@ -998,89 +998,89 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
         <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>25</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>26</v>
-      </c>
       <c r="CA2" t="n">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>4.8</v>
       </c>
       <c r="K3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR3" t="n">
         <v>5.2</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G4" t="n">
         <v>3.15</v>
@@ -1380,19 +1380,19 @@
         <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.48</v>
@@ -1401,194 +1401,194 @@
         <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="H8" t="n">
         <v>14.5</v>
@@ -2393,7 +2393,7 @@
         <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -2895,13 +2895,13 @@
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>870</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>4.6</v>
@@ -2913,28 +2913,28 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J11" t="n">
         <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 08:24:12</t>
+          <t>2026-05-18 10:42:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -863,7 +863,7 @@
         <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
         <v>3.6</v>
@@ -1028,13 +1028,13 @@
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
@@ -1046,13 +1046,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1064,23 +1064,23 @@
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
         <v>5.3</v>
@@ -1141,7 +1141,7 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>1.48</v>
@@ -1162,7 +1162,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X3" t="n">
         <v>36</v>
@@ -1177,7 +1177,7 @@
         <v>140</v>
       </c>
       <c r="AB3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
         <v>14.5</v>
@@ -1222,13 +1222,13 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1240,7 +1240,7 @@
         <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1252,7 +1252,7 @@
         <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
         <v>4.5</v>
@@ -1282,13 +1282,13 @@
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL3" t="n">
         <v>90</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
@@ -1300,41 +1300,41 @@
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
         <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ3" t="n">
         <v>13.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
@@ -1467,7 +1467,7 @@
         <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>14.5</v>
@@ -1536,13 +1536,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL4" t="n">
         <v>85</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
@@ -1554,13 +1554,13 @@
         <v>24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
@@ -1572,23 +1572,23 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX4" t="n">
         <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>18.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
         <v>2.78</v>
@@ -1643,28 +1643,28 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
         <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
         <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1709,19 +1709,19 @@
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
         <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>24</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1766,13 +1766,13 @@
         <v>34</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
         <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
@@ -1784,19 +1784,19 @@
         <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN5" t="n">
         <v>7.2</v>
@@ -1808,13 +1808,13 @@
         <v>27</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
@@ -1826,23 +1826,23 @@
         <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BX5" t="n">
         <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -1876,227 +1876,227 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.9</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
         <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -2895,13 +2895,13 @@
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>870</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>4.6</v>
@@ -2913,28 +2913,28 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G11" t="n">
         <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I11" t="n">
         <v>2.12</v>
@@ -3158,7 +3158,7 @@
         <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H12" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 10:42:32</t>
+          <t>2026-05-18 12:56:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
         <v>2.32</v>
@@ -905,7 +905,7 @@
         <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1141,16 +1141,16 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
@@ -1162,10 +1162,10 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
         <v>34</v>
@@ -1174,19 +1174,19 @@
         <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>15.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>15</v>
@@ -1195,7 +1195,7 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1207,16 +1207,16 @@
         <v>17</v>
       </c>
       <c r="AL3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
         <v>5</v>
@@ -1225,19 +1225,19 @@
         <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
         <v>5.4</v>
@@ -1249,10 +1249,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1267,10 +1267,10 @@
         <v>5.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="n">
         <v>5.4</v>
@@ -1282,13 +1282,13 @@
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BL3" t="n">
         <v>90</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
@@ -1300,16 +1300,16 @@
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU3" t="n">
         <v>3.8</v>
@@ -1318,23 +1318,23 @@
         <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>13.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
         <v>2.44</v>
@@ -1530,37 +1530,37 @@
         <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BL4" t="n">
         <v>85</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
         <v>5.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
@@ -1572,23 +1572,23 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX4" t="n">
         <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ4" t="n">
         <v>18.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1652,19 +1652,19 @@
         <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2062,13 +2062,13 @@
         <v>32</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR6" t="n">
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2080,30 +2080,30 @@
         <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,229 +2118,229 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>9.6</v>
+        <v>1.58</v>
       </c>
       <c r="I7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW7" t="n">
         <v>13</v>
       </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H8" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
         <v>22</v>
       </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="I9" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W10" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" t="n">
+      <c r="X10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>460</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.6</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>1.26</v>
       </c>
       <c r="I11" t="n">
-        <v>2.12</v>
+        <v>1.28</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.35</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,498 +3383,5578 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>3.85</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02</v>
+        <v>4.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>2.14</v>
       </c>
       <c r="J12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.75</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 12:56:25</t>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lillestrom</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>95</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Odds BK</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X16" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Strommen</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hodd</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Asane</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>90</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Stromsgodset</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>27</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Al-Masry</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Ahly Cairo</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Smouha</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H23" t="n">
+        <v>16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>230</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>490</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ascoli</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Union Brescia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S.S.D. Casarano Calcio</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Aalesunds</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Al Najma Club</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Al-Shabab (KSA)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Al-Khaleej Saihat</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Lecco</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Nacional (Uru)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Universitario de Deportes</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-05-18 12:56:25</t>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:10:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,7 +905,7 @@
         <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
         <v>1.7</v>
@@ -1120,7 +1120,7 @@
         <v>5.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1129,13 +1129,13 @@
         <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1147,16 +1147,16 @@
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1213,64 +1213,64 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH3" t="n">
         <v>5.4</v>
@@ -1279,62 +1279,62 @@
         <v>3.85</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
         <v>3.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT3" t="n">
         <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
         <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>5.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
         <v>2.78</v>
@@ -1655,13 +1655,13 @@
         <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
         <v>2.34</v>
@@ -1736,7 +1736,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1760,10 +1760,10 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
         <v>7.4</v>
@@ -1778,7 +1778,7 @@
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="n">
         <v>4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
         <v>5.1</v>
@@ -2068,7 +2068,7 @@
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2080,23 +2080,23 @@
         <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="I7" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
         <v>5.2</v>
@@ -2172,34 +2172,34 @@
         <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>12.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AB7" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AD7" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
         <v>16.5</v>
@@ -2208,19 +2208,19 @@
         <v>55</v>
       </c>
       <c r="AG7" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>30</v>
       </c>
       <c r="AJ7" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AK7" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
@@ -2229,13 +2229,13 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.199999999999999</v>
@@ -2244,10 +2244,10 @@
         <v>9.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>3.45</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
         <v>7.4</v>
@@ -2256,40 +2256,40 @@
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>13.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>55</v>
+        <v>2.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI7" t="n">
         <v>3.2</v>
@@ -2298,49 +2298,49 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BL7" t="n">
         <v>120</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ7" t="n">
-        <v>25</v>
+        <v>4.3</v>
       </c>
       <c r="BR7" t="n">
         <v>55</v>
       </c>
       <c r="BS7" t="n">
-        <v>28</v>
+        <v>4.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU7" t="n">
         <v>4</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>3.45</v>
       </c>
       <c r="BX7" t="n">
         <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
         <v>5.7</v>
@@ -2408,7 +2408,7 @@
         <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
         <v>2.68</v>
@@ -2447,10 +2447,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
         <v>48</v>
@@ -2459,43 +2459,43 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
         <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.01</v>
@@ -2507,10 +2507,10 @@
         <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,7 +2522,7 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
         <v>8.4</v>
@@ -2531,16 +2531,16 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
         <v>5.4</v>
@@ -2552,13 +2552,13 @@
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>140</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>4.5</v>
@@ -2576,35 +2576,35 @@
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="BU8" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>95</v>
       </c>
       <c r="BW8" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>80</v>
       </c>
       <c r="BY8" t="n">
-        <v>50</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2665,28 +2665,28 @@
         <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
         <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>30</v>
@@ -2695,10 +2695,10 @@
         <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
         <v>22</v>
@@ -2710,7 +2710,7 @@
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
         <v>32</v>
@@ -2740,34 +2740,34 @@
         <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
@@ -2776,89 +2776,89 @@
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM9" t="n">
-        <v>50</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP9" t="n">
         <v>26</v>
       </c>
       <c r="BQ9" t="n">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="n">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA9" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -2928,13 +2928,13 @@
         <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2946,7 +2946,7 @@
         <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z10" t="n">
         <v>120</v>
@@ -2976,7 +2976,7 @@
         <v>34</v>
       </c>
       <c r="AI10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ10" t="n">
         <v>14</v>
@@ -3000,10 +3000,10 @@
         <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
         <v>4.4</v>
@@ -3012,7 +3012,7 @@
         <v>6.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV10" t="n">
         <v>4</v>
@@ -3021,7 +3021,7 @@
         <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY10" t="n">
         <v>8</v>
@@ -3039,7 +3039,7 @@
         <v>11</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
         <v>4.3</v>
@@ -3048,7 +3048,7 @@
         <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
         <v>4.6</v>
@@ -3060,13 +3060,13 @@
         <v>14.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="BL10" t="n">
         <v>190</v>
       </c>
       <c r="BM10" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
@@ -3084,35 +3084,35 @@
         <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="BT10" t="n">
         <v>15.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="BV10" t="n">
         <v>110</v>
       </c>
       <c r="BW10" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BX10" t="n">
         <v>100</v>
       </c>
       <c r="BY10" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3179,13 +3179,13 @@
         <v>1.35</v>
       </c>
       <c r="R11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>1.87</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
         <v>1.93</v>
@@ -3278,13 +3278,13 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -3314,31 +3314,31 @@
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>120</v>
       </c>
       <c r="BM11" t="n">
-        <v>65</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>17.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>90</v>
       </c>
       <c r="BQ11" t="n">
-        <v>50</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>70</v>
       </c>
       <c r="BS11" t="n">
-        <v>40</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>5.1</v>
@@ -3356,7 +3356,7 @@
         <v>21</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>8.800000000000001</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3400,28 +3400,28 @@
         <v>3.85</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I12" t="n">
         <v>2.14</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
@@ -3430,25 +3430,25 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
         <v>20</v>
@@ -3475,7 +3475,7 @@
         <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG12" t="n">
         <v>22</v>
@@ -3514,7 +3514,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
@@ -3541,7 +3541,7 @@
         <v>2.46</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BC12" t="n">
         <v>2.5</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
         <v>1.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S13" t="n">
         <v>2.12</v>
@@ -3822,13 +3822,13 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>100</v>
       </c>
       <c r="BM13" t="n">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
@@ -3840,41 +3840,41 @@
         <v>9.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>13</v>
       </c>
       <c r="BU13" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>60</v>
       </c>
       <c r="BW13" t="n">
-        <v>36</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>32</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>11.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
@@ -3920,13 +3920,13 @@
         <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
         <v>5.5</v>
@@ -3935,16 +3935,16 @@
         <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
         <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
         <v>1.58</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>95</v>
       </c>
       <c r="BM14" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>5.5</v>
@@ -4094,41 +4094,41 @@
         <v>13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>24</v>
       </c>
       <c r="BS14" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>38</v>
       </c>
       <c r="BW14" t="n">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>42</v>
       </c>
       <c r="BY14" t="n">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>16</v>
       </c>
       <c r="CA14" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4201,7 +4201,7 @@
         <v>2.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="U15" t="n">
         <v>2.58</v>
@@ -4330,13 +4330,13 @@
         <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>70</v>
       </c>
       <c r="BM15" t="n">
-        <v>44</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>7.6</v>
@@ -4348,13 +4348,13 @@
         <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>27</v>
       </c>
       <c r="BS15" t="n">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>7</v>
@@ -4366,23 +4366,23 @@
         <v>18</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>25</v>
       </c>
       <c r="BY15" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>15.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R16" t="n">
         <v>1.69</v>
@@ -4584,13 +4584,13 @@
         <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>48</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>6.6</v>
@@ -4602,13 +4602,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
       </c>
       <c r="BS16" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>8</v>
@@ -4620,23 +4620,23 @@
         <v>24</v>
       </c>
       <c r="BW16" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>29</v>
       </c>
       <c r="BY16" t="n">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>15.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>3.75</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="H17" t="n">
         <v>1.85</v>
@@ -4688,7 +4688,7 @@
         <v>1.23</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
         <v>5.3</v>
@@ -4709,106 +4709,106 @@
         <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.94</v>
       </c>
       <c r="W17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP17" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB17" t="n">
         <v>1.01</v>
@@ -4823,74 +4823,74 @@
         <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.61</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="U18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU18" t="n">
         <v>6.6</v>
       </c>
-      <c r="J18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK18" t="n">
+      <c r="AV18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF18" t="n">
         <v>18</v>
       </c>
-      <c r="AL18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG18" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5166,239 +5166,239 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.98</v>
+        <v>1.61</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W19" t="n">
         <v>2.4</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP19" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI19" t="n">
+      <c r="BQ19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR19" t="n">
         <v>29</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="BS19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV19" t="n">
         <v>50</v>
       </c>
-      <c r="AK19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>90</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BY19" t="n">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>20</v>
       </c>
       <c r="CA19" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="G20" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" t="n">
         <v>4.3</v>
       </c>
-      <c r="K20" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>1.44</v>
+        <v>2.46</v>
       </c>
       <c r="T20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U20" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
         <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE20" t="n">
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
+        <v>1.78</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="S21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG21" t="n">
         <v>4.4</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="BH21" t="n">
         <v>1000</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="BI21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT21" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH21" t="n">
+      <c r="BU21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX21" t="n">
         <v>28</v>
       </c>
-      <c r="AI21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>240</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>26</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>70</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>85</v>
-      </c>
       <c r="BY21" t="n">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>27</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
         <v>4.6</v>
       </c>
-      <c r="G22" t="n">
+      <c r="AQ22" t="n">
         <v>5.3</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="AR22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH22" t="n">
         <v>3.3</v>
       </c>
-      <c r="K22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.28</v>
+        <v>4.6</v>
       </c>
       <c r="G23" t="n">
-        <v>1.34</v>
+        <v>5.3</v>
       </c>
       <c r="H23" t="n">
-        <v>16</v>
+        <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>2.04</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="W23" t="n">
-        <v>3.9</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="Z23" t="n">
-        <v>230</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB23" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF23" t="n">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>490</v>
+        <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11.5</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="n">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN23" t="n">
-        <v>7.8</v>
+        <v>110</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.4</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.7</v>
+        <v>32</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,239 +6436,239 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.94</v>
+        <v>1.27</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4</v>
+        <v>1.34</v>
       </c>
       <c r="H24" t="n">
-        <v>2.26</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>2.52</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="U24" t="n">
-        <v>2.32</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>3.9</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC24" t="n">
         <v>16</v>
       </c>
-      <c r="AC24" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>6.6</v>
       </c>
       <c r="AG24" t="n">
         <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="AJ24" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AM24" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="AR24" t="n">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>22</v>
+        <v>5.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>5.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>5.4</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>5.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>48</v>
+        <v>5.7</v>
       </c>
       <c r="BF24" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6699,230 +6699,230 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G25" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>4.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
         <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -6953,230 +6953,230 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7207,230 +7207,230 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7461,34 +7461,34 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="G28" t="n">
         <v>4.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I28" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P28" t="n">
         <v>2.76</v>
@@ -7497,194 +7497,194 @@
         <v>1.48</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7733,16 +7733,16 @@
         <v>6.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P29" t="n">
         <v>2.92</v>
@@ -7751,10 +7751,10 @@
         <v>1.42</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T29" t="n">
         <v>1.6</v>
@@ -7763,10 +7763,10 @@
         <v>2.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X29" t="n">
         <v>42</v>
@@ -7817,13 +7817,13 @@
         <v>90</v>
       </c>
       <c r="AN29" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO29" t="n">
         <v>5.9</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
@@ -7835,7 +7835,7 @@
         <v>12.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU29" t="n">
         <v>11</v>
@@ -7847,7 +7847,7 @@
         <v>12</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY29" t="n">
         <v>20</v>
@@ -7859,7 +7859,7 @@
         <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC29" t="n">
         <v>9.199999999999999</v>
@@ -7868,77 +7868,77 @@
         <v>4.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG29" t="n">
         <v>4.3</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>6.4</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I30" t="n">
         <v>1.57</v>
@@ -7987,212 +7987,212 @@
         <v>6.4</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q30" t="n">
         <v>1.54</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -8223,230 +8223,230 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
@@ -8477,237 +8477,237 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,234 +8717,234 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,261 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-18 15:10:34</t>
+          <t>2026-05-18 17:23:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-05-18 17:23:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -1028,16 +1028,16 @@
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO2" t="n">
         <v>4.1</v>
@@ -1046,13 +1046,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1070,17 +1070,17 @@
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
         <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1147,7 +1147,7 @@
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
@@ -1162,7 +1162,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
@@ -1213,22 +1213,22 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1237,10 +1237,10 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1249,10 +1249,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
@@ -1264,13 +1264,13 @@
         <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
         <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="n">
         <v>5.4</v>
@@ -1285,7 +1285,7 @@
         <v>4.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM3" t="n">
         <v>7.4</v>
@@ -1294,7 +1294,7 @@
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R4" t="n">
         <v>1.65</v>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
@@ -1467,7 +1467,7 @@
         <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>14.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
         <v>2.78</v>
@@ -1670,7 +1670,7 @@
         <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2068,7 +2068,7 @@
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2083,7 +2083,7 @@
         <v>4.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I7" t="n">
         <v>1.76</v>
@@ -2178,7 +2178,7 @@
         <v>2.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -2232,10 +2232,10 @@
         <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.199999999999999</v>
@@ -2244,10 +2244,10 @@
         <v>9.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
         <v>7.4</v>
@@ -2256,40 +2256,40 @@
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
         <v>3.95</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI7" t="n">
         <v>3.2</v>
@@ -2298,16 +2298,16 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BL7" t="n">
         <v>120</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO7" t="n">
         <v>3.25</v>
@@ -2316,7 +2316,7 @@
         <v>48</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR7" t="n">
         <v>55</v>
@@ -2325,7 +2325,7 @@
         <v>4.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU7" t="n">
         <v>4</v>
@@ -2334,13 +2334,13 @@
         <v>13</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BX7" t="n">
         <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2435,10 +2435,10 @@
         <v>3.75</v>
       </c>
       <c r="X8" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>130</v>
@@ -2447,13 +2447,13 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="AD8" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2462,10 +2462,10 @@
         <v>9.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>140</v>
@@ -2531,7 +2531,7 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2689,10 +2689,10 @@
         <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>20</v>
@@ -2701,13 +2701,13 @@
         <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2716,10 +2716,10 @@
         <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>32</v>
@@ -2746,16 +2746,16 @@
         <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS9" t="n">
         <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX9" t="n">
         <v>1.01</v>
@@ -2791,7 +2791,7 @@
         <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>8.199999999999999</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
         <v>1.43</v>
@@ -2928,13 +2928,13 @@
         <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2997,7 +2997,7 @@
         <v>280</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>3.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>4</v>
@@ -3009,7 +3009,7 @@
         <v>4.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
         <v>10.5</v>
@@ -3021,10 +3021,10 @@
         <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>20</v>
@@ -3033,7 +3033,7 @@
         <v>4.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>1.11</v>
@@ -3176,7 +3176,7 @@
         <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R11" t="n">
         <v>2</v>
@@ -3197,7 +3197,7 @@
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
@@ -3209,7 +3209,7 @@
         <v>11.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AC11" t="n">
         <v>18</v>
@@ -3224,10 +3224,10 @@
         <v>150</v>
       </c>
       <c r="AG11" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
@@ -3278,7 +3278,7 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>19</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>3.85</v>
       </c>
       <c r="G12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>2.1</v>
@@ -3409,154 +3409,154 @@
         <v>2.14</v>
       </c>
       <c r="J12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.7</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W12" t="n">
         <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
         <v>14</v>
       </c>
-      <c r="Z12" t="n">
-        <v>18</v>
-      </c>
       <c r="AA12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AB12" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO12" t="n">
         <v>15</v>
       </c>
-      <c r="AE12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP12" t="n">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BD12" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.6</v>
+        <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3568,7 +3568,7 @@
         <v>13</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP12" t="n">
         <v>42</v>
@@ -3598,7 +3598,7 @@
         <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV12" t="n">
         <v>20</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.42</v>
       </c>
       <c r="G13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H13" t="n">
         <v>7</v>
@@ -3684,7 +3684,7 @@
         <v>2.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R13" t="n">
         <v>1.78</v>
@@ -3702,7 +3702,7 @@
         <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X13" t="n">
         <v>40</v>
@@ -3753,22 +3753,22 @@
         <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO13" t="n">
         <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3792,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>10.5</v>
@@ -3804,13 +3804,13 @@
         <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
         <v>3.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="n">
         <v>5.7</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
         <v>5.5</v>
@@ -3935,7 +3935,7 @@
         <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q14" t="n">
         <v>1.53</v>
@@ -3944,13 +3944,13 @@
         <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
         <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
         <v>1.22</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BL14" t="n">
         <v>95</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN14" t="n">
         <v>5.5</v>
@@ -4094,41 +4094,41 @@
         <v>13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR14" t="n">
         <v>24</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT14" t="n">
         <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV14" t="n">
         <v>38</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX14" t="n">
         <v>42</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ14" t="n">
         <v>16</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4207,16 +4207,16 @@
         <v>2.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>1.48</v>
       </c>
       <c r="X15" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>25</v>
@@ -4225,7 +4225,7 @@
         <v>38</v>
       </c>
       <c r="AB15" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
         <v>12.5</v>
@@ -4267,7 +4267,7 @@
         <v>12.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>23</v>
+        <v>1.05</v>
       </c>
       <c r="AQ15" t="n">
         <v>14</v>
@@ -4276,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
         <v>15.5</v>
@@ -4291,7 +4291,7 @@
         <v>16.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>1.05</v>
       </c>
       <c r="AY15" t="n">
         <v>10.5</v>
@@ -4300,19 +4300,19 @@
         <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>19.5</v>
+        <v>1.05</v>
       </c>
       <c r="BB15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>1.05</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>1.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>10.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.22</v>
@@ -4437,206 +4437,206 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U16" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM16" t="n">
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>18</v>
       </c>
-      <c r="AP16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>1.05</v>
       </c>
       <c r="AS16" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="AX16" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>1.05</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL16" t="n">
         <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT16" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="BV16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX16" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>1.85</v>
       </c>
       <c r="I17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -4700,7 +4700,7 @@
         <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.59</v>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W17" t="n">
         <v>1.29</v>
@@ -4772,7 +4772,7 @@
         <v>44</v>
       </c>
       <c r="AO17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -4927,10 +4927,10 @@
         <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J18" t="n">
         <v>3.5</v>
@@ -4969,7 +4969,7 @@
         <v>2.32</v>
       </c>
       <c r="V18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W18" t="n">
         <v>1.42</v>
@@ -5038,7 +5038,7 @@
         <v>12.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
@@ -5062,19 +5062,19 @@
         <v>11</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>1.05</v>
       </c>
       <c r="BB18" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>1.05</v>
       </c>
       <c r="BD18" t="n">
-        <v>27</v>
+        <v>1.05</v>
       </c>
       <c r="BE18" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
         <v>18</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
         <v>1.71</v>
@@ -5190,7 +5190,7 @@
         <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.21</v>
@@ -5223,13 +5223,13 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
         <v>2.4</v>
       </c>
       <c r="X19" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
         <v>29</v>
@@ -5247,7 +5247,7 @@
         <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
         <v>70</v>
@@ -5289,52 +5289,52 @@
         <v>19</v>
       </c>
       <c r="AR19" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.5</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J20" t="n">
         <v>3.8</v>
@@ -5447,7 +5447,7 @@
         <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
@@ -5483,10 +5483,10 @@
         <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
@@ -5495,7 +5495,7 @@
         <v>32</v>
       </c>
       <c r="AB20" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AC20" t="n">
         <v>9.800000000000001</v>
@@ -5510,10 +5510,10 @@
         <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AH20" t="n">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
         <v>29</v>
@@ -5591,7 +5591,7 @@
         <v>9</v>
       </c>
       <c r="BH20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI20" t="n">
         <v>3.35</v>
@@ -5606,7 +5606,7 @@
         <v>90</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN20" t="n">
         <v>8</v>
@@ -5618,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR20" t="n">
         <v>34</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT20" t="n">
         <v>6.6</v>
@@ -5636,23 +5636,23 @@
         <v>18.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BX20" t="n">
         <v>28</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ20" t="n">
         <v>20</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -5940,34 +5940,34 @@
         <v>1.71</v>
       </c>
       <c r="G22" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
         <v>1.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
         <v>2.2</v>
@@ -5979,22 +5979,22 @@
         <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>55</v>
@@ -6003,28 +6003,28 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD22" t="n">
         <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
         <v>950</v>
       </c>
       <c r="AI22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>21</v>
@@ -6033,52 +6033,52 @@
         <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
         <v>5.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="AX22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY22" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY22" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="BB22" t="n">
         <v>5.5</v>
@@ -6087,16 +6087,16 @@
         <v>5.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="BF22" t="n">
         <v>5.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="BH22" t="n">
         <v>3.3</v>
@@ -6108,16 +6108,16 @@
         <v>13.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO22" t="n">
         <v>3.35</v>
@@ -6132,7 +6132,7 @@
         <v>40</v>
       </c>
       <c r="BS22" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BT22" t="n">
         <v>10.5</v>
@@ -6141,26 +6141,26 @@
         <v>7</v>
       </c>
       <c r="BV22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX22" t="n">
         <v>90</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>38</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>5.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
@@ -6209,7 +6209,7 @@
         <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -6224,7 +6224,7 @@
         <v>1.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R23" t="n">
         <v>1.27</v>
@@ -6233,13 +6233,13 @@
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="V23" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
         <v>1.23</v>
@@ -6254,7 +6254,7 @@
         <v>11.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB23" t="n">
         <v>15.5</v>
@@ -6272,7 +6272,7 @@
         <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
@@ -6284,7 +6284,7 @@
         <v>140</v>
       </c>
       <c r="AK23" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="n">
         <v>85</v>
@@ -6335,19 +6335,19 @@
         <v>32</v>
       </c>
       <c r="BB23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC23" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC23" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
         <v>13</v>
@@ -6362,59 +6362,59 @@
         <v>12.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL23" t="n">
         <v>190</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP23" t="n">
         <v>55</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR23" t="n">
         <v>70</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BV23" t="n">
         <v>16.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="I24" t="n">
         <v>22</v>
@@ -6460,10 +6460,10 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -6478,7 +6478,7 @@
         <v>1.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
         <v>1.28</v>
@@ -6487,16 +6487,16 @@
         <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -6505,16 +6505,16 @@
         <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
         <v>950</v>
@@ -6523,7 +6523,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AG24" t="n">
         <v>14.5</v>
@@ -6532,19 +6532,19 @@
         <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>540</v>
       </c>
       <c r="AN24" t="n">
         <v>7.8</v>
@@ -6556,13 +6556,13 @@
         <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT24" t="n">
         <v>5.1</v>
@@ -6571,10 +6571,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX24" t="n">
         <v>5.4</v>
@@ -6583,10 +6583,10 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB24" t="n">
         <v>8</v>
@@ -6595,80 +6595,80 @@
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
         <v>5.7</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BJ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BN24" t="n">
         <v>4.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BP24" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR24" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BT24" t="n">
         <v>25</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BZ24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.93</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.94</v>
-      </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
         <v>4.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,28 +6723,28 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
         <v>2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
         <v>1.29</v>
@@ -6753,130 +6753,130 @@
         <v>2.06</v>
       </c>
       <c r="X25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>23</v>
       </c>
-      <c r="Y25" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AK25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>15</v>
       </c>
-      <c r="AC25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.34</v>
-      </c>
       <c r="BA25" t="n">
-        <v>2.52</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
-        <v>2.42</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.56</v>
+        <v>11</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.62</v>
+        <v>30</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BJ25" t="n">
         <v>13</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BN25" t="n">
         <v>6.6</v>
@@ -6888,41 +6888,41 @@
         <v>18</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BR25" t="n">
         <v>34</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BT25" t="n">
         <v>11</v>
       </c>
       <c r="BU25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV25" t="n">
         <v>48</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BX25" t="n">
         <v>55</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BZ25" t="n">
         <v>26</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>3.25</v>
@@ -7228,7 +7228,7 @@
         <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -7240,7 +7240,7 @@
         <v>1.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
@@ -7249,13 +7249,13 @@
         <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U27" t="n">
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W27" t="n">
         <v>1.9</v>
@@ -7318,13 +7318,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT27" t="n">
         <v>5.9</v>
@@ -7333,40 +7333,40 @@
         <v>5.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.05</v>
+        <v>3.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY27" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.05</v>
+        <v>3.55</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH27" t="n">
         <v>3.65</v>
@@ -7378,13 +7378,13 @@
         <v>950</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL27" t="n">
         <v>180</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN27" t="n">
         <v>5.4</v>
@@ -7396,13 +7396,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BR27" t="n">
         <v>38</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT27" t="n">
         <v>9.199999999999999</v>
@@ -7414,23 +7414,23 @@
         <v>50</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX27" t="n">
         <v>65</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>36</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7467,13 +7467,13 @@
         <v>4.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
@@ -7482,7 +7482,7 @@
         <v>1.22</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N28" t="n">
         <v>6.2</v>
@@ -7509,7 +7509,7 @@
         <v>2.7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W28" t="n">
         <v>1.33</v>
@@ -7524,7 +7524,7 @@
         <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB28" t="n">
         <v>27</v>
@@ -7593,7 +7593,7 @@
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY28" t="n">
         <v>14</v>
@@ -7635,7 +7635,7 @@
         <v>1.04</v>
       </c>
       <c r="BL28" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BM28" t="n">
         <v>1.04</v>
@@ -7653,7 +7653,7 @@
         <v>1.04</v>
       </c>
       <c r="BR28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS28" t="n">
         <v>1.04</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
         <v>1.24</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
         <v>5.2</v>
@@ -8002,7 +8002,7 @@
         <v>2.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R30" t="n">
         <v>1.58</v>
@@ -8011,7 +8011,7 @@
         <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="U30" t="n">
         <v>2.1</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H31" t="n">
         <v>5.3</v>
@@ -8331,76 +8331,76 @@
         <v>250</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="BJ31" t="n">
         <v>13.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL31" t="n">
         <v>240</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN31" t="n">
         <v>4.6</v>
@@ -8412,41 +8412,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR31" t="n">
         <v>40</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT31" t="n">
         <v>11</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV31" t="n">
         <v>75</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX31" t="n">
         <v>90</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ31" t="n">
         <v>36</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -8585,58 +8585,58 @@
         <v>60</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.05</v>
+        <v>3.15</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH32" t="n">
         <v>3.25</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G33" t="n">
         <v>6</v>
       </c>
-      <c r="G33" t="n">
-        <v>6.2</v>
-      </c>
       <c r="H33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8749,13 +8749,13 @@
         <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O33" t="n">
         <v>1.36</v>
@@ -8764,25 +8764,25 @@
         <v>1.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
         <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V33" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
@@ -8794,10 +8794,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC33" t="n">
         <v>9</v>
@@ -8863,7 +8863,7 @@
         <v>18.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AY33" t="n">
         <v>21</v>
@@ -8872,7 +8872,7 @@
         <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB33" t="n">
         <v>48</v>
@@ -8902,49 +8902,49 @@
         <v>13.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BL33" t="n">
         <v>200</v>
       </c>
       <c r="BM33" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BN33" t="n">
         <v>11.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP33" t="n">
         <v>60</v>
       </c>
       <c r="BQ33" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR33" t="n">
         <v>80</v>
       </c>
       <c r="BS33" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT33" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BU33" t="n">
         <v>3.7</v>
       </c>
       <c r="BV33" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX33" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BY33" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>
@@ -8985,230 +8985,230 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-18 17:23:29</t>
+          <t>2026-05-18 19:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -863,16 +863,16 @@
         <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -905,7 +905,7 @@
         <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
@@ -944,10 +944,10 @@
         <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
         <v>26</v>
@@ -974,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -1007,7 +1007,7 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
         <v>6.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G3" t="n">
         <v>1.68</v>
@@ -1120,13 +1120,13 @@
         <v>5.3</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1135,7 +1135,7 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1147,7 +1147,7 @@
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
@@ -1156,13 +1156,13 @@
         <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
@@ -1171,16 +1171,16 @@
         <v>34</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AA3" t="n">
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>26</v>
@@ -1192,10 +1192,10 @@
         <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1204,73 +1204,73 @@
         <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="BH3" t="n">
         <v>5.4</v>
@@ -1282,13 +1282,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
@@ -1300,22 +1300,22 @@
         <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT3" t="n">
         <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
         <v>6.8</v>
@@ -1324,17 +1324,17 @@
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ3" t="n">
         <v>13</v>
       </c>
       <c r="CA3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1395,25 +1395,25 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
         <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W4" t="n">
         <v>1.47</v>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
@@ -1467,7 +1467,7 @@
         <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>14.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1619,49 +1619,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="U5" t="n">
         <v>2.34</v>
@@ -1730,7 +1730,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
         <v>15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -1903,7 +1903,7 @@
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.87</v>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ6" t="n">
         <v>5.1</v>
@@ -2074,19 +2074,19 @@
         <v>5.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
         <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>5.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
@@ -2244,7 +2244,7 @@
         <v>9.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.72</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
         <v>5.8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
         <v>1.49</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
         <v>460</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
         <v>14.5</v>
@@ -2967,10 +2967,10 @@
         <v>200</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>34</v>
@@ -2991,22 +2991,22 @@
         <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO10" t="n">
         <v>280</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>7.6</v>
@@ -3015,13 +3015,13 @@
         <v>10.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY10" t="n">
         <v>9.199999999999999</v>
@@ -3030,7 +3030,7 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
         <v>10</v>
@@ -3039,16 +3039,16 @@
         <v>11</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
         <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="n">
         <v>4.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J11" t="n">
         <v>7.2</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.17</v>
@@ -3167,22 +3167,22 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.11</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q11" t="n">
         <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T11" t="n">
         <v>1.77</v>
@@ -3197,7 +3197,7 @@
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
@@ -3212,7 +3212,7 @@
         <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD11" t="n">
         <v>12.5</v>
@@ -3230,7 +3230,7 @@
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ11" t="n">
         <v>440</v>
@@ -3251,19 +3251,19 @@
         <v>3.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>15.5</v>
@@ -3275,10 +3275,10 @@
         <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>19</v>
@@ -3287,25 +3287,25 @@
         <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BE11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI11" t="n">
         <v>4.4</v>
@@ -3323,19 +3323,19 @@
         <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BO11" t="n">
         <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BS11" t="n">
         <v>1.04</v>
@@ -3344,29 +3344,29 @@
         <v>5.1</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY11" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -3430,7 +3430,7 @@
         <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
@@ -3442,7 +3442,7 @@
         <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
         <v>1.87</v>
@@ -3580,7 +3580,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>42</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.42</v>
       </c>
       <c r="G13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H13" t="n">
         <v>7</v>
@@ -3663,46 +3663,46 @@
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X13" t="n">
         <v>40</v>
@@ -3714,7 +3714,7 @@
         <v>80</v>
       </c>
       <c r="AA13" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB13" t="n">
         <v>15.5</v>
@@ -3726,7 +3726,7 @@
         <v>34</v>
       </c>
       <c r="AE13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF13" t="n">
         <v>13.5</v>
@@ -3735,40 +3735,40 @@
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
         <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AX13" t="n">
         <v>9</v>
@@ -3792,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB13" t="n">
         <v>10.5</v>
@@ -3804,37 +3804,37 @@
         <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
         <v>3.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BI13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
         <v>1.04</v>
       </c>
       <c r="BL13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BM13" t="n">
         <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP13" t="n">
         <v>9.6</v>
@@ -3843,7 +3843,7 @@
         <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS13" t="n">
         <v>1.04</v>
@@ -3867,14 +3867,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA13" t="n">
         <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.8</v>
@@ -3923,7 +3923,7 @@
         <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3935,88 +3935,88 @@
         <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U14" t="n">
         <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
         <v>2.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>1.01</v>
@@ -4025,49 +4025,49 @@
         <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
         <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
         <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI14" t="n">
         <v>3.6</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BN14" t="n">
         <v>5.5</v>
@@ -4106,19 +4106,19 @@
         <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV14" t="n">
         <v>38</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BX14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ14" t="n">
         <v>16</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
         <v>2.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="U15" t="n">
         <v>2.58</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="R16" t="n">
         <v>1.73</v>
@@ -4455,7 +4455,7 @@
         <v>2.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U16" t="n">
         <v>2.48</v>
@@ -4584,59 +4584,59 @@
         <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BL16" t="n">
         <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BO16" t="n">
         <v>4.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BR16" t="n">
         <v>23</v>
       </c>
       <c r="BS16" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="BV16" t="n">
         <v>27</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BX16" t="n">
         <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BZ16" t="n">
         <v>15</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>4.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I17" t="n">
         <v>2.08</v>
@@ -4700,7 +4700,7 @@
         <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="R17" t="n">
         <v>1.59</v>
@@ -4736,7 +4736,7 @@
         <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>16</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -4927,10 +4927,10 @@
         <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J18" t="n">
         <v>3.5</v>
@@ -4945,31 +4945,31 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
         <v>1.61</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
         <v>1.42</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5295,22 +5295,22 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU19" t="n">
         <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.01</v>
@@ -5319,13 +5319,13 @@
         <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5471,10 @@
         <v>2.46</v>
       </c>
       <c r="T20" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="V20" t="n">
         <v>1.71</v>
@@ -5600,7 +5600,7 @@
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="BL20" t="n">
         <v>90</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G21" t="n">
         <v>4.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I21" t="n">
         <v>1.95</v>
@@ -5716,7 +5716,7 @@
         <v>2.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R21" t="n">
         <v>1.75</v>
@@ -5734,7 +5734,7 @@
         <v>2.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5764,7 +5764,7 @@
         <v>55</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
         <v>23</v>
@@ -5842,7 +5842,7 @@
         <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="G22" t="n">
         <v>1.76</v>
@@ -5946,22 +5946,22 @@
         <v>5.8</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
         <v>1.44</v>
@@ -5970,7 +5970,7 @@
         <v>1.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
@@ -5982,10 +5982,10 @@
         <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
         <v>2.3</v>
@@ -6003,10 +6003,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>950</v>
@@ -6048,61 +6048,61 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY22" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="BA22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.15</v>
       </c>
-      <c r="BB22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE22" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="BH22" t="n">
         <v>3.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ22" t="n">
         <v>13.5</v>
@@ -6114,37 +6114,37 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BP22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BR22" t="n">
         <v>40</v>
       </c>
       <c r="BS22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU22" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="BV22" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX22" t="n">
         <v>90</v>
@@ -6153,14 +6153,14 @@
         <v>5.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA22" t="n">
         <v>5.1</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6200,10 +6200,10 @@
         <v>1.86</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>3.85</v>
@@ -6236,10 +6236,10 @@
         <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W23" t="n">
         <v>1.23</v>
@@ -6392,7 +6392,7 @@
         <v>5</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV23" t="n">
         <v>16.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6451,10 +6451,10 @@
         <v>1.35</v>
       </c>
       <c r="H24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -6469,25 +6469,25 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" t="n">
         <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
         <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U24" t="n">
         <v>1.46</v>
@@ -6520,19 +6520,19 @@
         <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AF24" t="n">
         <v>6.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
         <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AJ24" t="n">
         <v>11</v>
@@ -6541,10 +6541,10 @@
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AN24" t="n">
         <v>7.8</v>
@@ -6556,25 +6556,25 @@
         <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX24" t="n">
         <v>5.4</v>
@@ -6586,7 +6586,7 @@
         <v>36</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB24" t="n">
         <v>8</v>
@@ -6595,80 +6595,80 @@
         <v>16</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BJ24" t="n">
         <v>22</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="BP24" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BR24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BT24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BZ24" t="n">
         <v>23</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G25" t="n">
         <v>1.93</v>
@@ -6735,16 +6735,16 @@
         <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T25" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="U25" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.29</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7207,25 +7207,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H27" t="n">
         <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
         <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -7237,7 +7237,7 @@
         <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
         <v>1.96</v>
@@ -7249,16 +7249,16 @@
         <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W27" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X27" t="n">
         <v>950</v>
@@ -7267,40 +7267,40 @@
         <v>950</v>
       </c>
       <c r="Z27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC27" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
         <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AH27" t="n">
         <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
@@ -7309,22 +7309,22 @@
         <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT27" t="n">
         <v>5.9</v>
@@ -7333,10 +7333,10 @@
         <v>5.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX27" t="n">
         <v>3.3</v>
@@ -7345,22 +7345,22 @@
         <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BC27" t="n">
         <v>3.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF27" t="n">
         <v>3.55</v>
@@ -7372,7 +7372,7 @@
         <v>3.65</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ27" t="n">
         <v>950</v>
@@ -7387,13 +7387,13 @@
         <v>4.8</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO27" t="n">
         <v>3.55</v>
       </c>
       <c r="BP27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ27" t="n">
         <v>3.85</v>
@@ -7405,16 +7405,16 @@
         <v>4.4</v>
       </c>
       <c r="BT27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU27" t="n">
         <v>5.7</v>
       </c>
       <c r="BV27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX27" t="n">
         <v>65</v>
@@ -7426,11 +7426,11 @@
         <v>36</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7461,230 +7461,230 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="I28" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.22</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="S28" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T28" t="n">
         <v>1.44</v>
       </c>
       <c r="U28" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V28" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Y28" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB28" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AC28" t="n">
         <v>12</v>
       </c>
       <c r="AD28" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AG28" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ28" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
         <v>55</v>
       </c>
       <c r="AN28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS28" t="n">
         <v>18</v>
       </c>
       <c r="AT28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG28" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD28" t="n">
+      <c r="BH28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT28" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>6</v>
       </c>
       <c r="BU28" t="n">
         <v>4.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW28" t="n">
         <v>1.04</v>
       </c>
       <c r="BX28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY28" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA28" t="n">
         <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>20</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="I30" t="n">
         <v>1.57</v>
@@ -7999,7 +7999,7 @@
         <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
         <v>1.55</v>
@@ -8014,10 +8014,10 @@
         <v>1.62</v>
       </c>
       <c r="U30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W30" t="n">
         <v>1.14</v>
@@ -8047,7 +8047,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AG30" t="n">
         <v>32</v>
@@ -8119,7 +8119,7 @@
         <v>4.7</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE30" t="n">
         <v>4.7</v>
@@ -8143,19 +8143,19 @@
         <v>1.04</v>
       </c>
       <c r="BL30" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM30" t="n">
         <v>1.04</v>
       </c>
       <c r="BN30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO30" t="n">
         <v>1.04</v>
       </c>
       <c r="BP30" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.04</v>
@@ -8167,7 +8167,7 @@
         <v>1.04</v>
       </c>
       <c r="BT30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU30" t="n">
         <v>3.35</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X31" t="n">
         <v>12.5</v>
@@ -8385,7 +8385,7 @@
         <v>5</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BI31" t="n">
         <v>2.72</v>
@@ -8394,13 +8394,13 @@
         <v>13.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BL31" t="n">
         <v>240</v>
       </c>
       <c r="BM31" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BN31" t="n">
         <v>4.6</v>
@@ -8412,41 +8412,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BR31" t="n">
         <v>40</v>
       </c>
       <c r="BS31" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BT31" t="n">
         <v>11</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV31" t="n">
         <v>75</v>
       </c>
       <c r="BW31" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX31" t="n">
         <v>90</v>
       </c>
       <c r="BY31" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BZ31" t="n">
         <v>36</v>
       </c>
       <c r="CA31" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I33" t="n">
         <v>1.7</v>
@@ -8773,7 +8773,7 @@
         <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
         <v>1.9</v>
@@ -8782,7 +8782,7 @@
         <v>2.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X33" t="n">
         <v>13</v>
@@ -8791,7 +8791,7 @@
         <v>7.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="n">
         <v>16.5</v>
@@ -8818,7 +8818,7 @@
         <v>24</v>
       </c>
       <c r="AI33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="n">
         <v>180</v>
@@ -8839,7 +8839,7 @@
         <v>11</v>
       </c>
       <c r="AP33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>7.4</v>
@@ -8848,7 +8848,7 @@
         <v>8.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT33" t="n">
         <v>16.5</v>
@@ -8872,7 +8872,7 @@
         <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB33" t="n">
         <v>48</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="G34" t="n">
         <v>2.02</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K34" t="n">
         <v>4.6</v>
@@ -9009,16 +9009,16 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
@@ -9033,7 +9033,7 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W34" t="n">
         <v>1.98</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-18 19:35:30</t>
+          <t>2026-05-18 21:46:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -866,10 +866,10 @@
         <v>3.3</v>
       </c>
       <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
@@ -878,28 +878,28 @@
         <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
         <v>2.24</v>
@@ -974,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
@@ -992,7 +992,7 @@
         <v>13.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -1007,16 +1007,16 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
@@ -1040,7 +1040,7 @@
         <v>5.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
         <v>16.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1141,43 +1141,43 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AA3" t="n">
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
         <v>12</v>
@@ -1189,7 +1189,7 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1204,7 +1204,7 @@
         <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -1213,19 +1213,19 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1237,13 +1237,13 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
@@ -1255,22 +1255,22 @@
         <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="n">
         <v>5.4</v>
@@ -1282,59 +1282,59 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL3" t="n">
         <v>75</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT3" t="n">
         <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV3" t="n">
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.92</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
         <v>2.46</v>
@@ -1389,19 +1389,19 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
         <v>2.46</v>
@@ -1410,7 +1410,7 @@
         <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V4" t="n">
         <v>1.68</v>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>46</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
@@ -1467,28 +1467,28 @@
         <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>14.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
         <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>4.1</v>
@@ -1500,19 +1500,19 @@
         <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
         <v>21</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
         <v>5</v>
@@ -1521,10 +1521,10 @@
         <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
         <v>4.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
         <v>2.76</v>
@@ -1637,13 +1637,13 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
@@ -1661,16 +1661,16 @@
         <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
         <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1697,13 +1697,13 @@
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1727,7 +1727,7 @@
         <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1760,19 +1760,19 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
         <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
@@ -1790,7 +1790,7 @@
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
@@ -1808,10 +1808,10 @@
         <v>27</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
         <v>4.2</v>
@@ -1826,23 +1826,23 @@
         <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
         <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5" t="n">
         <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W6" t="n">
         <v>1.33</v>
@@ -2044,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2059,16 +2059,16 @@
         <v>5.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2080,23 +2080,23 @@
         <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ6" t="n">
         <v>28</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I7" t="n">
         <v>1.76</v>
@@ -2145,7 +2145,7 @@
         <v>5.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
         <v>3.55</v>
@@ -2644,10 +2644,10 @@
         <v>2.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -2659,7 +2659,7 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.18</v>
@@ -2683,7 +2683,7 @@
         <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W9" t="n">
         <v>1.39</v>
@@ -2800,7 +2800,7 @@
         <v>5.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
         <v>950</v>
@@ -2809,13 +2809,13 @@
         <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM9" t="n">
         <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
         <v>5.5</v>
@@ -2833,13 +2833,13 @@
         <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU9" t="n">
         <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW9" t="n">
         <v>1.04</v>
@@ -2851,14 +2851,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
         <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         <v>1.86</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
         <v>1.93</v>
@@ -3203,7 +3203,7 @@
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
         <v>11.5</v>
@@ -3212,7 +3212,7 @@
         <v>950</v>
       </c>
       <c r="AC11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD11" t="n">
         <v>12.5</v>
@@ -3230,7 +3230,7 @@
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ11" t="n">
         <v>440</v>
@@ -3248,10 +3248,10 @@
         <v>150</v>
       </c>
       <c r="AO11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>13.5</v>
@@ -3263,7 +3263,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU11" t="n">
         <v>15.5</v>
@@ -3275,34 +3275,34 @@
         <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA11" t="n">
         <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF11" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BH11" t="n">
         <v>7</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
         <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>20</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -3678,7 +3678,7 @@
         <v>7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
         <v>3.2</v>
@@ -3693,10 +3693,10 @@
         <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>1.14</v>
@@ -3759,16 +3759,16 @@
         <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>9.6</v>
@@ -3804,10 +3804,10 @@
         <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BG13" t="n">
         <v>5.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -3953,10 +3953,10 @@
         <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>30</v>
@@ -4067,68 +4067,68 @@
         <v>1.05</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4192,13 +4192,13 @@
         <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
         <v>1.45</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4449,10 +4449,10 @@
         <v>1.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
         <v>1.49</v>
@@ -4467,7 +4467,7 @@
         <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
         <v>26</v>
@@ -4491,19 +4491,19 @@
         <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
         <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>18.5</v>
@@ -4515,7 +4515,7 @@
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
         <v>24</v>
@@ -4554,7 +4554,7 @@
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.05</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
         <v>17.5</v>
@@ -4575,7 +4575,7 @@
         <v>16.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BI16" t="n">
         <v>3.9</v>
@@ -4584,59 +4584,59 @@
         <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="BL16" t="n">
         <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN16" t="n">
         <v>6.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP16" t="n">
         <v>15</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR16" t="n">
         <v>23</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT16" t="n">
         <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV16" t="n">
         <v>27</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BX16" t="n">
         <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BZ16" t="n">
         <v>15</v>
       </c>
       <c r="CA16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
         <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB17" t="n">
         <v>950</v>
@@ -4745,7 +4745,7 @@
         <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG17" t="n">
         <v>25</v>
@@ -4754,7 +4754,7 @@
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -4838,7 +4838,7 @@
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4850,7 +4850,7 @@
         <v>11</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP17" t="n">
         <v>40</v>
@@ -4868,7 +4868,7 @@
         <v>7</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BV17" t="n">
         <v>18</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
         <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG18" t="n">
         <v>11</v>
@@ -5092,7 +5092,7 @@
         <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,7 +5104,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP18" t="n">
         <v>34</v>
@@ -5122,7 +5122,7 @@
         <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV18" t="n">
         <v>23</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
         <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
         <v>55</v>
@@ -5298,7 +5298,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
         <v>16.5</v>
@@ -5313,7 +5313,7 @@
         <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
@@ -5325,13 +5325,13 @@
         <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>21</v>
+        <v>1.05</v>
       </c>
       <c r="BE19" t="n">
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
@@ -5358,7 +5358,7 @@
         <v>6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP19" t="n">
         <v>14.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>4.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I21" t="n">
         <v>1.95</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G22" t="n">
         <v>1.76</v>
@@ -5949,34 +5949,34 @@
         <v>7.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>1.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
         <v>2.16</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
         <v>2.02</v>
@@ -6048,25 +6048,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AX22" t="n">
         <v>7.6</v>
@@ -6075,31 +6075,31 @@
         <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI22" t="n">
         <v>2.5</v>
@@ -6114,13 +6114,13 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BN22" t="n">
         <v>4.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP22" t="n">
         <v>14.5</v>
@@ -6132,35 +6132,35 @@
         <v>40</v>
       </c>
       <c r="BS22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT22" t="n">
         <v>11</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX22" t="n">
         <v>90</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ22" t="n">
         <v>36</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>5.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I23" t="n">
         <v>1.95</v>
@@ -6209,7 +6209,7 @@
         <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -6224,7 +6224,7 @@
         <v>1.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R23" t="n">
         <v>1.27</v>
@@ -6233,10 +6233,10 @@
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
         <v>2.04</v>
@@ -6284,7 +6284,7 @@
         <v>140</v>
       </c>
       <c r="AK23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="n">
         <v>85</v>
@@ -6371,7 +6371,7 @@
         <v>5.7</v>
       </c>
       <c r="BN23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO23" t="n">
         <v>3.6</v>
@@ -6395,7 +6395,7 @@
         <v>3.55</v>
       </c>
       <c r="BV23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW23" t="n">
         <v>4.3</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -6484,13 +6484,13 @@
         <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
         <v>2.72</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
@@ -6520,7 +6520,7 @@
         <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="AF24" t="n">
         <v>6.4</v>
@@ -6559,7 +6559,7 @@
         <v>6.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS24" t="n">
         <v>8.4</v>
@@ -6574,7 +6574,7 @@
         <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
         <v>5.4</v>
@@ -6586,7 +6586,7 @@
         <v>36</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB24" t="n">
         <v>8</v>
@@ -6598,7 +6598,7 @@
         <v>7.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
         <v>6.4</v>
@@ -6610,65 +6610,65 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BJ24" t="n">
         <v>22</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.79</v>
+        <v>10</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BN24" t="n">
         <v>4.3</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BP24" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR24" t="n">
         <v>48</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BT24" t="n">
         <v>24</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BZ24" t="n">
         <v>23</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -6723,16 +6723,16 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
         <v>1.45</v>
@@ -6741,10 +6741,10 @@
         <v>2.78</v>
       </c>
       <c r="T25" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
         <v>1.29</v>
@@ -6759,7 +6759,7 @@
         <v>19</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="n">
         <v>90</v>
@@ -6777,13 +6777,13 @@
         <v>48</v>
       </c>
       <c r="AF25" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI25" t="n">
         <v>50</v>
@@ -6804,7 +6804,7 @@
         <v>11</v>
       </c>
       <c r="AO25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP25" t="n">
         <v>17</v>
@@ -6813,16 +6813,16 @@
         <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
         <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV25" t="n">
         <v>15.5</v>
@@ -6840,7 +6840,7 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
         <v>20</v>
@@ -6855,10 +6855,10 @@
         <v>11</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6882,7 +6882,7 @@
         <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP25" t="n">
         <v>18</v>
@@ -6900,7 +6900,7 @@
         <v>11</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="BV25" t="n">
         <v>48</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7210,10 +7210,10 @@
         <v>1.85</v>
       </c>
       <c r="G27" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
         <v>5.6</v>
@@ -7222,7 +7222,7 @@
         <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -7237,28 +7237,28 @@
         <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
         <v>1.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
         <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>950</v>
@@ -7267,10 +7267,10 @@
         <v>950</v>
       </c>
       <c r="Z27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA27" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
         <v>9.6</v>
@@ -7282,10 +7282,10 @@
         <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG27" t="n">
         <v>950</v>
@@ -7297,7 +7297,7 @@
         <v>95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
         <v>27</v>
@@ -7309,10 +7309,10 @@
         <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP27" t="n">
         <v>8.6</v>
@@ -7321,7 +7321,7 @@
         <v>3.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS27" t="n">
         <v>4.2</v>
@@ -7333,13 +7333,13 @@
         <v>5.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW27" t="n">
         <v>4.1</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
         <v>7.8</v>
@@ -7354,7 +7354,7 @@
         <v>3.75</v>
       </c>
       <c r="BC27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BD27" t="n">
         <v>4</v>
@@ -7366,46 +7366,46 @@
         <v>3.55</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ27" t="n">
         <v>950</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BL27" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BM27" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO27" t="n">
         <v>3.55</v>
       </c>
       <c r="BP27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BR27" t="n">
         <v>38</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BT27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU27" t="n">
         <v>5.7</v>
@@ -7414,23 +7414,23 @@
         <v>55</v>
       </c>
       <c r="BW27" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7497,10 +7497,10 @@
         <v>1.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T28" t="n">
         <v>1.44</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -7999,10 +7999,10 @@
         <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R30" t="n">
         <v>1.58</v>
@@ -8155,7 +8155,7 @@
         <v>1.04</v>
       </c>
       <c r="BP30" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.04</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -8232,16 +8232,16 @@
         <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>3.25</v>
       </c>
       <c r="K31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
@@ -8268,7 +8268,7 @@
         <v>2.18</v>
       </c>
       <c r="U31" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
         <v>1.16</v>
@@ -8280,7 +8280,7 @@
         <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z31" t="n">
         <v>60</v>
@@ -8337,13 +8337,13 @@
         <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AU31" t="n">
         <v>3.35</v>
@@ -8352,7 +8352,7 @@
         <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
         <v>3.5</v>
@@ -8361,34 +8361,34 @@
         <v>3.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC31" t="n">
         <v>4.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF31" t="n">
         <v>4</v>
       </c>
       <c r="BG31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH31" t="n">
         <v>3.3</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="BJ31" t="n">
         <v>13.5</v>
@@ -8406,7 +8406,7 @@
         <v>4.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP31" t="n">
         <v>14.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="H32" t="n">
         <v>2.94</v>
@@ -8501,7 +8501,7 @@
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O32" t="n">
         <v>1.45</v>
@@ -8510,7 +8510,7 @@
         <v>1.58</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -8585,58 +8585,58 @@
         <v>60</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AQ32" t="n">
         <v>3.55</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="AT32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE32" t="n">
         <v>3.45</v>
       </c>
-      <c r="AU32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF32" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="BH32" t="n">
         <v>3.25</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
         <v>6.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I33" t="n">
         <v>1.7</v>
@@ -8869,7 +8869,7 @@
         <v>21</v>
       </c>
       <c r="AZ33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA33" t="n">
         <v>36</v>
@@ -8902,28 +8902,28 @@
         <v>13.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL33" t="n">
         <v>200</v>
       </c>
       <c r="BM33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN33" t="n">
         <v>11.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP33" t="n">
         <v>60</v>
       </c>
       <c r="BQ33" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR33" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="BS33" t="n">
         <v>8.800000000000001</v>
@@ -8938,13 +8938,13 @@
         <v>11.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX33" t="n">
         <v>29</v>
       </c>
       <c r="BY33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="G34" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9015,10 +9015,10 @@
         <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
@@ -9033,10 +9033,10 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W34" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X34" t="n">
         <v>14</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-18 21:46:56</t>
+          <t>2026-05-19 00:00:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
@@ -878,61 +878,61 @@
         <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
         <v>16</v>
@@ -941,55 +941,55 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
         <v>30</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
@@ -998,28 +998,28 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
         <v>3.05</v>
@@ -1028,13 +1028,13 @@
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.3</v>
@@ -1046,10 +1046,10 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
         <v>7.2</v>
@@ -1064,23 +1064,23 @@
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CA2" t="n">
         <v>6.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>2.34</v>
       </c>
       <c r="I4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1389,31 +1389,31 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
         <v>1.47</v>
@@ -1422,28 +1422,28 @@
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1503,10 +1503,10 @@
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
         <v>27</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1652,19 +1652,19 @@
         <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
         <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.57</v>
@@ -1736,7 +1736,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1760,13 +1760,13 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD5" t="n">
         <v>30</v>
@@ -1802,7 +1802,7 @@
         <v>7.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
         <v>27</v>
@@ -1811,10 +1811,10 @@
         <v>4.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
@@ -1829,10 +1829,10 @@
         <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1903,7 +1903,7 @@
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
         <v>1.92</v>
@@ -2050,13 +2050,13 @@
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BP6" t="n">
         <v>36</v>
@@ -2068,7 +2068,7 @@
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT6" t="n">
         <v>5.6</v>
@@ -2083,7 +2083,7 @@
         <v>4.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
         <v>5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,13 +2151,13 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.14</v>
@@ -2169,13 +2169,13 @@
         <v>1.14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>12.5</v>
       </c>
       <c r="G8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -2405,7 +2405,7 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.11</v>
@@ -2417,7 +2417,7 @@
         <v>1.37</v>
       </c>
       <c r="R8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S8" t="n">
         <v>1.9</v>
@@ -2429,7 +2429,7 @@
         <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
@@ -2441,7 +2441,7 @@
         <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA8" t="n">
         <v>11</v>
@@ -2540,7 +2540,7 @@
         <v>42</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BH8" t="n">
         <v>7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2668,25 +2668,25 @@
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>9.6</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
         <v>5.2</v>
@@ -2913,25 +2913,25 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
         <v>1.84</v>
@@ -2955,7 +2955,7 @@
         <v>450</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
         <v>14.5</v>
@@ -2967,7 +2967,7 @@
         <v>200</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
@@ -3009,7 +3009,7 @@
         <v>95</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
         <v>10.5</v>
@@ -3024,16 +3024,16 @@
         <v>7.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA10" t="n">
         <v>42</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -3051,7 +3051,7 @@
         <v>48</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI10" t="n">
         <v>3.1</v>
@@ -3060,13 +3060,13 @@
         <v>14.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BL10" t="n">
         <v>190</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
@@ -3081,38 +3081,38 @@
         <v>6</v>
       </c>
       <c r="BR10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT10" t="n">
         <v>15.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV10" t="n">
         <v>110</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX10" t="n">
         <v>100</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="I11" t="n">
         <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
         <v>1.23</v>
@@ -3194,7 +3194,7 @@
         <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G12" t="n">
         <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="U12" t="n">
         <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3460,7 +3460,7 @@
         <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
@@ -3499,13 +3499,13 @@
         <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO12" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.199999999999999</v>
@@ -3514,10 +3514,10 @@
         <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
         <v>7.4</v>
@@ -3526,49 +3526,49 @@
         <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BC12" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BL12" t="n">
         <v>120</v>
@@ -3580,7 +3580,7 @@
         <v>11.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP12" t="n">
         <v>55</v>
@@ -3595,10 +3595,10 @@
         <v>4.3</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="BV12" t="n">
         <v>12</v>
@@ -3610,7 +3610,7 @@
         <v>26</v>
       </c>
       <c r="BY12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3663,10 @@
         <v>2.28</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.25</v>
@@ -3675,7 +3675,7 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.18</v>
@@ -3684,10 +3684,10 @@
         <v>2.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
         <v>2.32</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3908,19 +3908,19 @@
         <v>1.09</v>
       </c>
       <c r="G14" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>210</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3932,31 +3932,31 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.09</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4198,19 +4198,19 @@
         <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4413,28 +4413,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
         <v>1.99</v>
       </c>
       <c r="H16" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
         <v>7.2</v>
@@ -4443,25 +4443,25 @@
         <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -4476,7 +4476,7 @@
         <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
         <v>21</v>
@@ -4521,7 +4521,7 @@
         <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
         <v>18</v>
@@ -4542,7 +4542,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX16" t="n">
         <v>12</v>
@@ -4584,59 +4584,59 @@
         <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL16" t="n">
         <v>75</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR16" t="n">
         <v>23</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="BV16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX16" t="n">
         <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>14.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -4796,7 +4796,7 @@
         <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>9</v>
@@ -4823,7 +4823,7 @@
         <v>11.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG17" t="n">
         <v>13</v>
@@ -4838,7 +4838,7 @@
         <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="BL17" t="n">
         <v>140</v>
@@ -4868,13 +4868,13 @@
         <v>5.9</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV17" t="n">
         <v>18</v>
       </c>
       <c r="BW17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX17" t="n">
         <v>34</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
         <v>5.5</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.2</v>
@@ -4948,25 +4948,25 @@
         <v>7.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="S18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
         <v>1.14</v>
@@ -4990,7 +4990,7 @@
         <v>15.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
         <v>34</v>
@@ -4999,7 +4999,7 @@
         <v>95</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -5029,16 +5029,16 @@
         <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -5050,7 +5050,7 @@
         <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5062,7 +5062,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -5074,77 +5074,77 @@
         <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BL18" t="n">
         <v>90</v>
       </c>
       <c r="BM18" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP18" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BR18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BT18" t="n">
         <v>13</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BV18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW18" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BX18" t="n">
         <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -5178,13 +5178,13 @@
         <v>1.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
         <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.8</v>
@@ -5196,7 +5196,7 @@
         <v>1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
         <v>5.6</v>
@@ -5223,10 +5223,10 @@
         <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
         <v>32</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -5432,10 +5432,10 @@
         <v>2.74</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I20" t="n">
         <v>2.56</v>
@@ -5450,7 +5450,7 @@
         <v>1.22</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
         <v>6.2</v>
@@ -5459,28 +5459,28 @@
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R20" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="S20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V20" t="n">
         <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5513,10 +5513,10 @@
         <v>16</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ20" t="n">
         <v>50</v>
@@ -5525,7 +5525,7 @@
         <v>30</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
         <v>55</v>
@@ -5534,7 +5534,7 @@
         <v>16</v>
       </c>
       <c r="AO20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
         <v>1.05</v>
@@ -5552,7 +5552,7 @@
         <v>15.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV20" t="n">
         <v>9.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>3.3</v>
@@ -5698,10 +5698,10 @@
         <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5719,7 +5719,7 @@
         <v>1.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
         <v>2.8</v>
@@ -5728,7 +5728,7 @@
         <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
         <v>1.66</v>
@@ -5854,59 +5854,59 @@
         <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="BL21" t="n">
         <v>110</v>
       </c>
       <c r="BM21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BP21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BR21" t="n">
         <v>38</v>
       </c>
       <c r="BS21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV21" t="n">
         <v>19.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BX21" t="n">
         <v>32</v>
       </c>
       <c r="BY21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BZ21" t="n">
         <v>25</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.3</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
         <v>1.04</v>
@@ -5964,85 +5964,85 @@
         <v>5.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S22" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V22" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="X22" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF22" t="n">
         <v>32</v>
       </c>
-      <c r="Y22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AG22" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>18</v>
-      </c>
       <c r="AH22" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AK22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL22" t="n">
         <v>42</v>
       </c>
       <c r="AM22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AP22" t="n">
         <v>18.5</v>
@@ -6051,16 +6051,16 @@
         <v>11.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>18.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
         <v>9.199999999999999</v>
@@ -6072,10 +6072,10 @@
         <v>1.05</v>
       </c>
       <c r="AY22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>1.05</v>
@@ -6084,83 +6084,83 @@
         <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE22" t="n">
         <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.05</v>
+        <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BI22" t="n">
         <v>3.45</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
         <v>6.4</v>
       </c>
       <c r="BL22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM22" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BN22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BP22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BR22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS22" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BT22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY22" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BZ22" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>3.3</v>
       </c>
       <c r="H23" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="I23" t="n">
         <v>2.42</v>
@@ -6206,7 +6206,7 @@
         <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.3</v>
@@ -6236,7 +6236,7 @@
         <v>1.46</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="V23" t="n">
         <v>1.71</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -6448,19 +6448,19 @@
         <v>3.65</v>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I24" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.2</v>
@@ -6493,7 +6493,7 @@
         <v>2.46</v>
       </c>
       <c r="V24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W24" t="n">
         <v>1.31</v>
@@ -6664,11 +6664,11 @@
         <v>14</v>
       </c>
       <c r="CA24" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>1.75</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I25" t="n">
         <v>7.2</v>
@@ -6714,7 +6714,7 @@
         <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>1.43</v>
@@ -6729,10 +6729,10 @@
         <v>1.44</v>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
@@ -6744,7 +6744,7 @@
         <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
         <v>1.16</v>
@@ -6870,7 +6870,7 @@
         <v>13.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6888,7 +6888,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR25" t="n">
         <v>40</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         <v>5.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J26" t="n">
         <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.43</v>
@@ -6977,7 +6977,7 @@
         <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
         <v>1.36</v>
@@ -6986,7 +6986,7 @@
         <v>1.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R26" t="n">
         <v>1.29</v>
@@ -6995,13 +6995,13 @@
         <v>3.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
         <v>1.89</v>
       </c>
       <c r="V26" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W26" t="n">
         <v>1.2</v>
@@ -7016,7 +7016,7 @@
         <v>11</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="n">
         <v>16.5</v>
@@ -7076,7 +7076,7 @@
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -7085,7 +7085,7 @@
         <v>17.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>17</v>
@@ -7094,10 +7094,10 @@
         <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
         <v>10</v>
@@ -7124,7 +7124,7 @@
         <v>12.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL26" t="n">
         <v>180</v>
@@ -7136,7 +7136,7 @@
         <v>10</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="BP26" t="n">
         <v>60</v>
@@ -7154,13 +7154,13 @@
         <v>4.8</v>
       </c>
       <c r="BU26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV26" t="n">
         <v>14.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX26" t="n">
         <v>36</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G27" t="n">
         <v>1.36</v>
       </c>
       <c r="H27" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="I27" t="n">
         <v>18.5</v>
@@ -7225,13 +7225,13 @@
         <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.36</v>
@@ -7246,13 +7246,13 @@
         <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
         <v>1.05</v>
@@ -7267,7 +7267,7 @@
         <v>950</v>
       </c>
       <c r="Z27" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
@@ -7282,7 +7282,7 @@
         <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="AF27" t="n">
         <v>6.6</v>
@@ -7306,7 +7306,7 @@
         <v>75</v>
       </c>
       <c r="AM27" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
         <v>7.8</v>
@@ -7315,10 +7315,10 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AR27" t="n">
         <v>7.8</v>
@@ -7330,7 +7330,7 @@
         <v>5.3</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV27" t="n">
         <v>7.2</v>
@@ -7357,7 +7357,7 @@
         <v>6</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
         <v>8</v>
@@ -7369,7 +7369,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI27" t="n">
         <v>2.68</v>
@@ -7390,10 +7390,10 @@
         <v>3.85</v>
       </c>
       <c r="BO27" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BP27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ27" t="n">
         <v>5.8</v>
@@ -7402,7 +7402,7 @@
         <v>42</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT27" t="n">
         <v>22</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G28" t="n">
         <v>1.69</v>
@@ -7470,13 +7470,13 @@
         <v>5.4</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
         <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.26</v>
@@ -7503,13 +7503,13 @@
         <v>2.46</v>
       </c>
       <c r="T28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
         <v>2.44</v>
@@ -7632,7 +7632,7 @@
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="BL28" t="n">
         <v>110</v>
@@ -7644,7 +7644,7 @@
         <v>5.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP28" t="n">
         <v>12</v>
@@ -7662,7 +7662,7 @@
         <v>10.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="BV28" t="n">
         <v>46</v>
@@ -7680,11 +7680,11 @@
         <v>16.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
         <v>1.49</v>
       </c>
       <c r="I29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -7748,16 +7748,16 @@
         <v>2.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S29" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T29" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U29" t="n">
         <v>2.4</v>
@@ -7802,7 +7802,7 @@
         <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
         <v>170</v>
@@ -7814,7 +7814,7 @@
         <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN29" t="n">
         <v>55</v>
@@ -7823,7 +7823,7 @@
         <v>5.2</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BD29" t="n">
         <v>7.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -8011,13 +8011,13 @@
         <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="U30" t="n">
         <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W30" t="n">
         <v>1.14</v>
@@ -8101,7 +8101,7 @@
         <v>12.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY30" t="n">
         <v>19</v>
@@ -8146,16 +8146,16 @@
         <v>120</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN30" t="n">
         <v>13</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP30" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BQ30" t="n">
         <v>4.3</v>
@@ -8182,17 +8182,17 @@
         <v>25</v>
       </c>
       <c r="BY30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BZ30" t="n">
         <v>15.5</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="G31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K31" t="n">
         <v>4.4</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.22</v>
@@ -8247,70 +8247,70 @@
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S31" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T31" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U31" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V31" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X31" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="Y31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB31" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AC31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AF31" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AG31" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AJ31" t="n">
         <v>80</v>
@@ -8325,64 +8325,64 @@
         <v>55</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AO31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR31" t="n">
         <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AY31" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BC31" t="n">
         <v>32</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BF31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BH31" t="n">
         <v>5.5</v>
@@ -8403,16 +8403,16 @@
         <v>5.2</v>
       </c>
       <c r="BN31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="BP31" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR31" t="n">
         <v>34</v>
@@ -8421,16 +8421,16 @@
         <v>4.8</v>
       </c>
       <c r="BT31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX31" t="n">
         <v>23</v>
@@ -8439,14 +8439,14 @@
         <v>4.5</v>
       </c>
       <c r="BZ31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA31" t="n">
         <v>4</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -8501,13 +8501,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
         <v>1.36</v>
@@ -8516,7 +8516,7 @@
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H33" t="n">
         <v>4.3</v>
@@ -8746,43 +8746,43 @@
         <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
         <v>1.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T33" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U33" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V33" t="n">
         <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X33" t="n">
         <v>19.5</v>
@@ -8812,7 +8812,7 @@
         <v>13.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH33" t="n">
         <v>17.5</v>
@@ -8833,7 +8833,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO33" t="n">
         <v>46</v>
@@ -8857,13 +8857,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY33" t="n">
         <v>9.199999999999999</v>
@@ -8872,37 +8872,37 @@
         <v>15.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD33" t="n">
         <v>24</v>
       </c>
       <c r="BE33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF33" t="n">
         <v>9.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH33" t="n">
         <v>4.5</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ33" t="n">
         <v>11.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BL33" t="n">
         <v>120</v>
@@ -8911,16 +8911,16 @@
         <v>4.6</v>
       </c>
       <c r="BN33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP33" t="n">
         <v>15</v>
       </c>
       <c r="BQ33" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BR33" t="n">
         <v>29</v>
@@ -8929,19 +8929,19 @@
         <v>4.1</v>
       </c>
       <c r="BT33" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="BV33" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW33" t="n">
         <v>4.3</v>
       </c>
       <c r="BX33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY33" t="n">
         <v>4.3</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
         <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L34" t="n">
         <v>1.37</v>
@@ -9012,13 +9012,13 @@
         <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P34" t="n">
         <v>1.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R34" t="n">
         <v>1.29</v>
@@ -9030,7 +9030,7 @@
         <v>1.89</v>
       </c>
       <c r="U34" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V34" t="n">
         <v>1.22</v>
@@ -9150,7 +9150,7 @@
         <v>3.3</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="BJ34" t="n">
         <v>12.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.69</v>
       </c>
       <c r="G35" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="H35" t="n">
         <v>5.3</v>
@@ -9251,19 +9251,19 @@
         <v>8</v>
       </c>
       <c r="J35" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
         <v>1.45</v>
@@ -9278,7 +9278,7 @@
         <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T35" t="n">
         <v>2.02</v>
@@ -9290,7 +9290,7 @@
         <v>1.14</v>
       </c>
       <c r="W35" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="X35" t="n">
         <v>12</v>
@@ -9371,7 +9371,7 @@
         <v>5.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY35" t="n">
         <v>3.7</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -9505,28 +9505,28 @@
         <v>3.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K36" t="n">
         <v>3.7</v>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M36" t="n">
         <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O36" t="n">
         <v>1.46</v>
       </c>
       <c r="P36" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R36" t="n">
         <v>1.23</v>
@@ -9598,40 +9598,40 @@
         <v>42</v>
       </c>
       <c r="AO36" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS36" t="n">
         <v>4.9</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU36" t="n">
         <v>3.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW36" t="n">
         <v>4.8</v>
       </c>
       <c r="AX36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY36" t="n">
         <v>4</v>
       </c>
-      <c r="AY36" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AZ36" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA36" t="n">
         <v>4.9</v>
@@ -9643,7 +9643,7 @@
         <v>4.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE36" t="n">
         <v>5.1</v>
@@ -9655,7 +9655,7 @@
         <v>4.9</v>
       </c>
       <c r="BH36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI36" t="n">
         <v>2.1</v>
@@ -9664,59 +9664,59 @@
         <v>970</v>
       </c>
       <c r="BK36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BN36" t="n">
         <v>6</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP36" t="n">
         <v>25</v>
       </c>
       <c r="BQ36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR36" t="n">
         <v>46</v>
       </c>
       <c r="BS36" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT36" t="n">
         <v>7.2</v>
       </c>
       <c r="BU36" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV36" t="n">
         <v>34</v>
       </c>
       <c r="BW36" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX36" t="n">
         <v>55</v>
       </c>
       <c r="BY36" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ36" t="n">
         <v>48</v>
       </c>
       <c r="CA36" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G37" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I37" t="n">
-        <v>200</v>
+        <v>990</v>
       </c>
       <c r="J37" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="K37" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9789,16 +9789,16 @@
         <v>1.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -10001,16 +10001,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I38" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>4.1</v>
@@ -10019,25 +10019,25 @@
         <v>4.2</v>
       </c>
       <c r="L38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O38" t="n">
         <v>1.36</v>
       </c>
       <c r="P38" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
         <v>3.85</v>
@@ -10046,13 +10046,13 @@
         <v>2.08</v>
       </c>
       <c r="U38" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V38" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
         <v>13.5</v>
@@ -10061,10 +10061,10 @@
         <v>7.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AB38" t="n">
         <v>17.5</v>
@@ -10082,7 +10082,7 @@
         <v>48</v>
       </c>
       <c r="AG38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH38" t="n">
         <v>24</v>
@@ -10100,10 +10100,10 @@
         <v>90</v>
       </c>
       <c r="AM38" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN38" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AO38" t="n">
         <v>11</v>
@@ -10127,13 +10127,13 @@
         <v>8.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW38" t="n">
         <v>18.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AY38" t="n">
         <v>21</v>
@@ -10178,7 +10178,7 @@
         <v>190</v>
       </c>
       <c r="BM38" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="BN38" t="n">
         <v>11.5</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -10261,13 +10261,13 @@
         <v>1.97</v>
       </c>
       <c r="H39" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J39" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K39" t="n">
         <v>3.95</v>
@@ -10372,7 +10372,7 @@
         <v>2.84</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.98</v>
+        <v>1.83</v>
       </c>
       <c r="AT39" t="n">
         <v>4.3</v>
@@ -10396,7 +10396,7 @@
         <v>7.2</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.96</v>
+        <v>1.82</v>
       </c>
       <c r="BB39" t="n">
         <v>7.2</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -10518,13 +10518,13 @@
         <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K40" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L40" t="n">
         <v>1.38</v>
@@ -10533,7 +10533,7 @@
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
         <v>1.41</v>
@@ -10545,7 +10545,7 @@
         <v>2.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
         <v>4.3</v>
@@ -10560,7 +10560,7 @@
         <v>1.1</v>
       </c>
       <c r="W40" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X40" t="n">
         <v>14</v>
@@ -10578,7 +10578,7 @@
         <v>6.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD40" t="n">
         <v>40</v>
@@ -10593,7 +10593,7 @@
         <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AI40" t="n">
         <v>250</v>
@@ -10623,10 +10623,10 @@
         <v>18</v>
       </c>
       <c r="AR40" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT40" t="n">
         <v>5.4</v>
@@ -10635,10 +10635,10 @@
         <v>9</v>
       </c>
       <c r="AV40" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX40" t="n">
         <v>6.2</v>
@@ -10647,10 +10647,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ40" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB40" t="n">
         <v>10</v>
@@ -10659,16 +10659,16 @@
         <v>16.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF40" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH40" t="n">
         <v>3.6</v>
@@ -10680,59 +10680,59 @@
         <v>17</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL40" t="n">
         <v>340</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO40" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BP40" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR40" t="n">
         <v>42</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT40" t="n">
         <v>16.5</v>
       </c>
       <c r="BU40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BV40" t="n">
         <v>150</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX40" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ40" t="n">
         <v>27</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
         <v>1.3</v>
       </c>
       <c r="P41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>1.87</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -11017,28 +11017,28 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
         <v>1.41</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N42" t="n">
         <v>2.9</v>
@@ -11050,197 +11050,197 @@
         <v>1.65</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R42" t="n">
         <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="X42" t="n">
         <v>13</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z42" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA42" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE42" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AF42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>27</v>
       </c>
-      <c r="AI42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>30</v>
-      </c>
       <c r="AK42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL42" t="n">
         <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO42" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP42" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT42" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW42" t="n">
         <v>4.7</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB42" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BC42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE42" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB42" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF42" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH42" t="n">
         <v>3.4</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK42" t="n">
         <v>1.01</v>
       </c>
       <c r="BL42" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BM42" t="n">
         <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP42" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ42" t="n">
         <v>1.01</v>
       </c>
       <c r="BR42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS42" t="n">
         <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BU42" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW42" t="n">
         <v>1.01</v>
       </c>
       <c r="BX42" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BY42" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA42" t="n">
         <v>1.01</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G43" t="n">
         <v>1.88</v>
@@ -11286,7 +11286,7 @@
         <v>3.65</v>
       </c>
       <c r="K43" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L43" t="n">
         <v>1.35</v>
@@ -11295,28 +11295,28 @@
         <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O43" t="n">
         <v>1.31</v>
       </c>
       <c r="P43" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R43" t="n">
         <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T43" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V43" t="n">
         <v>1.21</v>
@@ -11337,7 +11337,7 @@
         <v>160</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC43" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
         <v>100</v>
       </c>
       <c r="AP43" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43" t="n">
         <v>15</v>
@@ -11388,7 +11388,7 @@
         <v>5.1</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -11406,7 +11406,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY43" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ43" t="n">
         <v>17.5</v>
@@ -11430,13 +11430,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ43" t="n">
         <v>12</v>
@@ -11445,16 +11445,16 @@
         <v>1.01</v>
       </c>
       <c r="BL43" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM43" t="n">
         <v>1.01</v>
       </c>
       <c r="BN43" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO43" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP43" t="n">
         <v>14</v>
@@ -11481,20 +11481,20 @@
         <v>1.01</v>
       </c>
       <c r="BX43" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY43" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA43" t="n">
         <v>1.01</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O44" t="n">
         <v>1.44</v>
@@ -11558,7 +11558,7 @@
         <v>1.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
@@ -11606,7 +11606,7 @@
         <v>19</v>
       </c>
       <c r="AG44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH44" t="n">
         <v>24</v>
@@ -11642,7 +11642,7 @@
         <v>4.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT44" t="n">
         <v>7.8</v>
@@ -11672,13 +11672,13 @@
         <v>4.8</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD44" t="n">
         <v>4.7</v>
       </c>
       <c r="BE44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF44" t="n">
         <v>4.8</v>
@@ -11726,7 +11726,7 @@
         <v>7.4</v>
       </c>
       <c r="BU44" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV44" t="n">
         <v>36</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -863,7 +863,7 @@
         <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I2" t="n">
         <v>3.6</v>
@@ -899,7 +899,7 @@
         <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.14</v>
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -1025,16 +1025,16 @@
         <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.3</v>
@@ -1046,13 +1046,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1064,23 +1064,23 @@
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>28</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
         <v>5.9</v>
@@ -1126,10 +1126,10 @@
         <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1147,10 +1147,10 @@
         <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
@@ -1183,25 +1183,25 @@
         <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
         <v>17</v>
@@ -1276,10 +1276,10 @@
         <v>5.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
         <v>5.2</v>
@@ -1288,7 +1288,7 @@
         <v>75</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
@@ -1300,13 +1300,13 @@
         <v>10</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
         <v>19</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
         <v>9.4</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
         <v>36</v>
       </c>
       <c r="BY3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>3.15</v>
@@ -1380,7 +1380,7 @@
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1389,19 +1389,19 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>1.59</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
         <v>2.44</v>
@@ -1413,31 +1413,31 @@
         <v>2.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
       </c>
       <c r="Y4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z4" t="n">
         <v>19.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>21</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>29</v>
@@ -1446,10 +1446,10 @@
         <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
@@ -1464,22 +1464,22 @@
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
         <v>12.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
         <v>21</v>
@@ -1488,16 +1488,16 @@
         <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1521,7 +1521,7 @@
         <v>27</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG4" t="n">
         <v>10.5</v>
@@ -1533,19 +1533,19 @@
         <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>75</v>
       </c>
       <c r="BM4" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BO4" t="n">
         <v>5.1</v>
@@ -1554,13 +1554,13 @@
         <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>5.8</v>
@@ -1569,26 +1569,26 @@
         <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
         <v>24</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1649,13 +1649,13 @@
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
         <v>1.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
         <v>3.35</v>
@@ -1664,16 +1664,16 @@
         <v>1.72</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
         <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
         <v>12</v>
@@ -1688,7 +1688,7 @@
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
@@ -1736,7 +1736,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1763,16 +1763,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC5" t="n">
-        <v>8</v>
-      </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
         <v>7.8</v>
@@ -1790,31 +1790,31 @@
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
@@ -1823,26 +1823,26 @@
         <v>4.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
         <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK6" t="n">
         <v>1.04</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="BL6" t="n">
+        <v>200</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1.04</v>
       </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2298,13 +2298,13 @@
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BL7" t="n">
         <v>130</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN7" t="n">
         <v>8</v>
@@ -2316,13 +2316,13 @@
         <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT7" t="n">
         <v>5.6</v>
@@ -2334,10 +2334,10 @@
         <v>17.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
         <v>5.1</v>
@@ -2346,11 +2346,11 @@
         <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>950</v>
+      </c>
+      <c r="BK8" t="n">
         <v>1.04</v>
       </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>1.04</v>
       </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2635,94 +2635,94 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>870</v>
+        <v>1.36</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>1.98</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2740,7 +2740,7 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2794,16 +2794,16 @@
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI9" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BK9" t="n">
         <v>1.04</v>
@@ -2815,50 +2815,50 @@
         <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BO9" t="n">
         <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS9" t="n">
         <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU9" t="n">
         <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW9" t="n">
         <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA9" t="n">
         <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>1.25</v>
       </c>
       <c r="I10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J10" t="n">
         <v>7.4</v>
@@ -2928,13 +2928,13 @@
         <v>2.04</v>
       </c>
       <c r="S10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="T10" t="n">
         <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
         <v>4.6</v>
@@ -3048,7 +3048,7 @@
         <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BH10" t="n">
         <v>7</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -3143,118 +3143,118 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.09</v>
       </c>
-      <c r="G11" t="n">
-        <v>600</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I11" t="n">
-        <v>990</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K11" t="n">
-        <v>500</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.25</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR11" t="n">
         <v>1.01</v>
@@ -3266,7 +3266,7 @@
         <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
         <v>1.01</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
         <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM11" t="n">
         <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO11" t="n">
         <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS11" t="n">
         <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
         <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW11" t="n">
         <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11" t="n">
         <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H12" t="n">
         <v>8.800000000000001</v>
@@ -3409,13 +3409,13 @@
         <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K12" t="n">
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3439,7 +3439,7 @@
         <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
         <v>1.88</v>
@@ -3460,7 +3460,7 @@
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AB12" t="n">
         <v>9.199999999999999</v>
@@ -3475,7 +3475,7 @@
         <v>180</v>
       </c>
       <c r="AF12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -3502,7 +3502,7 @@
         <v>6.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP12" t="n">
         <v>14.5</v>
@@ -3532,10 +3532,10 @@
         <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA12" t="n">
         <v>42</v>
@@ -3547,7 +3547,7 @@
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
         <v>46</v>
@@ -3601,7 +3601,7 @@
         <v>3.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BW12" t="n">
         <v>4.7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="G14" t="n">
         <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="J14" t="n">
         <v>4.5</v>
@@ -3953,7 +3953,7 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="W14" t="n">
         <v>1.17</v>
@@ -4088,7 +4088,7 @@
         <v>13</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="BP14" t="n">
         <v>65</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J16" t="n">
         <v>1.1</v>
@@ -4434,25 +4434,25 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q16" t="n">
         <v>1.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.09</v>
       </c>
       <c r="G17" t="n">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H17" t="n">
         <v>1.09</v>
@@ -4688,22 +4688,22 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.34</v>
+        <v>1.74</v>
       </c>
       <c r="O17" t="n">
         <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.34</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>1.34</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
         <v>1.05</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
         <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J18" t="n">
         <v>3.7</v>
@@ -4942,10 +4942,10 @@
         <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.19</v>
@@ -4969,13 +4969,13 @@
         <v>2.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W18" t="n">
         <v>1.37</v>
       </c>
       <c r="X18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y18" t="n">
         <v>15.5</v>
@@ -4987,7 +4987,7 @@
         <v>29</v>
       </c>
       <c r="AB18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
         <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>60</v>
@@ -5053,7 +5053,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
@@ -5092,31 +5092,31 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BL18" t="n">
         <v>90</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP18" t="n">
         <v>30</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT18" t="n">
         <v>6.4</v>
@@ -5128,23 +5128,23 @@
         <v>16.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="BX18" t="n">
         <v>27</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
         <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
         <v>1.88</v>
@@ -5220,16 +5220,16 @@
         <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W19" t="n">
         <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
@@ -5244,7 +5244,7 @@
         <v>15.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5292,7 +5292,7 @@
         <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
@@ -5307,7 +5307,7 @@
         <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
@@ -5316,16 +5316,16 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
         <v>11</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
         <v>11.5</v>
@@ -5358,10 +5358,10 @@
         <v>8.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ19" t="n">
         <v>4.1</v>
@@ -5373,7 +5373,7 @@
         <v>4.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU19" t="n">
         <v>3.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
         <v>2.06</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U20" t="n">
         <v>2.4</v>
@@ -5510,7 +5510,7 @@
         <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -5522,7 +5522,7 @@
         <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -5537,16 +5537,16 @@
         <v>65</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT20" t="n">
         <v>13</v>
@@ -5558,7 +5558,7 @@
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -5570,7 +5570,7 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -5582,19 +5582,19 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20" t="n">
         <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BH20" t="n">
         <v>6</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -5701,7 +5701,7 @@
         <v>5.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5710,10 +5710,10 @@
         <v>5.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" t="n">
         <v>1.47</v>
@@ -5722,7 +5722,7 @@
         <v>1.64</v>
       </c>
       <c r="S21" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
         <v>1.57</v>
@@ -5731,7 +5731,7 @@
         <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
         <v>2.16</v>
@@ -5740,7 +5740,7 @@
         <v>32</v>
       </c>
       <c r="Y21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z21" t="n">
         <v>46</v>
@@ -5785,7 +5785,7 @@
         <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO21" t="n">
         <v>42</v>
@@ -5794,7 +5794,7 @@
         <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR21" t="n">
         <v>1.01</v>
@@ -5833,7 +5833,7 @@
         <v>12.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE21" t="n">
         <v>1.01</v>
@@ -5848,7 +5848,7 @@
         <v>5.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -5943,10 +5943,10 @@
         <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I22" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -5982,13 +5982,13 @@
         <v>1.46</v>
       </c>
       <c r="U22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V22" t="n">
         <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
         <v>950</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G23" t="n">
         <v>1.99</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
         <v>4.1</v>
@@ -6209,7 +6209,7 @@
         <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -6224,13 +6224,13 @@
         <v>2.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
         <v>1.45</v>
@@ -6248,10 +6248,10 @@
         <v>42</v>
       </c>
       <c r="Y23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Z23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
         <v>75</v>
@@ -6296,19 +6296,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>5.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6320,7 +6320,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
         <v>12</v>
@@ -6332,7 +6332,7 @@
         <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -6344,7 +6344,7 @@
         <v>17.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF23" t="n">
         <v>6.2</v>
@@ -6362,13 +6362,13 @@
         <v>9.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="BL23" t="n">
         <v>75</v>
       </c>
       <c r="BM23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BN23" t="n">
         <v>6.4</v>
@@ -6377,44 +6377,44 @@
         <v>4.4</v>
       </c>
       <c r="BP23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR23" t="n">
         <v>23</v>
       </c>
       <c r="BS23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ23" t="n">
         <v>14.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I24" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.28</v>
@@ -6469,34 +6469,34 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T24" t="n">
         <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
         <v>20</v>
@@ -6556,7 +6556,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR24" t="n">
         <v>12.5</v>
@@ -6607,7 +6607,7 @@
         <v>11</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI24" t="n">
         <v>3.05</v>
@@ -6616,22 +6616,22 @@
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>110</v>
       </c>
       <c r="BM24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ24" t="n">
         <v>4</v>
@@ -6640,35 +6640,35 @@
         <v>38</v>
       </c>
       <c r="BS24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT24" t="n">
         <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA24" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.3</v>
@@ -6977,28 +6977,28 @@
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R26" t="n">
         <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U26" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V26" t="n">
         <v>1.71</v>
@@ -7088,7 +7088,7 @@
         <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
@@ -7118,19 +7118,19 @@
         <v>5</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ26" t="n">
         <v>10.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BL26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN26" t="n">
         <v>8</v>
@@ -7142,7 +7142,7 @@
         <v>26</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR26" t="n">
         <v>34</v>
@@ -7160,7 +7160,7 @@
         <v>18.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BX26" t="n">
         <v>29</v>
@@ -7169,14 +7169,14 @@
         <v>4</v>
       </c>
       <c r="BZ26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA26" t="n">
         <v>3.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>1.84</v>
       </c>
       <c r="I27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="J27" t="n">
         <v>4.4</v>
@@ -7225,40 +7225,40 @@
         <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
         <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R27" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="S27" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
         <v>1.48</v>
       </c>
       <c r="U27" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
         <v>40</v>
@@ -7369,16 +7369,16 @@
         <v>5.9</v>
       </c>
       <c r="BH27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BL27" t="n">
         <v>75</v>
@@ -7396,41 +7396,41 @@
         <v>32</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR27" t="n">
         <v>34</v>
       </c>
       <c r="BS27" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BT27" t="n">
         <v>6.4</v>
       </c>
       <c r="BU27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV27" t="n">
         <v>14</v>
       </c>
       <c r="BW27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BX27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY27" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BZ27" t="n">
         <v>14</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -7461,220 +7461,220 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>950</v>
+      </c>
+      <c r="BK28" t="n">
         <v>1.04</v>
       </c>
-      <c r="G28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
         <v>1.04</v>
       </c>
-      <c r="I28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="G29" t="n">
         <v>1.76</v>
       </c>
       <c r="H29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
         <v>7.2</v>
@@ -7730,31 +7730,31 @@
         <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O29" t="n">
         <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T29" t="n">
         <v>2.02</v>
@@ -7823,64 +7823,64 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
         <v>12</v>
       </c>
       <c r="BG29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ29" t="n">
         <v>13.5</v>
@@ -7892,25 +7892,25 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN29" t="n">
         <v>4.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP29" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR29" t="n">
         <v>40</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT29" t="n">
         <v>11</v>
@@ -7919,26 +7919,26 @@
         <v>3.85</v>
       </c>
       <c r="BV29" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BW29" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX29" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ29" t="n">
         <v>36</v>
       </c>
       <c r="CA29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I30" t="n">
         <v>1.72</v>
@@ -7987,7 +7987,7 @@
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -7999,10 +7999,10 @@
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R30" t="n">
         <v>1.32</v>
@@ -8011,7 +8011,7 @@
         <v>3.6</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
         <v>1.76</v>
@@ -8026,7 +8026,7 @@
         <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z30" t="n">
         <v>9.800000000000001</v>
@@ -8041,7 +8041,7 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>970</v>
@@ -8101,7 +8101,7 @@
         <v>16.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY30" t="n">
         <v>18.5</v>
@@ -8110,22 +8110,22 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG30" t="n">
         <v>9.6</v>
@@ -8134,7 +8134,7 @@
         <v>3.7</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ30" t="n">
         <v>12.5</v>
@@ -8152,7 +8152,7 @@
         <v>11</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP30" t="n">
         <v>65</v>
@@ -8164,7 +8164,7 @@
         <v>75</v>
       </c>
       <c r="BS30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT30" t="n">
         <v>4.7</v>
@@ -8185,14 +8185,14 @@
         <v>4.9</v>
       </c>
       <c r="BZ30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA30" t="n">
         <v>4.8</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>1.35</v>
       </c>
       <c r="H31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I31" t="n">
         <v>20</v>
@@ -8247,7 +8247,7 @@
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>1.36</v>
@@ -8259,16 +8259,16 @@
         <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
         <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
         <v>1.05</v>
@@ -8283,7 +8283,7 @@
         <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -8322,7 +8322,7 @@
         <v>75</v>
       </c>
       <c r="AM31" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="AN31" t="n">
         <v>7.8</v>
@@ -8394,13 +8394,13 @@
         <v>20</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL31" t="n">
         <v>440</v>
       </c>
       <c r="BM31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN31" t="n">
         <v>3.85</v>
@@ -8415,7 +8415,7 @@
         <v>5.8</v>
       </c>
       <c r="BR31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS31" t="n">
         <v>4.5</v>
@@ -8424,13 +8424,13 @@
         <v>22</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV31" t="n">
         <v>260</v>
       </c>
       <c r="BW31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BX31" t="n">
         <v>230</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -8483,16 +8483,16 @@
         <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J32" t="n">
         <v>4.6</v>
       </c>
       <c r="K32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.24</v>
@@ -8513,13 +8513,13 @@
         <v>1.49</v>
       </c>
       <c r="R32" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S32" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U32" t="n">
         <v>1.95</v>
@@ -8546,7 +8546,7 @@
         <v>950</v>
       </c>
       <c r="AC32" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD32" t="n">
         <v>11</v>
@@ -8570,7 +8570,7 @@
         <v>220</v>
       </c>
       <c r="AK32" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL32" t="n">
         <v>75</v>
@@ -8609,7 +8609,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY32" t="n">
         <v>19</v>
@@ -8618,28 +8618,28 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG32" t="n">
         <v>5.1</v>
       </c>
       <c r="BH32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI32" t="n">
         <v>3.4</v>
@@ -8648,31 +8648,31 @@
         <v>12</v>
       </c>
       <c r="BK32" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BL32" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BN32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP32" t="n">
         <v>65</v>
       </c>
       <c r="BQ32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR32" t="n">
         <v>60</v>
       </c>
       <c r="BS32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT32" t="n">
         <v>5.1</v>
@@ -8684,23 +8684,23 @@
         <v>11</v>
       </c>
       <c r="BW32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BX32" t="n">
         <v>25</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BZ32" t="n">
         <v>15.5</v>
       </c>
       <c r="CA32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G33" t="n">
         <v>4.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I33" t="n">
         <v>1.97</v>
@@ -8761,7 +8761,7 @@
         <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q33" t="n">
         <v>1.51</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>6.8</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I34" t="n">
         <v>1.56</v>
@@ -9000,7 +9000,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L34" t="n">
         <v>1.2</v>
@@ -9024,7 +9024,7 @@
         <v>1.79</v>
       </c>
       <c r="S34" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T34" t="n">
         <v>1.61</v>
@@ -9156,31 +9156,31 @@
         <v>11.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BL34" t="n">
         <v>95</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BN34" t="n">
         <v>12.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BP34" t="n">
         <v>55</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BR34" t="n">
         <v>48</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BT34" t="n">
         <v>5.5</v>
@@ -9189,7 +9189,7 @@
         <v>3.6</v>
       </c>
       <c r="BV34" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BW34" t="n">
         <v>3.2</v>
@@ -9198,17 +9198,17 @@
         <v>22</v>
       </c>
       <c r="BY34" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BZ34" t="n">
         <v>13</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -9239,230 +9239,230 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G35" t="n">
-        <v>990</v>
+        <v>1.49</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>990</v>
+        <v>14</v>
       </c>
       <c r="J35" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="K35" t="n">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O35" t="n">
         <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL35" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>1.86</v>
       </c>
       <c r="H36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I36" t="n">
         <v>4.7</v>
@@ -9532,13 +9532,13 @@
         <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
         <v>1.72</v>
       </c>
       <c r="U36" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V36" t="n">
         <v>1.27</v>
@@ -9547,7 +9547,7 @@
         <v>2.16</v>
       </c>
       <c r="X36" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y36" t="n">
         <v>21</v>
@@ -9562,22 +9562,22 @@
         <v>10.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE36" t="n">
         <v>55</v>
       </c>
       <c r="AF36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG36" t="n">
         <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI36" t="n">
         <v>55</v>
@@ -9598,19 +9598,19 @@
         <v>10.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP36" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR36" t="n">
         <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
@@ -9622,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="AW36" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX36" t="n">
         <v>11.5</v>
@@ -9646,13 +9646,13 @@
         <v>23</v>
       </c>
       <c r="BE36" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF36" t="n">
         <v>9</v>
       </c>
       <c r="BG36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH36" t="n">
         <v>4.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -9753,13 +9753,13 @@
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
         <v>5.7</v>
       </c>
       <c r="J37" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
         <v>3.95</v>
@@ -9771,7 +9771,7 @@
         <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O37" t="n">
         <v>1.36</v>
@@ -9780,13 +9780,13 @@
         <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R37" t="n">
         <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T37" t="n">
         <v>1.75</v>
@@ -9795,7 +9795,7 @@
         <v>1.78</v>
       </c>
       <c r="V37" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W37" t="n">
         <v>2</v>
@@ -9912,7 +9912,7 @@
         <v>3.65</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="BJ37" t="n">
         <v>12.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -10004,37 +10004,37 @@
         <v>1.69</v>
       </c>
       <c r="G38" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="H38" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O38" t="n">
         <v>1.45</v>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
         <v>1.23</v>
@@ -10043,19 +10043,19 @@
         <v>4.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="U38" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V38" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W38" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="X38" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y38" t="n">
         <v>19</v>
@@ -10076,7 +10076,7 @@
         <v>30</v>
       </c>
       <c r="AE38" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF38" t="n">
         <v>10.5</v>
@@ -10097,7 +10097,7 @@
         <v>26</v>
       </c>
       <c r="AL38" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM38" t="n">
         <v>240</v>
@@ -10106,125 +10106,125 @@
         <v>18.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
         <v>5.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BD38" t="n">
         <v>5</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ38" t="n">
         <v>14</v>
       </c>
       <c r="BK38" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BL38" t="n">
         <v>250</v>
       </c>
       <c r="BM38" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BN38" t="n">
         <v>4.6</v>
       </c>
       <c r="BO38" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="BP38" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BR38" t="n">
         <v>40</v>
       </c>
       <c r="BS38" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BT38" t="n">
         <v>11</v>
       </c>
       <c r="BU38" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BV38" t="n">
         <v>80</v>
       </c>
       <c r="BW38" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX38" t="n">
         <v>95</v>
       </c>
       <c r="BY38" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BZ38" t="n">
         <v>36</v>
       </c>
       <c r="CA38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -10267,43 +10267,43 @@
         <v>3.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K39" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L39" t="n">
         <v>1.46</v>
       </c>
       <c r="M39" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P39" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R39" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S39" t="n">
         <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U39" t="n">
         <v>1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W39" t="n">
         <v>1.54</v>
@@ -10342,7 +10342,7 @@
         <v>950</v>
       </c>
       <c r="AI39" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
         <v>50</v>
@@ -10360,22 +10360,22 @@
         <v>42</v>
       </c>
       <c r="AO39" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT39" t="n">
         <v>3.45</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.5</v>
       </c>
       <c r="AU39" t="n">
         <v>3.4</v>
@@ -10384,101 +10384,101 @@
         <v>4.1</v>
       </c>
       <c r="AW39" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX39" t="n">
         <v>4.1</v>
       </c>
       <c r="AY39" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ39" t="n">
         <v>970</v>
       </c>
       <c r="BK39" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BN39" t="n">
         <v>6</v>
       </c>
       <c r="BO39" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="BP39" t="n">
         <v>25</v>
       </c>
       <c r="BQ39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR39" t="n">
         <v>46</v>
       </c>
       <c r="BS39" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BT39" t="n">
         <v>7.2</v>
       </c>
       <c r="BU39" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV39" t="n">
         <v>34</v>
       </c>
       <c r="BW39" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BX39" t="n">
         <v>55</v>
       </c>
       <c r="BY39" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BZ39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CA39" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -10763,16 +10763,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G41" t="n">
         <v>6</v>
       </c>
-      <c r="G41" t="n">
-        <v>6.2</v>
-      </c>
       <c r="H41" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="J41" t="n">
         <v>4.1</v>
@@ -10787,49 +10787,49 @@
         <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P41" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R41" t="n">
         <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T41" t="n">
         <v>2.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V41" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="W41" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y41" t="n">
         <v>7.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC41" t="n">
         <v>9.199999999999999</v>
@@ -10841,10 +10841,10 @@
         <v>19</v>
       </c>
       <c r="AF41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH41" t="n">
         <v>24</v>
@@ -10853,7 +10853,7 @@
         <v>42</v>
       </c>
       <c r="AJ41" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK41" t="n">
         <v>85</v>
@@ -10865,7 +10865,7 @@
         <v>140</v>
       </c>
       <c r="AN41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO41" t="n">
         <v>11</v>
@@ -10874,13 +10874,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR41" t="n">
         <v>8.6</v>
       </c>
       <c r="AS41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT41" t="n">
         <v>16.5</v>
@@ -10895,7 +10895,7 @@
         <v>18.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AY41" t="n">
         <v>21</v>
@@ -10904,16 +10904,16 @@
         <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB41" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="BC41" t="n">
         <v>80</v>
       </c>
       <c r="BD41" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BE41" t="n">
         <v>110</v>
@@ -10922,10 +10922,10 @@
         <v>110</v>
       </c>
       <c r="BG41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI41" t="n">
         <v>3.05</v>
@@ -10934,7 +10934,7 @@
         <v>11</v>
       </c>
       <c r="BK41" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL41" t="n">
         <v>190</v>
@@ -10946,37 +10946,37 @@
         <v>9.4</v>
       </c>
       <c r="BO41" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP41" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BQ41" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR41" t="n">
         <v>65</v>
       </c>
       <c r="BS41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BT41" t="n">
         <v>4.1</v>
       </c>
       <c r="BU41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV41" t="n">
         <v>11.5</v>
       </c>
       <c r="BW41" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX41" t="n">
         <v>29</v>
       </c>
       <c r="BY41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -11017,28 +11017,28 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G42" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
         <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L42" t="n">
         <v>1.43</v>
       </c>
       <c r="M42" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
         <v>3</v>
@@ -11065,16 +11065,16 @@
         <v>1.76</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>970</v>
       </c>
       <c r="Y42" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z42" t="n">
         <v>42</v>
@@ -11110,7 +11110,7 @@
         <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL42" t="n">
         <v>46</v>
@@ -11125,58 +11125,58 @@
         <v>130</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ42" t="n">
         <v>6.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="AS42" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AT42" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV42" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD42" t="n">
         <v>2.62</v>
       </c>
-      <c r="AX42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>2.86</v>
-      </c>
       <c r="BE42" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="BH42" t="n">
         <v>3.35</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -11277,10 +11277,10 @@
         <v>1.4</v>
       </c>
       <c r="H43" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="I43" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J43" t="n">
         <v>4.9</v>
@@ -11301,7 +11301,7 @@
         <v>1.3</v>
       </c>
       <c r="P43" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
         <v>1.87</v>
@@ -11313,13 +11313,13 @@
         <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U43" t="n">
         <v>1.56</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W43" t="n">
         <v>3.5</v>
@@ -11379,7 +11379,7 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ43" t="n">
         <v>5.5</v>
@@ -11391,13 +11391,13 @@
         <v>2.28</v>
       </c>
       <c r="AT43" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU43" t="n">
         <v>4.5</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW43" t="n">
         <v>3.15</v>
@@ -11409,10 +11409,10 @@
         <v>4.3</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA43" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BB43" t="n">
         <v>4.2</v>
@@ -11430,7 +11430,7 @@
         <v>5.2</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BH43" t="n">
         <v>4.1</v>
@@ -11442,13 +11442,13 @@
         <v>16</v>
       </c>
       <c r="BK43" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL43" t="n">
         <v>260</v>
       </c>
       <c r="BM43" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN43" t="n">
         <v>3.95</v>
@@ -11457,7 +11457,7 @@
         <v>2.92</v>
       </c>
       <c r="BP43" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ43" t="n">
         <v>6</v>
@@ -11466,25 +11466,25 @@
         <v>34</v>
       </c>
       <c r="BS43" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT43" t="n">
         <v>17.5</v>
       </c>
       <c r="BU43" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV43" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BW43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX43" t="n">
         <v>140</v>
       </c>
       <c r="BY43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ43" t="n">
         <v>17</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -11534,16 +11534,16 @@
         <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J44" t="n">
         <v>4.4</v>
       </c>
       <c r="K44" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L44" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -11555,10 +11555,10 @@
         <v>1.41</v>
       </c>
       <c r="P44" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
@@ -11567,7 +11567,7 @@
         <v>4.3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U44" t="n">
         <v>1.58</v>
@@ -11735,7 +11735,7 @@
         <v>4.9</v>
       </c>
       <c r="BX44" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BY44" t="n">
         <v>4.9</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -11779,34 +11779,34 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="G45" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>4.8</v>
       </c>
       <c r="I45" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="n">
         <v>3.4</v>
       </c>
       <c r="K45" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L45" t="n">
         <v>1.41</v>
       </c>
       <c r="M45" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N45" t="n">
         <v>2.9</v>
       </c>
       <c r="O45" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P45" t="n">
         <v>1.65</v>
@@ -11821,13 +11821,13 @@
         <v>4.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U45" t="n">
         <v>1.68</v>
       </c>
       <c r="V45" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W45" t="n">
         <v>2</v>
@@ -11839,10 +11839,10 @@
         <v>17</v>
       </c>
       <c r="Z45" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA45" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB45" t="n">
         <v>8</v>
@@ -11854,7 +11854,7 @@
         <v>24</v>
       </c>
       <c r="AE45" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF45" t="n">
         <v>12</v>
@@ -11896,7 +11896,7 @@
         <v>30</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -11905,10 +11905,10 @@
         <v>7.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX45" t="n">
         <v>9.199999999999999</v>
@@ -11917,10 +11917,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB45" t="n">
         <v>19</v>
@@ -11929,16 +11929,16 @@
         <v>20</v>
       </c>
       <c r="BD45" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF45" t="n">
         <v>16</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH45" t="n">
         <v>3.4</v>
@@ -11950,19 +11950,19 @@
         <v>13.5</v>
       </c>
       <c r="BK45" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL45" t="n">
         <v>220</v>
       </c>
       <c r="BM45" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN45" t="n">
         <v>5.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP45" t="n">
         <v>18</v>
@@ -11977,7 +11977,7 @@
         <v>4.4</v>
       </c>
       <c r="BT45" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU45" t="n">
         <v>6</v>
@@ -11992,7 +11992,7 @@
         <v>80</v>
       </c>
       <c r="BY45" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ45" t="n">
         <v>42</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
         <v>1.97</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W46" t="n">
         <v>2.14</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
         <v>19</v>
       </c>
       <c r="AG47" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH47" t="n">
         <v>24</v>
@@ -12401,10 +12401,10 @@
         <v>9.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT47" t="n">
         <v>7.8</v>
@@ -12416,7 +12416,7 @@
         <v>12.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX47" t="n">
         <v>13.5</v>
@@ -12428,25 +12428,25 @@
         <v>17</v>
       </c>
       <c r="BA47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC47" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB47" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD47" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG47" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH47" t="n">
         <v>3.45</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,76 +857,76 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
         <v>3.35</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
@@ -953,13 +953,13 @@
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
         <v>38</v>
@@ -974,13 +974,13 @@
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>13.5</v>
@@ -992,34 +992,34 @@
         <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
         <v>7.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI2" t="n">
         <v>3.05</v>
@@ -1028,13 +1028,13 @@
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.3</v>
@@ -1046,41 +1046,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G3" t="n">
         <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
         <v>5.9</v>
@@ -1150,13 +1150,13 @@
         <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1195,7 +1195,7 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1216,7 +1216,7 @@
         <v>5.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -1237,7 +1237,7 @@
         <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
         <v>29</v>
@@ -1261,7 +1261,7 @@
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE3" t="n">
         <v>32</v>
@@ -1273,7 +1273,7 @@
         <v>26</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BI3" t="n">
         <v>4</v>
@@ -1282,59 +1282,59 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BM3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>10</v>
-      </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BR3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW3" t="n">
         <v>8</v>
       </c>
-      <c r="BV3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I4" t="n">
         <v>2.44</v>
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1395,13 +1395,13 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>1.59</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
         <v>2.44</v>
@@ -1422,16 +1422,16 @@
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
         <v>9.4</v>
@@ -1449,7 +1449,7 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
@@ -1464,10 +1464,10 @@
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>12.5</v>
@@ -1479,7 +1479,7 @@
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1524,71 +1524,71 @@
         <v>16</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI4" t="n">
         <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BL4" t="n">
         <v>75</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
         <v>5.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
         <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BX4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BZ4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -1634,13 +1634,13 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>3.9</v>
@@ -1661,10 +1661,10 @@
         <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
         <v>1.55</v>
@@ -1685,7 +1685,7 @@
         <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
@@ -1736,7 +1736,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1760,22 +1760,22 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
         <v>19</v>
@@ -1790,13 +1790,13 @@
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BN5" t="n">
         <v>7</v>
@@ -1805,16 +1805,16 @@
         <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
@@ -1826,23 +1826,23 @@
         <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BX5" t="n">
         <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -1981,58 +1981,58 @@
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.6</v>
+        <v>2.92</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>3.65</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>3.65</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="BH6" t="n">
         <v>3.7</v>
@@ -2044,49 +2044,49 @@
         <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL6" t="n">
         <v>200</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN6" t="n">
         <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP6" t="n">
         <v>65</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR6" t="n">
         <v>75</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT6" t="n">
         <v>5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BV6" t="n">
         <v>15.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BX6" t="n">
         <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
@@ -2166,7 +2166,7 @@
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
         <v>1.76</v>
@@ -2175,13 +2175,13 @@
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W7" t="n">
         <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
         <v>10.5</v>
@@ -2193,13 +2193,13 @@
         <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
@@ -2223,7 +2223,7 @@
         <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -2232,7 +2232,7 @@
         <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
         <v>13</v>
@@ -2259,31 +2259,31 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG7" t="n">
         <v>13</v>
@@ -2292,65 +2292,65 @@
         <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BL7" t="n">
         <v>130</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
         <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BT7" t="n">
         <v>5.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
         <v>17.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX7" t="n">
         <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BZ7" t="n">
         <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.47</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
@@ -2405,55 +2405,55 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
         <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>170</v>
@@ -2462,16 +2462,16 @@
         <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
         <v>21</v>
@@ -2489,10 +2489,10 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
         <v>1.01</v>
@@ -2501,34 +2501,34 @@
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
         <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
         <v>1.01</v>
@@ -2537,7 +2537,7 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
@@ -2549,52 +2549,52 @@
         <v>2.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN8" t="n">
         <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BP8" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BR8" t="n">
         <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV8" t="n">
         <v>90</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX8" t="n">
         <v>95</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="I9" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
         <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
         <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA9" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>12</v>
       </c>
       <c r="AB9" t="n">
         <v>950</v>
@@ -2707,13 +2707,13 @@
         <v>950</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AG9" t="n">
         <v>950</v>
@@ -2722,7 +2722,7 @@
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2731,40 +2731,40 @@
         <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
         <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
         <v>1.01</v>
@@ -2794,71 +2794,71 @@
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>140</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BW9" t="n">
         <v>5.2</v>
       </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>950</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>950</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>110</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H10" t="n">
         <v>1.25</v>
@@ -2901,13 +2901,13 @@
         <v>1.27</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
@@ -2919,28 +2919,28 @@
         <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="T10" t="n">
         <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>60</v>
@@ -2994,28 +2994,28 @@
         <v>150</v>
       </c>
       <c r="AO10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AP10" t="n">
         <v>27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU10" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
         <v>11.5</v>
@@ -3024,10 +3024,10 @@
         <v>42</v>
       </c>
       <c r="AY10" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
         <v>19.5</v>
@@ -3048,13 +3048,13 @@
         <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH10" t="n">
         <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>13.5</v>
@@ -3066,13 +3066,13 @@
         <v>120</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP10" t="n">
         <v>95</v>
@@ -3084,13 +3084,13 @@
         <v>75</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT10" t="n">
         <v>5.1</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV10" t="n">
         <v>8.199999999999999</v>
@@ -3099,20 +3099,20 @@
         <v>5.1</v>
       </c>
       <c r="BX10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY10" t="n">
         <v>3.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -3143,118 +3143,118 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
         <v>2.94</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
         <v>3.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
         <v>1.01</v>
@@ -3266,7 +3266,7 @@
         <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
         <v>1.01</v>
@@ -3314,59 +3314,59 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL11" t="n">
         <v>170</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN11" t="n">
         <v>6.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
         <v>26</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
         <v>44</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT11" t="n">
         <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV11" t="n">
         <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ11" t="n">
         <v>42</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G12" t="n">
         <v>1.43</v>
@@ -3406,7 +3406,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>5.1</v>
@@ -3415,25 +3415,25 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
         <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
         <v>2.88</v>
@@ -3442,16 +3442,16 @@
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>950</v>
@@ -3460,25 +3460,25 @@
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
         <v>46</v>
       </c>
       <c r="AE12" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>34</v>
@@ -3496,16 +3496,16 @@
         <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN12" t="n">
         <v>6.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ12" t="n">
         <v>19</v>
@@ -3523,25 +3523,25 @@
         <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
         <v>42</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
         <v>42</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
@@ -3550,10 +3550,10 @@
         <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG12" t="n">
         <v>48</v>
@@ -3562,65 +3562,65 @@
         <v>4.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
         <v>14</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BL12" t="n">
         <v>180</v>
       </c>
       <c r="BM12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO12" t="n">
         <v>3.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BR12" t="n">
         <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BT12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BV12" t="n">
         <v>95</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BX12" t="n">
         <v>90</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
         <v>5.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
         <v>2.72</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
         <v>5.7</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3935,13 +3935,13 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
         <v>1.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
         <v>2.4</v>
@@ -3953,7 +3953,7 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W14" t="n">
         <v>1.17</v>
@@ -4058,67 +4058,67 @@
         <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG14" t="n">
         <v>4.1</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL14" t="n">
         <v>130</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BN14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BQ14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY14" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>3.85</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         <v>5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="G16" t="n">
-        <v>990</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="I16" t="n">
-        <v>870</v>
+        <v>2.98</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>2.88</v>
       </c>
       <c r="K16" t="n">
-        <v>500</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>2.42</v>
       </c>
       <c r="O16" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -4667,230 +4667,230 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>600</v>
+        <v>2.68</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="I17" t="n">
-        <v>990</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -4927,22 +4927,22 @@
         <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
         <v>5.2</v>
@@ -4969,7 +4969,7 @@
         <v>2.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W18" t="n">
         <v>1.37</v>
@@ -5035,7 +5035,7 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
         <v>18.5</v>
@@ -5053,7 +5053,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -5175,40 +5175,40 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G19" t="n">
         <v>3.8</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="H19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I19" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.65</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
         <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
@@ -5217,124 +5217,124 @@
         <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="W19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BB19" t="n">
         <v>11</v>
       </c>
       <c r="BC19" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BE19" t="n">
         <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH19" t="n">
         <v>4.2</v>
@@ -5346,7 +5346,7 @@
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BL19" t="n">
         <v>140</v>
@@ -5358,25 +5358,25 @@
         <v>8.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="BP19" t="n">
         <v>38</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR19" t="n">
         <v>48</v>
       </c>
       <c r="BS19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT19" t="n">
         <v>5.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV19" t="n">
         <v>18</v>
@@ -5391,14 +5391,14 @@
         <v>4.1</v>
       </c>
       <c r="BZ19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA19" t="n">
         <v>4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>7.2</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J20" t="n">
         <v>5.5</v>
@@ -5471,13 +5471,13 @@
         <v>2.06</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
         <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
         <v>3.1</v>
@@ -5594,7 +5594,7 @@
         <v>6</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H21" t="n">
         <v>4.4</v>
@@ -5695,13 +5695,13 @@
         <v>5.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5713,7 +5713,7 @@
         <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q21" t="n">
         <v>1.47</v>
@@ -5734,7 +5734,7 @@
         <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X21" t="n">
         <v>32</v>
@@ -5791,7 +5791,7 @@
         <v>42</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>1.05</v>
       </c>
       <c r="AQ21" t="n">
         <v>17.5</v>
@@ -5833,7 +5833,7 @@
         <v>12.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         <v>2.32</v>
       </c>
       <c r="I22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -5973,7 +5973,7 @@
         <v>1.41</v>
       </c>
       <c r="R22" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
         <v>2.02</v>
@@ -5982,7 +5982,7 @@
         <v>1.46</v>
       </c>
       <c r="U22" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="V22" t="n">
         <v>1.65</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="G23" t="n">
         <v>1.99</v>
@@ -6209,7 +6209,7 @@
         <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -6224,10 +6224,10 @@
         <v>2.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S23" t="n">
         <v>2.08</v>
@@ -6362,13 +6362,13 @@
         <v>9.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL23" t="n">
         <v>75</v>
       </c>
       <c r="BM23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BN23" t="n">
         <v>6.4</v>
@@ -6377,44 +6377,44 @@
         <v>4.4</v>
       </c>
       <c r="BP23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR23" t="n">
         <v>23</v>
       </c>
       <c r="BS23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW23" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW23" t="n">
+      <c r="BX23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY23" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>4.7</v>
       </c>
       <c r="BZ23" t="n">
         <v>14.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H24" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="I24" t="n">
         <v>2.48</v>
@@ -6460,7 +6460,7 @@
         <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>1.28</v>
@@ -6487,16 +6487,16 @@
         <v>2.76</v>
       </c>
       <c r="T24" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
         <v>2.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X24" t="n">
         <v>20</v>
@@ -6508,7 +6508,7 @@
         <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
         <v>16</v>
@@ -6520,7 +6520,7 @@
         <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF24" t="n">
         <v>25</v>
@@ -6535,10 +6535,10 @@
         <v>34</v>
       </c>
       <c r="AJ24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -6556,13 +6556,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.05</v>
+        <v>22</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -6574,10 +6574,10 @@
         <v>8.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -6589,19 +6589,19 @@
         <v>1.05</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.05</v>
       </c>
-      <c r="BD24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BG24" t="n">
         <v>11</v>
@@ -6616,7 +6616,7 @@
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="BL24" t="n">
         <v>110</v>
@@ -6625,16 +6625,16 @@
         <v>4.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BR24" t="n">
         <v>38</v>
@@ -6643,16 +6643,16 @@
         <v>4.1</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BV24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
@@ -6661,14 +6661,14 @@
         <v>4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA24" t="n">
         <v>3.85</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.2</v>
@@ -6741,16 +6741,16 @@
         <v>2.46</v>
       </c>
       <c r="T25" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X25" t="n">
         <v>950</v>
@@ -6813,10 +6813,10 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
@@ -6828,7 +6828,7 @@
         <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -6840,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB25" t="n">
         <v>12.5</v>
@@ -6849,16 +6849,16 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
         <v>5.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH25" t="n">
         <v>4.8</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
         <v>3.3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I26" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.3</v>
@@ -6983,13 +6983,13 @@
         <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
         <v>1.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
         <v>2.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
         <v>4.2</v>
@@ -7216,10 +7216,10 @@
         <v>1.84</v>
       </c>
       <c r="I27" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
@@ -7243,10 +7243,10 @@
         <v>1.41</v>
       </c>
       <c r="R27" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
         <v>1.48</v>
@@ -7255,7 +7255,7 @@
         <v>2.76</v>
       </c>
       <c r="V27" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
         <v>2.92</v>
       </c>
       <c r="K28" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -7515,10 +7515,10 @@
         <v>1.79</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
         <v>36</v>
@@ -7527,25 +7527,25 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE28" t="n">
         <v>75</v>
       </c>
       <c r="AF28" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -7569,58 +7569,58 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT28" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH28" t="n">
         <v>3.35</v>
@@ -7629,52 +7629,52 @@
         <v>2.5</v>
       </c>
       <c r="BJ28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BN28" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BP28" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR28" t="n">
         <v>40</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV28" t="n">
         <v>46</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BX28" t="n">
         <v>65</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -7733,13 +7733,13 @@
         <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
         <v>1.44</v>
@@ -7784,7 +7784,7 @@
         <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
@@ -7802,7 +7802,7 @@
         <v>950</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ29" t="n">
         <v>21</v>
@@ -7823,13 +7823,13 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AQ29" t="n">
         <v>5.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS29" t="n">
         <v>6.4</v>
@@ -7841,10 +7841,10 @@
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
@@ -7853,19 +7853,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC29" t="n">
         <v>5.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE29" t="n">
         <v>6.4</v>
@@ -7877,68 +7877,68 @@
         <v>6.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP29" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BQ29" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BR29" t="n">
         <v>40</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU29" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW29" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX29" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ29" t="n">
         <v>36</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
         <v>1.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1.32</v>
@@ -8011,10 +8011,10 @@
         <v>3.6</v>
       </c>
       <c r="T30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.86</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.76</v>
       </c>
       <c r="V30" t="n">
         <v>2.38</v>
@@ -8038,7 +8038,7 @@
         <v>19.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
         <v>10</v>
@@ -8101,7 +8101,7 @@
         <v>16.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY30" t="n">
         <v>18.5</v>
@@ -8110,25 +8110,25 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG30" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="n">
         <v>3.7</v>
@@ -8170,7 +8170,7 @@
         <v>4.7</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BV30" t="n">
         <v>13.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -8241,10 +8241,10 @@
         <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
         <v>3.25</v>
@@ -8253,28 +8253,28 @@
         <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
         <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X31" t="n">
         <v>14.5</v>
@@ -8283,13 +8283,13 @@
         <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC31" t="n">
         <v>13.5</v>
@@ -8298,7 +8298,7 @@
         <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AF31" t="n">
         <v>6.6</v>
@@ -8310,19 +8310,19 @@
         <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>440</v>
+        <v>390</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
         <v>75</v>
       </c>
       <c r="AM31" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>7.8</v>
@@ -8334,13 +8334,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT31" t="n">
         <v>5.3</v>
@@ -8349,104 +8349,104 @@
         <v>10.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AY31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA31" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB31" t="n">
         <v>4.7</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF31" t="n">
         <v>6.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>420</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO31" t="n">
         <v>2.68</v>
       </c>
-      <c r="BJ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>440</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BP31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR31" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BS31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BU31" t="n">
         <v>4.1</v>
       </c>
       <c r="BV31" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="BW31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX31" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="BY31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G32" t="n">
         <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I32" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J32" t="n">
         <v>4.6</v>
       </c>
       <c r="K32" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.24</v>
@@ -8525,7 +8525,7 @@
         <v>1.95</v>
       </c>
       <c r="V32" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="W32" t="n">
         <v>1.14</v>
@@ -8663,7 +8663,7 @@
         <v>3.45</v>
       </c>
       <c r="BP32" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BQ32" t="n">
         <v>4.4</v>
@@ -8684,7 +8684,7 @@
         <v>11</v>
       </c>
       <c r="BW32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BX32" t="n">
         <v>25</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G33" t="n">
         <v>4.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="I33" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8761,16 +8761,16 @@
         <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1.51</v>
       </c>
       <c r="R33" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T33" t="n">
         <v>1.53</v>
@@ -8779,10 +8779,10 @@
         <v>2.76</v>
       </c>
       <c r="V33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
         <v>50</v>
@@ -8797,7 +8797,7 @@
         <v>24</v>
       </c>
       <c r="AB33" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AC33" t="n">
         <v>10.5</v>
@@ -8806,25 +8806,25 @@
         <v>11.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AF33" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG33" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AH33" t="n">
         <v>15.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="n">
         <v>70</v>
       </c>
       <c r="AK33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL33" t="n">
         <v>40</v>
@@ -8833,10 +8833,10 @@
         <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AP33" t="n">
         <v>19.5</v>
@@ -8845,7 +8845,7 @@
         <v>13.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS33" t="n">
         <v>16</v>
@@ -8857,7 +8857,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
         <v>15</v>
@@ -8887,7 +8887,7 @@
         <v>26</v>
       </c>
       <c r="BF33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG33" t="n">
         <v>7</v>
@@ -8902,16 +8902,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL33" t="n">
         <v>80</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO33" t="n">
         <v>6</v>
@@ -8920,7 +8920,7 @@
         <v>30</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR33" t="n">
         <v>34</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -8988,22 +8988,22 @@
         <v>5.8</v>
       </c>
       <c r="G34" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H34" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I34" t="n">
         <v>1.56</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
@@ -9015,7 +9015,7 @@
         <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q34" t="n">
         <v>1.43</v>
@@ -9027,16 +9027,16 @@
         <v>2.08</v>
       </c>
       <c r="T34" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U34" t="n">
         <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
         <v>42</v>
@@ -9168,10 +9168,10 @@
         <v>12.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BQ34" t="n">
         <v>4.2</v>
@@ -9180,7 +9180,7 @@
         <v>48</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT34" t="n">
         <v>5.5</v>
@@ -9198,17 +9198,17 @@
         <v>22</v>
       </c>
       <c r="BY34" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BZ34" t="n">
         <v>13</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -9272,13 +9272,13 @@
         <v>1.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="R35" t="n">
         <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
         <v>2.3</v>
@@ -9290,7 +9290,7 @@
         <v>1.07</v>
       </c>
       <c r="W35" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="X35" t="n">
         <v>16</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -9493,16 +9493,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G36" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H36" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>4.1</v>
@@ -9523,25 +9523,25 @@
         <v>1.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R36" t="n">
         <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T36" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U36" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
         <v>2.16</v>
@@ -9553,10 +9553,10 @@
         <v>21</v>
       </c>
       <c r="Z36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA36" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB36" t="n">
         <v>10.5</v>
@@ -9595,22 +9595,22 @@
         <v>85</v>
       </c>
       <c r="AN36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO36" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP36" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR36" t="n">
         <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
@@ -9622,10 +9622,10 @@
         <v>16</v>
       </c>
       <c r="AW36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY36" t="n">
         <v>9.199999999999999</v>
@@ -9637,49 +9637,49 @@
         <v>12</v>
       </c>
       <c r="BB36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC36" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD36" t="n">
         <v>23</v>
       </c>
       <c r="BE36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF36" t="n">
         <v>9</v>
       </c>
       <c r="BG36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH36" t="n">
         <v>4.5</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="BL36" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN36" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO36" t="n">
         <v>4</v>
       </c>
       <c r="BP36" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ36" t="n">
         <v>3.65</v>
@@ -9688,35 +9688,35 @@
         <v>29</v>
       </c>
       <c r="BS36" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT36" t="n">
         <v>9.6</v>
       </c>
       <c r="BU36" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV36" t="n">
         <v>42</v>
       </c>
       <c r="BW36" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY36" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ36" t="n">
         <v>23</v>
       </c>
       <c r="CA36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -9750,19 +9750,19 @@
         <v>1.85</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H37" t="n">
         <v>4.5</v>
       </c>
       <c r="I37" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J37" t="n">
         <v>3.3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.37</v>
@@ -9780,7 +9780,7 @@
         <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R37" t="n">
         <v>1.29</v>
@@ -9792,13 +9792,13 @@
         <v>1.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
         <v>1.22</v>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X37" t="n">
         <v>970</v>
@@ -9912,7 +9912,7 @@
         <v>3.65</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="BJ37" t="n">
         <v>12.5</v>
@@ -9930,7 +9930,7 @@
         <v>5.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="BP37" t="n">
         <v>970</v>
@@ -9948,7 +9948,7 @@
         <v>9.6</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="BV37" t="n">
         <v>55</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>7.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>3.9</v>
@@ -10040,19 +10040,19 @@
         <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T38" t="n">
         <v>2.18</v>
       </c>
       <c r="U38" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V38" t="n">
         <v>1.16</v>
       </c>
       <c r="W38" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X38" t="n">
         <v>12.5</v>
@@ -10112,7 +10112,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR38" t="n">
         <v>5</v>
@@ -10139,16 +10139,16 @@
         <v>8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BA38" t="n">
         <v>5.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD38" t="n">
         <v>5</v>
@@ -10157,28 +10157,28 @@
         <v>5.2</v>
       </c>
       <c r="BF38" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG38" t="n">
         <v>5.2</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ38" t="n">
         <v>14</v>
       </c>
       <c r="BK38" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BL38" t="n">
         <v>250</v>
       </c>
       <c r="BM38" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BN38" t="n">
         <v>4.6</v>
@@ -10190,41 +10190,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BR38" t="n">
         <v>40</v>
       </c>
       <c r="BS38" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BT38" t="n">
         <v>11</v>
       </c>
       <c r="BU38" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV38" t="n">
         <v>80</v>
       </c>
       <c r="BW38" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BX38" t="n">
         <v>95</v>
       </c>
       <c r="BY38" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BZ38" t="n">
         <v>36</v>
       </c>
       <c r="CA38" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H39" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I39" t="n">
         <v>3.8</v>
@@ -10273,7 +10273,7 @@
         <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
@@ -10303,7 +10303,7 @@
         <v>1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
         <v>1.54</v>
@@ -10375,7 +10375,7 @@
         <v>4.8</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU39" t="n">
         <v>3.4</v>
@@ -10390,7 +10390,7 @@
         <v>4.1</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ39" t="n">
         <v>4.3</v>
@@ -10402,7 +10402,7 @@
         <v>4.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD39" t="n">
         <v>4.8</v>
@@ -10411,7 +10411,7 @@
         <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG39" t="n">
         <v>4.8</v>
@@ -10438,7 +10438,7 @@
         <v>6</v>
       </c>
       <c r="BO39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP39" t="n">
         <v>25</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -10509,230 +10509,230 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G40" t="n">
-        <v>110</v>
+        <v>1.61</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I40" t="n">
-        <v>990</v>
+        <v>12</v>
       </c>
       <c r="J40" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K40" t="n">
-        <v>500</v>
+        <v>4.7</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.25</v>
       </c>
-      <c r="O40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S40" t="n">
-        <v>1.4</v>
+        <v>3.45</v>
       </c>
       <c r="T40" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U40" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W40" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE40" t="n">
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH40" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN40" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BR40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV40" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX40" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -10775,52 +10775,52 @@
         <v>1.72</v>
       </c>
       <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
         <v>4.1</v>
       </c>
-      <c r="K41" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T41" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U41" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W41" t="n">
         <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z41" t="n">
         <v>9.199999999999999</v>
@@ -10829,7 +10829,7 @@
         <v>17</v>
       </c>
       <c r="AB41" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC41" t="n">
         <v>9.199999999999999</v>
@@ -10847,49 +10847,49 @@
         <v>23</v>
       </c>
       <c r="AH41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI41" t="n">
         <v>42</v>
       </c>
       <c r="AJ41" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK41" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL41" t="n">
         <v>90</v>
       </c>
       <c r="AM41" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN41" t="n">
         <v>140</v>
       </c>
-      <c r="AN41" t="n">
-        <v>130</v>
-      </c>
       <c r="AO41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP41" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR41" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS41" t="n">
         <v>16</v>
       </c>
       <c r="AT41" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AU41" t="n">
         <v>8.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW41" t="n">
         <v>18.5</v>
@@ -10901,40 +10901,40 @@
         <v>21</v>
       </c>
       <c r="AZ41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BC41" t="n">
         <v>80</v>
       </c>
       <c r="BD41" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BE41" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="BF41" t="n">
         <v>110</v>
       </c>
       <c r="BG41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI41" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BJ41" t="n">
         <v>11</v>
       </c>
       <c r="BK41" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL41" t="n">
         <v>190</v>
@@ -10949,16 +10949,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BP41" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ41" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BR41" t="n">
         <v>65</v>
       </c>
       <c r="BS41" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BT41" t="n">
         <v>4.1</v>
@@ -10967,16 +10967,16 @@
         <v>3.8</v>
       </c>
       <c r="BV41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW41" t="n">
         <v>10</v>
       </c>
       <c r="BX41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -11020,10 +11020,10 @@
         <v>1.89</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I42" t="n">
         <v>5.3</v>
@@ -11032,7 +11032,7 @@
         <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
         <v>1.43</v>
@@ -11104,7 +11104,7 @@
         <v>950</v>
       </c>
       <c r="AI42" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ42" t="n">
         <v>23</v>
@@ -11134,13 +11134,13 @@
         <v>2.94</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AT42" t="n">
         <v>4.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV42" t="n">
         <v>7.6</v>
@@ -11164,7 +11164,7 @@
         <v>2.78</v>
       </c>
       <c r="BC42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD42" t="n">
         <v>2.62</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G43" t="n">
         <v>1.4</v>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="I43" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J43" t="n">
         <v>4.9</v>
       </c>
       <c r="K43" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L43" t="n">
         <v>1.32</v>
@@ -11319,7 +11319,7 @@
         <v>1.56</v>
       </c>
       <c r="V43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
         <v>3.5</v>
@@ -11358,7 +11358,7 @@
         <v>950</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ43" t="n">
         <v>12</v>
@@ -11475,7 +11475,7 @@
         <v>4.5</v>
       </c>
       <c r="BV43" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BW43" t="n">
         <v>5.8</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v>1.45</v>
       </c>
       <c r="G44" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H44" t="n">
         <v>9</v>
@@ -11552,7 +11552,7 @@
         <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P44" t="n">
         <v>1.71</v>
@@ -11651,7 +11651,7 @@
         <v>9</v>
       </c>
       <c r="AV44" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AW44" t="n">
         <v>7.2</v>
@@ -11714,7 +11714,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ44" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="BR44" t="n">
         <v>42</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H45" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J45" t="n">
         <v>3.4</v>
       </c>
       <c r="K45" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L45" t="n">
         <v>1.41</v>
@@ -11827,7 +11827,7 @@
         <v>1.68</v>
       </c>
       <c r="V45" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W45" t="n">
         <v>2</v>
@@ -11842,7 +11842,7 @@
         <v>38</v>
       </c>
       <c r="AA45" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB45" t="n">
         <v>8</v>
@@ -11884,7 +11884,7 @@
         <v>22</v>
       </c>
       <c r="AO45" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP45" t="n">
         <v>9.4</v>
@@ -11917,7 +11917,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA45" t="n">
         <v>5.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -12045,25 +12045,25 @@
         <v>5.8</v>
       </c>
       <c r="J46" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O46" t="n">
         <v>1.31</v>
       </c>
       <c r="P46" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q46" t="n">
         <v>1.86</v>
@@ -12072,13 +12072,13 @@
         <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T46" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U46" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V46" t="n">
         <v>1.21</v>
@@ -12195,68 +12195,68 @@
         <v>5.3</v>
       </c>
       <c r="BH46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ46" t="n">
         <v>12</v>
       </c>
       <c r="BK46" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BL46" t="n">
         <v>160</v>
       </c>
       <c r="BM46" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN46" t="n">
         <v>4.9</v>
       </c>
       <c r="BO46" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP46" t="n">
         <v>14</v>
       </c>
       <c r="BQ46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR46" t="n">
         <v>32</v>
       </c>
       <c r="BS46" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT46" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU46" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV46" t="n">
         <v>55</v>
       </c>
       <c r="BW46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX46" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY46" t="n">
         <v>5.4</v>
       </c>
       <c r="BZ46" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CA46" t="n">
         <v>4.8</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H47" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
         <v>1.41</v>
@@ -12317,10 +12317,10 @@
         <v>1.44</v>
       </c>
       <c r="P47" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R47" t="n">
         <v>1.25</v>
@@ -12335,10 +12335,10 @@
         <v>1.94</v>
       </c>
       <c r="V47" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W47" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X47" t="n">
         <v>13</v>
@@ -12359,7 +12359,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD47" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE47" t="n">
         <v>55</v>
@@ -12380,7 +12380,7 @@
         <v>46</v>
       </c>
       <c r="AK47" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL47" t="n">
         <v>55</v>
@@ -12401,10 +12401,10 @@
         <v>9.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT47" t="n">
         <v>7.8</v>
@@ -12416,7 +12416,7 @@
         <v>12.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX47" t="n">
         <v>13.5</v>
@@ -12428,25 +12428,25 @@
         <v>17</v>
       </c>
       <c r="BA47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC47" t="n">
         <v>5</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BD47" t="n">
         <v>5</v>
       </c>
-      <c r="BC47" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE47" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF47" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG47" t="n">
         <v>5</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH47" t="n">
         <v>3.45</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -890,16 +890,16 @@
         <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
         <v>2.22</v>
@@ -908,7 +908,7 @@
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -926,7 +926,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
@@ -941,10 +941,10 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>36</v>
@@ -959,10 +959,10 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -974,7 +974,7 @@
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -983,7 +983,7 @@
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
         <v>30</v>
@@ -1001,22 +1001,22 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.9</v>
@@ -1025,7 +1025,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
         <v>5</v>
@@ -1034,7 +1034,7 @@
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>5.3</v>
@@ -1046,13 +1046,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.6</v>
@@ -1064,23 +1064,23 @@
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX2" t="n">
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
         <v>1.63</v>
@@ -1150,13 +1150,13 @@
         <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1171,7 +1171,7 @@
         <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA3" t="n">
         <v>130</v>
@@ -1180,19 +1180,19 @@
         <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>17</v>
@@ -1204,7 +1204,7 @@
         <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -1216,7 +1216,7 @@
         <v>5.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -1267,10 +1267,10 @@
         <v>32</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1282,25 +1282,25 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
@@ -1315,26 +1315,26 @@
         <v>4.7</v>
       </c>
       <c r="BV3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
       </c>
       <c r="BY3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
         <v>2.44</v>
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1395,7 +1395,7 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
         <v>1.59</v>
@@ -1404,7 +1404,7 @@
         <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1416,13 +1416,13 @@
         <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>9.4</v>
@@ -1440,16 +1440,16 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
@@ -1458,7 +1458,7 @@
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1467,7 +1467,7 @@
         <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
         <v>12.5</v>
@@ -1476,10 +1476,10 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1512,7 +1512,7 @@
         <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
         <v>21</v>
@@ -1521,7 +1521,7 @@
         <v>27</v>
       </c>
       <c r="BF4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
         <v>11</v>
@@ -1533,16 +1533,16 @@
         <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL4" t="n">
         <v>75</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
@@ -1554,13 +1554,13 @@
         <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BR4" t="n">
         <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
@@ -1572,23 +1572,23 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BZ4" t="n">
         <v>18</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1652,7 +1652,7 @@
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
@@ -1709,7 +1709,7 @@
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK5" t="n">
         <v>34</v>
@@ -1721,7 +1721,7 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>24</v>
@@ -1760,25 +1760,25 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB5" t="n">
-        <v>9</v>
-      </c>
       <c r="BC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="n">
         <v>4</v>
@@ -1787,7 +1787,7 @@
         <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
         <v>3.65</v>
@@ -1796,7 +1796,7 @@
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BN5" t="n">
         <v>7</v>
@@ -1808,13 +1808,13 @@
         <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
         <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
@@ -1826,23 +1826,23 @@
         <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5" t="n">
         <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
         <v>2.84</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
         <v>1.73</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2169,7 +2169,7 @@
         <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
         <v>2.22</v>
@@ -2310,7 +2310,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>36</v>
@@ -2328,7 +2328,7 @@
         <v>5.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BV7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>1.47</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
@@ -2432,7 +2432,7 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2450,7 +2450,7 @@
         <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2489,58 +2489,58 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="G9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I9" t="n">
         <v>1.27</v>
       </c>
       <c r="J9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2665,28 +2665,28 @@
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q9" t="n">
         <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>950</v>
@@ -2695,22 +2695,22 @@
         <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB9" t="n">
         <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
         <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AF9" t="n">
         <v>180</v>
@@ -2740,7 +2740,7 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2749,7 +2749,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
         <v>7.4</v>
@@ -2764,7 +2764,7 @@
         <v>9.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
         <v>1.01</v>
@@ -2797,68 +2797,68 @@
         <v>3.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR9" t="n">
         <v>110</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>13.5</v>
@@ -2901,7 +2901,7 @@
         <v>1.27</v>
       </c>
       <c r="J10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
@@ -2913,28 +2913,28 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
         <v>4.7</v>
@@ -2946,19 +2946,19 @@
         <v>60</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB10" t="n">
         <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
         <v>12.5</v>
@@ -2976,10 +2976,10 @@
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AJ10" t="n">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="AK10" t="n">
         <v>180</v>
@@ -2994,7 +2994,7 @@
         <v>150</v>
       </c>
       <c r="AO10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AP10" t="n">
         <v>27</v>
@@ -3030,7 +3030,7 @@
         <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BB10" t="n">
         <v>95</v>
@@ -3048,7 +3048,7 @@
         <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BH10" t="n">
         <v>7</v>
@@ -3060,7 +3060,7 @@
         <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BL10" t="n">
         <v>120</v>
@@ -3069,7 +3069,7 @@
         <v>4.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BO10" t="n">
         <v>3.75</v>
@@ -3078,7 +3078,7 @@
         <v>95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
         <v>75</v>
@@ -3102,17 +3102,17 @@
         <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BZ10" t="n">
         <v>8.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -3143,172 +3143,172 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
@@ -3317,56 +3317,56 @@
         <v>3.85</v>
       </c>
       <c r="BL11" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM11" t="n">
         <v>5.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS11" t="n">
         <v>5.1</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>5.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>1.41</v>
       </c>
       <c r="G12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
         <v>9.800000000000001</v>
@@ -3412,37 +3412,37 @@
         <v>5.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
         <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
@@ -3460,19 +3460,19 @@
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AE12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -3502,13 +3502,13 @@
         <v>6.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP12" t="n">
         <v>15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR12" t="n">
         <v>34</v>
@@ -3541,7 +3541,7 @@
         <v>42</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
@@ -3553,7 +3553,7 @@
         <v>44</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG12" t="n">
         <v>48</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
         <v>1.69</v>
       </c>
       <c r="S13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
         <v>1.91</v>
@@ -3771,7 +3771,7 @@
         <v>1.96</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
         <v>11</v>
@@ -3786,7 +3786,7 @@
         <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ13" t="n">
         <v>8.4</v>
@@ -3795,7 +3795,7 @@
         <v>3.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC13" t="n">
         <v>10.5</v>
@@ -3834,13 +3834,13 @@
         <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="BP13" t="n">
         <v>8.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR13" t="n">
         <v>24</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
         <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="n">
         <v>5.3</v>
@@ -3929,31 +3929,31 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="W14" t="n">
         <v>1.17</v>
@@ -3983,7 +3983,7 @@
         <v>970</v>
       </c>
       <c r="AF14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG14" t="n">
         <v>950</v>
@@ -4001,7 +4001,7 @@
         <v>75</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="n">
         <v>95</v>
@@ -4013,22 +4013,22 @@
         <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV14" t="n">
         <v>7.6</v>
@@ -4040,28 +4040,28 @@
         <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
         <v>1.89</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
         <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
         <v>4.1</v>
@@ -4070,55 +4070,55 @@
         <v>4.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BL14" t="n">
         <v>130</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BN14" t="n">
         <v>12.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
         <v>60</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR14" t="n">
         <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="BV14" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BX14" t="n">
         <v>24</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.25</v>
@@ -4207,10 +4207,10 @@
         <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4222,10 +4222,10 @@
         <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AB15" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
         <v>970</v>
@@ -4234,7 +4234,7 @@
         <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
         <v>32</v>
@@ -4249,34 +4249,34 @@
         <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK15" t="n">
         <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
         <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AP15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR15" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AS15" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
         <v>4.5</v>
@@ -4288,10 +4288,10 @@
         <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -4300,25 +4300,25 @@
         <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH15" t="n">
         <v>5</v>
@@ -4336,53 +4336,53 @@
         <v>85</v>
       </c>
       <c r="BM15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO15" t="n">
         <v>5.3</v>
       </c>
-      <c r="BN15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BP15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA15" t="n">
         <v>4.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H16" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="I16" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.46</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE16" t="n">
         <v>55</v>
       </c>
-      <c r="AB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>44</v>
-      </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
         <v>70</v>
       </c>
       <c r="AK16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM16" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AN16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK16" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>4</v>
-      </c>
       <c r="BL16" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN16" t="n">
         <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
         <v>34</v>
       </c>
       <c r="BQ16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW16" t="n">
         <v>5.1</v>
       </c>
-      <c r="BR16" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -4667,85 +4667,85 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="H17" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
         <v>70</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
         <v>950</v>
@@ -4754,121 +4754,121 @@
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AO17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>4</v>
-      </c>
       <c r="BR17" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BS17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU17" t="n">
-        <v>2.96</v>
+        <v>4.5</v>
       </c>
       <c r="BV17" t="n">
         <v>32</v>
@@ -4877,20 +4877,20 @@
         <v>4.2</v>
       </c>
       <c r="BX17" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -4921,31 +4921,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G18" t="n">
         <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.19</v>
@@ -4960,7 +4960,7 @@
         <v>1.59</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.52</v>
@@ -4969,7 +4969,7 @@
         <v>2.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W18" t="n">
         <v>1.37</v>
@@ -4978,7 +4978,7 @@
         <v>28</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
         <v>18.5</v>
@@ -4990,16 +4990,16 @@
         <v>21</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG18" t="n">
         <v>15.5</v>
@@ -5017,10 +5017,10 @@
         <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN18" t="n">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT18" t="n">
         <v>14.5</v>
@@ -5053,7 +5053,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
@@ -5062,19 +5062,19 @@
         <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
         <v>18</v>
@@ -5083,7 +5083,7 @@
         <v>9</v>
       </c>
       <c r="BH18" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BI18" t="n">
         <v>3.45</v>
@@ -5092,13 +5092,13 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BL18" t="n">
         <v>90</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BN18" t="n">
         <v>8.6</v>
@@ -5107,16 +5107,16 @@
         <v>5.4</v>
       </c>
       <c r="BP18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BT18" t="n">
         <v>6.4</v>
@@ -5128,23 +5128,23 @@
         <v>16.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BX18" t="n">
         <v>27</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5175,73 +5175,73 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
         <v>3.8</v>
       </c>
       <c r="H19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I19" t="n">
         <v>2.18</v>
       </c>
-      <c r="I19" t="n">
-        <v>2.22</v>
-      </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
         <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AB19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
         <v>8</v>
@@ -5250,7 +5250,7 @@
         <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
         <v>27</v>
@@ -5259,19 +5259,19 @@
         <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
         <v>38</v>
       </c>
       <c r="AJ19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
         <v>100</v>
@@ -5280,10 +5280,10 @@
         <v>46</v>
       </c>
       <c r="AO19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.6</v>
@@ -5295,7 +5295,7 @@
         <v>23</v>
       </c>
       <c r="AT19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
@@ -5307,7 +5307,7 @@
         <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
@@ -5319,7 +5319,7 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
         <v>36</v>
@@ -5328,7 +5328,7 @@
         <v>42</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BF19" t="n">
         <v>32</v>
@@ -5346,7 +5346,7 @@
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BL19" t="n">
         <v>140</v>
@@ -5358,31 +5358,31 @@
         <v>8.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR19" t="n">
         <v>48</v>
       </c>
       <c r="BS19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV19" t="n">
         <v>18</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BX19" t="n">
         <v>34</v>
@@ -5391,14 +5391,14 @@
         <v>4.1</v>
       </c>
       <c r="BZ19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA19" t="n">
         <v>4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.43</v>
       </c>
       <c r="G20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H20" t="n">
         <v>7.2</v>
@@ -5459,16 +5459,16 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
         <v>1.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
@@ -5480,7 +5480,7 @@
         <v>1.15</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X20" t="n">
         <v>40</v>
@@ -5495,7 +5495,7 @@
         <v>210</v>
       </c>
       <c r="AB20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC20" t="n">
         <v>14</v>
@@ -5540,10 +5540,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>10.5</v>
@@ -5570,7 +5570,7 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -5582,19 +5582,19 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
         <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>6</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
@@ -5618,7 +5618,7 @@
         <v>9.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BR20" t="n">
         <v>21</v>
@@ -5630,10 +5630,10 @@
         <v>13</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW20" t="n">
         <v>5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5689,16 +5689,16 @@
         <v>1.84</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.24</v>
@@ -5713,10 +5713,10 @@
         <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R21" t="n">
         <v>1.64</v>
@@ -5725,19 +5725,19 @@
         <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U21" t="n">
         <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y21" t="n">
         <v>27</v>
@@ -5785,7 +5785,7 @@
         <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO21" t="n">
         <v>42</v>
@@ -5839,7 +5839,7 @@
         <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG21" t="n">
         <v>1.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I22" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.22</v>
@@ -5976,7 +5976,7 @@
         <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T22" t="n">
         <v>1.46</v>
@@ -5985,7 +5985,7 @@
         <v>2.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W22" t="n">
         <v>1.5</v>
@@ -5994,58 +5994,58 @@
         <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB22" t="n">
         <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL22" t="n">
         <v>30</v>
       </c>
-      <c r="AL22" t="n">
-        <v>32</v>
-      </c>
       <c r="AM22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AO22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.05</v>
+        <v>23</v>
       </c>
       <c r="AQ22" t="n">
         <v>14</v>
@@ -6069,7 +6069,7 @@
         <v>16.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.05</v>
+        <v>19</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="G23" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
         <v>4.1</v>
@@ -6224,7 +6224,7 @@
         <v>2.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R23" t="n">
         <v>1.77</v>
@@ -6242,7 +6242,7 @@
         <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
@@ -6251,19 +6251,19 @@
         <v>29</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
         <v>75</v>
       </c>
       <c r="AB23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="n">
         <v>12</v>
       </c>
       <c r="AD23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
@@ -6275,10 +6275,10 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ23" t="n">
         <v>25</v>
@@ -6287,28 +6287,28 @@
         <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6320,7 +6320,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX23" t="n">
         <v>12</v>
@@ -6332,7 +6332,7 @@
         <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -6344,7 +6344,7 @@
         <v>17.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
         <v>6.2</v>
@@ -6362,59 +6362,59 @@
         <v>9.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BL23" t="n">
         <v>75</v>
       </c>
       <c r="BM23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR23" t="n">
         <v>23</v>
       </c>
       <c r="BS23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX23" t="n">
         <v>32</v>
       </c>
       <c r="BY23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ23" t="n">
         <v>14.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G24" t="n">
         <v>3.25</v>
@@ -6454,13 +6454,13 @@
         <v>2.34</v>
       </c>
       <c r="I24" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.28</v>
@@ -6478,22 +6478,22 @@
         <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R24" t="n">
         <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T24" t="n">
         <v>1.6</v>
       </c>
       <c r="U24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W24" t="n">
         <v>1.44</v>
@@ -6508,10 +6508,10 @@
         <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC24" t="n">
         <v>9.199999999999999</v>
@@ -6523,10 +6523,10 @@
         <v>26</v>
       </c>
       <c r="AF24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
         <v>16.5</v>
@@ -6547,7 +6547,7 @@
         <v>70</v>
       </c>
       <c r="AN24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO24" t="n">
         <v>16</v>
@@ -6616,7 +6616,7 @@
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>110</v>
@@ -6625,10 +6625,10 @@
         <v>4.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP24" t="n">
         <v>27</v>
@@ -6646,10 +6646,10 @@
         <v>6.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW24" t="n">
         <v>3.75</v>
@@ -6661,14 +6661,14 @@
         <v>4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA24" t="n">
         <v>3.85</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -6705,10 +6705,10 @@
         <v>1.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J25" t="n">
         <v>4.3</v>
@@ -6732,19 +6732,19 @@
         <v>2.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
@@ -6762,7 +6762,7 @@
         <v>55</v>
       </c>
       <c r="AA25" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB25" t="n">
         <v>13.5</v>
@@ -6852,16 +6852,16 @@
         <v>4.5</v>
       </c>
       <c r="BE25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG25" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI25" t="n">
         <v>3.45</v>
@@ -6870,13 +6870,13 @@
         <v>11</v>
       </c>
       <c r="BK25" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL25" t="n">
         <v>110</v>
       </c>
       <c r="BM25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN25" t="n">
         <v>5.2</v>
@@ -6888,41 +6888,41 @@
         <v>12</v>
       </c>
       <c r="BQ25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BR25" t="n">
         <v>25</v>
       </c>
       <c r="BS25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT25" t="n">
         <v>10.5</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV25" t="n">
         <v>46</v>
       </c>
       <c r="BW25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BX25" t="n">
         <v>48</v>
       </c>
       <c r="BY25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ25" t="n">
         <v>16.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -6956,22 +6956,22 @@
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H26" t="n">
         <v>2.26</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J26" t="n">
         <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
         <v>1.04</v>
@@ -6986,13 +6986,13 @@
         <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="R26" t="n">
         <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
         <v>1.57</v>
@@ -7001,7 +7001,7 @@
         <v>2.52</v>
       </c>
       <c r="V26" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W26" t="n">
         <v>1.43</v>
@@ -7022,7 +7022,7 @@
         <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
         <v>12</v>
@@ -7055,7 +7055,7 @@
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
         <v>12.5</v>
@@ -7106,7 +7106,7 @@
         <v>25</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF26" t="n">
         <v>14.5</v>
@@ -7130,53 +7130,53 @@
         <v>95</v>
       </c>
       <c r="BM26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BN26" t="n">
         <v>8</v>
       </c>
       <c r="BO26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ26" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT26" t="n">
         <v>6.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV26" t="n">
         <v>18.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BX26" t="n">
         <v>29</v>
       </c>
       <c r="BY26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ26" t="n">
         <v>21</v>
       </c>
       <c r="CA26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -7216,13 +7216,13 @@
         <v>1.84</v>
       </c>
       <c r="I27" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.19</v>
@@ -7237,16 +7237,16 @@
         <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S27" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
         <v>1.48</v>
@@ -7300,70 +7300,70 @@
         <v>75</v>
       </c>
       <c r="AK27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL27" t="n">
         <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE27" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG27" t="n">
         <v>5.9</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
         <v>3.6</v>
@@ -7476,7 +7476,7 @@
         <v>2.92</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -7503,7 +7503,7 @@
         <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="U28" t="n">
         <v>1.86</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -7715,37 +7715,37 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q29" t="n">
         <v>2.28</v>
@@ -7760,13 +7760,13 @@
         <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="V29" t="n">
         <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X29" t="n">
         <v>970</v>
@@ -7823,28 +7823,28 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
@@ -7853,28 +7853,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB29" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BC29" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF29" t="n">
         <v>12</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH29" t="n">
         <v>3.25</v>
@@ -7886,13 +7886,13 @@
         <v>12.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL29" t="n">
         <v>240</v>
       </c>
       <c r="BM29" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN29" t="n">
         <v>4.2</v>
@@ -7901,44 +7901,44 @@
         <v>3.65</v>
       </c>
       <c r="BP29" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ29" t="n">
         <v>5</v>
       </c>
       <c r="BR29" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS29" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV29" t="n">
         <v>75</v>
       </c>
       <c r="BW29" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX29" t="n">
         <v>90</v>
       </c>
       <c r="BY29" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ29" t="n">
         <v>36</v>
       </c>
       <c r="CA29" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
@@ -8008,13 +8008,13 @@
         <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V30" t="n">
         <v>2.38</v>
@@ -8101,7 +8101,7 @@
         <v>16.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AY30" t="n">
         <v>18.5</v>
@@ -8170,7 +8170,7 @@
         <v>4.7</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BV30" t="n">
         <v>13.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H31" t="n">
         <v>14</v>
@@ -8238,7 +8238,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.42</v>
@@ -8265,7 +8265,7 @@
         <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="U31" t="n">
         <v>1.5</v>
@@ -8274,7 +8274,7 @@
         <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X31" t="n">
         <v>14.5</v>
@@ -8283,16 +8283,16 @@
         <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
@@ -8304,7 +8304,7 @@
         <v>6.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
         <v>950</v>
@@ -8322,7 +8322,7 @@
         <v>75</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AN31" t="n">
         <v>7.8</v>
@@ -8334,13 +8334,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT31" t="n">
         <v>5.3</v>
@@ -8349,40 +8349,40 @@
         <v>10.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AY31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH31" t="n">
         <v>3.75</v>
@@ -8391,62 +8391,62 @@
         <v>2.62</v>
       </c>
       <c r="BJ31" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BL31" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="BM31" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BN31" t="n">
         <v>3.9</v>
       </c>
       <c r="BO31" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BP31" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ31" t="n">
         <v>6</v>
       </c>
       <c r="BR31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS31" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BT31" t="n">
         <v>21</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV31" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="BW31" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BX31" t="n">
         <v>210</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BZ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -8477,25 +8477,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="J32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M32" t="n">
         <v>1.04</v>
@@ -8510,28 +8510,28 @@
         <v>2.46</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R32" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S32" t="n">
         <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="U32" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="V32" t="n">
         <v>2.84</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y32" t="n">
         <v>11.5</v>
@@ -8549,7 +8549,7 @@
         <v>12.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE32" t="n">
         <v>18</v>
@@ -8609,7 +8609,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY32" t="n">
         <v>19</v>
@@ -8621,25 +8621,25 @@
         <v>5.6</v>
       </c>
       <c r="BB32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC32" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BD32" t="n">
         <v>6</v>
       </c>
-      <c r="BD32" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG32" t="n">
         <v>5.1</v>
       </c>
       <c r="BH32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI32" t="n">
         <v>3.4</v>
@@ -8651,10 +8651,10 @@
         <v>3.4</v>
       </c>
       <c r="BL32" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN32" t="n">
         <v>12.5</v>
@@ -8666,7 +8666,7 @@
         <v>55</v>
       </c>
       <c r="BQ32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR32" t="n">
         <v>60</v>
@@ -8684,7 +8684,7 @@
         <v>11</v>
       </c>
       <c r="BW32" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BX32" t="n">
         <v>25</v>
@@ -8696,11 +8696,11 @@
         <v>15.5</v>
       </c>
       <c r="CA32" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G33" t="n">
         <v>4.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8749,7 +8749,7 @@
         <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
@@ -8770,7 +8770,7 @@
         <v>1.73</v>
       </c>
       <c r="S33" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
         <v>1.53</v>
@@ -8779,10 +8779,10 @@
         <v>2.76</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X33" t="n">
         <v>50</v>
@@ -8809,19 +8809,19 @@
         <v>970</v>
       </c>
       <c r="AF33" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG33" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AH33" t="n">
         <v>15.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="n">
         <v>40</v>
@@ -8833,13 +8833,13 @@
         <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO33" t="n">
         <v>8</v>
       </c>
       <c r="AP33" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AQ33" t="n">
         <v>13.5</v>
@@ -8848,13 +8848,13 @@
         <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AT33" t="n">
         <v>20</v>
       </c>
       <c r="AU33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV33" t="n">
         <v>10</v>
@@ -8878,25 +8878,25 @@
         <v>34</v>
       </c>
       <c r="BC33" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BD33" t="n">
         <v>22</v>
       </c>
       <c r="BE33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BF33" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG33" t="n">
         <v>7</v>
       </c>
       <c r="BH33" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.800000000000001</v>
@@ -8911,13 +8911,13 @@
         <v>5.2</v>
       </c>
       <c r="BN33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO33" t="n">
         <v>6</v>
       </c>
       <c r="BP33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ33" t="n">
         <v>4.7</v>
@@ -8926,25 +8926,25 @@
         <v>34</v>
       </c>
       <c r="BS33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV33" t="n">
         <v>14</v>
       </c>
       <c r="BW33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX33" t="n">
         <v>23</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ33" t="n">
         <v>15</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -8985,46 +8985,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="I34" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="J34" t="n">
         <v>5.1</v>
       </c>
       <c r="K34" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="M34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R34" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="S34" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
         <v>1.6</v>
@@ -9033,13 +9033,13 @@
         <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="W34" t="n">
         <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y34" t="n">
         <v>15</v>
@@ -9048,7 +9048,7 @@
         <v>13.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB34" t="n">
         <v>950</v>
@@ -9057,7 +9057,7 @@
         <v>14</v>
       </c>
       <c r="AD34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE34" t="n">
         <v>15</v>
@@ -9078,22 +9078,22 @@
         <v>170</v>
       </c>
       <c r="AK34" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
         <v>60</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN34" t="n">
         <v>55</v>
       </c>
       <c r="AO34" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ34" t="n">
         <v>10</v>
@@ -9105,7 +9105,7 @@
         <v>12.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AU34" t="n">
         <v>11</v>
@@ -9117,7 +9117,7 @@
         <v>12</v>
       </c>
       <c r="AX34" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AY34" t="n">
         <v>20</v>
@@ -9129,19 +9129,19 @@
         <v>20</v>
       </c>
       <c r="BB34" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BG34" t="n">
         <v>4.3</v>
@@ -9171,7 +9171,7 @@
         <v>3.35</v>
       </c>
       <c r="BP34" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BQ34" t="n">
         <v>4.2</v>
@@ -9180,13 +9180,13 @@
         <v>48</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT34" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BV34" t="n">
         <v>11</v>
@@ -9195,20 +9195,20 @@
         <v>3.2</v>
       </c>
       <c r="BX34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY34" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="BZ34" t="n">
         <v>13</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -9239,230 +9239,230 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="G35" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="H35" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="P35" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="V35" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="W35" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="X35" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y35" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE35" t="n">
         <v>140</v>
       </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>340</v>
-      </c>
       <c r="AF35" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AG35" t="n">
         <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AI35" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
       <c r="AJ35" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AK35" t="n">
         <v>21</v>
       </c>
       <c r="AL35" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM35" t="n">
-        <v>360</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA35" t="n">
         <v>4</v>
       </c>
-      <c r="AV35" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>17</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>320</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO35" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BP35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BR35" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BT35" t="n">
-        <v>17</v>
-      </c>
-      <c r="BU35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV35" t="n">
-        <v>160</v>
-      </c>
-      <c r="BW35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>150</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BZ35" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA35" t="n">
-        <v>4.1</v>
-      </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G36" t="n">
         <v>1.85</v>
@@ -9511,7 +9511,7 @@
         <v>4.3</v>
       </c>
       <c r="L36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M36" t="n">
         <v>1.05</v>
@@ -9523,19 +9523,19 @@
         <v>1.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R36" t="n">
         <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U36" t="n">
         <v>2.3</v>
@@ -9562,10 +9562,10 @@
         <v>10.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE36" t="n">
         <v>55</v>
@@ -9586,7 +9586,7 @@
         <v>21</v>
       </c>
       <c r="AK36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL36" t="n">
         <v>28</v>
@@ -9601,7 +9601,7 @@
         <v>55</v>
       </c>
       <c r="AP36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ36" t="n">
         <v>18.5</v>
@@ -9610,19 +9610,19 @@
         <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV36" t="n">
         <v>16</v>
       </c>
       <c r="AW36" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -9634,16 +9634,16 @@
         <v>15.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BB36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE36" t="n">
         <v>14</v>
@@ -9652,10 +9652,10 @@
         <v>9</v>
       </c>
       <c r="BG36" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BH36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI36" t="n">
         <v>3</v>
@@ -9691,22 +9691,22 @@
         <v>4.2</v>
       </c>
       <c r="BT36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU36" t="n">
         <v>3.25</v>
       </c>
       <c r="BV36" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW36" t="n">
         <v>4.4</v>
       </c>
       <c r="BX36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ36" t="n">
         <v>23</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -9747,25 +9747,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G37" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H37" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K37" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L37" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9783,22 +9783,22 @@
         <v>2.06</v>
       </c>
       <c r="R37" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X37" t="n">
         <v>970</v>
@@ -9810,34 +9810,34 @@
         <v>46</v>
       </c>
       <c r="AA37" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB37" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD37" t="n">
         <v>950</v>
       </c>
       <c r="AE37" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH37" t="n">
         <v>950</v>
       </c>
       <c r="AI37" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK37" t="n">
         <v>27</v>
@@ -9852,125 +9852,125 @@
         <v>970</v>
       </c>
       <c r="AO37" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP37" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU37" t="n">
         <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY37" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB37" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD37" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF37" t="n">
         <v>13</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ37" t="n">
         <v>12.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BL37" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM37" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP37" t="n">
         <v>970</v>
       </c>
       <c r="BQ37" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BR37" t="n">
         <v>38</v>
       </c>
       <c r="BS37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW37" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT37" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU37" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV37" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW37" t="n">
+      <c r="BX37" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY37" t="n">
         <v>4.6</v>
       </c>
-      <c r="BX37" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY37" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BZ37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA37" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -10004,22 +10004,22 @@
         <v>1.69</v>
       </c>
       <c r="G38" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H38" t="n">
         <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K38" t="n">
         <v>3.9</v>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -10034,13 +10034,13 @@
         <v>1.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R38" t="n">
         <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T38" t="n">
         <v>2.18</v>
@@ -10064,7 +10064,7 @@
         <v>60</v>
       </c>
       <c r="AA38" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB38" t="n">
         <v>7.4</v>
@@ -10112,7 +10112,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR38" t="n">
         <v>5</v>
@@ -10121,7 +10121,7 @@
         <v>5.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU38" t="n">
         <v>7.4</v>
@@ -10163,22 +10163,22 @@
         <v>5.2</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ38" t="n">
         <v>14</v>
       </c>
       <c r="BK38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL38" t="n">
         <v>250</v>
       </c>
       <c r="BM38" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BN38" t="n">
         <v>4.6</v>
@@ -10196,35 +10196,35 @@
         <v>40</v>
       </c>
       <c r="BS38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT38" t="n">
         <v>11</v>
       </c>
       <c r="BU38" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV38" t="n">
         <v>80</v>
       </c>
       <c r="BW38" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX38" t="n">
         <v>95</v>
       </c>
       <c r="BY38" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BZ38" t="n">
         <v>36</v>
       </c>
       <c r="CA38" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H39" t="n">
         <v>2.96</v>
@@ -10288,7 +10288,7 @@
         <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
@@ -10306,7 +10306,7 @@
         <v>1.35</v>
       </c>
       <c r="W39" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X39" t="n">
         <v>970</v>
@@ -10315,7 +10315,7 @@
         <v>970</v>
       </c>
       <c r="Z39" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
@@ -10363,22 +10363,22 @@
         <v>65</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT39" t="n">
         <v>3.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV39" t="n">
         <v>4.1</v>
@@ -10393,13 +10393,13 @@
         <v>3.95</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC39" t="n">
         <v>4.6</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -10521,10 +10521,10 @@
         <v>12</v>
       </c>
       <c r="J40" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.39</v>
@@ -10623,40 +10623,40 @@
         <v>3.75</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS40" t="n">
         <v>4.3</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AU40" t="n">
         <v>3.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX40" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AY40" t="n">
         <v>3.25</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB40" t="n">
         <v>3.45</v>
       </c>
       <c r="BC40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD40" t="n">
         <v>4.1</v>
@@ -10665,7 +10665,7 @@
         <v>4.3</v>
       </c>
       <c r="BF40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG40" t="n">
         <v>4.3</v>
@@ -10677,7 +10677,7 @@
         <v>2.5</v>
       </c>
       <c r="BJ40" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BK40" t="n">
         <v>3.8</v>
@@ -10707,7 +10707,7 @@
         <v>4.4</v>
       </c>
       <c r="BT40" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="BU40" t="n">
         <v>3.75</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -10763,16 +10763,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G41" t="n">
         <v>5.9</v>
       </c>
-      <c r="G41" t="n">
-        <v>6</v>
-      </c>
       <c r="H41" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I41" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="J41" t="n">
         <v>4</v>
@@ -10781,37 +10781,37 @@
         <v>4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M41" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U41" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V41" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W41" t="n">
         <v>1.2</v>
@@ -10820,10 +10820,10 @@
         <v>12.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA41" t="n">
         <v>17</v>
@@ -10832,7 +10832,7 @@
         <v>16.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD41" t="n">
         <v>10</v>
@@ -10841,16 +10841,16 @@
         <v>19</v>
       </c>
       <c r="AF41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH41" t="n">
         <v>25</v>
       </c>
       <c r="AI41" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ41" t="n">
         <v>180</v>
@@ -10862,34 +10862,34 @@
         <v>90</v>
       </c>
       <c r="AM41" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN41" t="n">
         <v>150</v>
       </c>
-      <c r="AN41" t="n">
-        <v>140</v>
-      </c>
       <c r="AO41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP41" t="n">
         <v>12</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>7</v>
       </c>
       <c r="AR41" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS41" t="n">
         <v>16</v>
       </c>
       <c r="AT41" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU41" t="n">
         <v>8.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW41" t="n">
         <v>18.5</v>
@@ -10898,13 +10898,13 @@
         <v>38</v>
       </c>
       <c r="AY41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ41" t="n">
         <v>23</v>
       </c>
       <c r="BA41" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB41" t="n">
         <v>130</v>
@@ -10916,25 +10916,25 @@
         <v>85</v>
       </c>
       <c r="BE41" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BF41" t="n">
         <v>110</v>
       </c>
       <c r="BG41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ41" t="n">
         <v>11</v>
       </c>
       <c r="BK41" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL41" t="n">
         <v>190</v>
@@ -10955,10 +10955,10 @@
         <v>14</v>
       </c>
       <c r="BR41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS41" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BT41" t="n">
         <v>4.1</v>
@@ -10970,13 +10970,13 @@
         <v>12</v>
       </c>
       <c r="BW41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
         <v>1.89</v>
       </c>
       <c r="G42" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H42" t="n">
         <v>4.7</v>
@@ -11032,7 +11032,7 @@
         <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L42" t="n">
         <v>1.43</v>
@@ -11068,7 +11068,7 @@
         <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X42" t="n">
         <v>970</v>
@@ -11149,7 +11149,7 @@
         <v>2.7</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY42" t="n">
         <v>9</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G43" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H43" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I43" t="n">
         <v>14.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K43" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L43" t="n">
         <v>1.32</v>
@@ -11322,7 +11322,7 @@
         <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="X43" t="n">
         <v>970</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -11528,16 +11528,16 @@
         <v>1.45</v>
       </c>
       <c r="G44" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H44" t="n">
         <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K44" t="n">
         <v>4.8</v>
@@ -11576,7 +11576,7 @@
         <v>1.1</v>
       </c>
       <c r="W44" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X44" t="n">
         <v>14</v>
@@ -11606,7 +11606,7 @@
         <v>7.6</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH44" t="n">
         <v>40</v>
@@ -11639,22 +11639,22 @@
         <v>18</v>
       </c>
       <c r="AR44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT44" t="n">
         <v>5.4</v>
       </c>
       <c r="AU44" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV44" t="n">
         <v>30</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX44" t="n">
         <v>6.2</v>
@@ -11663,10 +11663,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB44" t="n">
         <v>10</v>
@@ -11675,16 +11675,16 @@
         <v>16.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF44" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH44" t="n">
         <v>3.6</v>
@@ -11714,7 +11714,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ44" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="BR44" t="n">
         <v>42</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="G45" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H45" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I45" t="n">
         <v>5.4</v>
@@ -11797,7 +11797,7 @@
         <v>3.7</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M45" t="n">
         <v>1.1</v>
@@ -11812,7 +11812,7 @@
         <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R45" t="n">
         <v>1.24</v>
@@ -11830,7 +11830,7 @@
         <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X45" t="n">
         <v>12</v>
@@ -11842,7 +11842,7 @@
         <v>38</v>
       </c>
       <c r="AA45" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB45" t="n">
         <v>8</v>
@@ -11851,13 +11851,13 @@
         <v>9</v>
       </c>
       <c r="AD45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE45" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG45" t="n">
         <v>12</v>
@@ -11866,7 +11866,7 @@
         <v>27</v>
       </c>
       <c r="AI45" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ45" t="n">
         <v>25</v>
@@ -11878,13 +11878,13 @@
         <v>55</v>
       </c>
       <c r="AM45" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN45" t="n">
         <v>22</v>
       </c>
       <c r="AO45" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP45" t="n">
         <v>9.4</v>
@@ -11896,7 +11896,7 @@
         <v>30</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -11908,7 +11908,7 @@
         <v>17.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX45" t="n">
         <v>9.199999999999999</v>
@@ -11920,25 +11920,25 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB45" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC45" t="n">
         <v>20</v>
       </c>
       <c r="BD45" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH45" t="n">
         <v>3.4</v>
@@ -11950,19 +11950,19 @@
         <v>13.5</v>
       </c>
       <c r="BK45" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL45" t="n">
         <v>220</v>
       </c>
       <c r="BM45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN45" t="n">
         <v>5.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP45" t="n">
         <v>18</v>
@@ -11977,7 +11977,7 @@
         <v>4.4</v>
       </c>
       <c r="BT45" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU45" t="n">
         <v>6</v>
@@ -11992,7 +11992,7 @@
         <v>80</v>
       </c>
       <c r="BY45" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ45" t="n">
         <v>42</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
         <v>4.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
@@ -12204,13 +12204,13 @@
         <v>12</v>
       </c>
       <c r="BK46" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL46" t="n">
         <v>160</v>
       </c>
       <c r="BM46" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN46" t="n">
         <v>4.9</v>
@@ -12222,41 +12222,41 @@
         <v>14</v>
       </c>
       <c r="BQ46" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR46" t="n">
         <v>32</v>
       </c>
       <c r="BS46" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT46" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU46" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV46" t="n">
         <v>55</v>
       </c>
       <c r="BW46" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX46" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY46" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ46" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CA46" t="n">
         <v>4.8</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G47" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K47" t="n">
         <v>3.4</v>
@@ -12311,7 +12311,7 @@
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>1.44</v>
@@ -12335,10 +12335,10 @@
         <v>1.94</v>
       </c>
       <c r="V47" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X47" t="n">
         <v>13</v>
@@ -12380,7 +12380,7 @@
         <v>46</v>
       </c>
       <c r="AK47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL47" t="n">
         <v>55</v>
@@ -12416,7 +12416,7 @@
         <v>12.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX47" t="n">
         <v>13.5</v>
@@ -12428,7 +12428,7 @@
         <v>17</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB47" t="n">
         <v>5.1</v>
@@ -12437,7 +12437,7 @@
         <v>5</v>
       </c>
       <c r="BD47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE47" t="n">
         <v>5.4</v>
@@ -12446,7 +12446,7 @@
         <v>22</v>
       </c>
       <c r="BG47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH47" t="n">
         <v>3.45</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>3.55</v>
@@ -881,7 +881,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
@@ -908,34 +908,34 @@
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -947,7 +947,7 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
@@ -962,7 +962,7 @@
         <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -974,10 +974,10 @@
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -986,7 +986,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.9</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
         <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>4.7</v>
@@ -1153,7 +1153,7 @@
         <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
         <v>2.54</v>
@@ -1162,7 +1162,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1171,7 +1171,7 @@
         <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AA3" t="n">
         <v>130</v>
@@ -1183,13 +1183,13 @@
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1216,16 +1216,16 @@
         <v>5.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1240,7 +1240,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1261,7 +1261,7 @@
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
         <v>32</v>
@@ -1270,7 +1270,7 @@
         <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1288,7 +1288,7 @@
         <v>80</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
@@ -1300,7 +1300,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
@@ -1318,7 +1318,7 @@
         <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
         <v>42</v>
@@ -1330,11 +1330,11 @@
         <v>11.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
         <v>1.59</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
         <v>1.53</v>
@@ -1440,25 +1440,25 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
         <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1467,7 +1467,7 @@
         <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>12.5</v>
@@ -1494,10 +1494,10 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1506,13 +1506,13 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
         <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>21</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1652,10 +1652,10 @@
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
         <v>3.35</v>
@@ -1736,7 +1736,7 @@
         <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1790,16 +1790,16 @@
         <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
         <v>4.5</v>
@@ -1808,16 +1808,16 @@
         <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
         <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU5" t="n">
         <v>4.3</v>
@@ -1826,23 +1826,23 @@
         <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX5" t="n">
         <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1900,13 +1900,13 @@
         <v>2.84</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
         <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I7" t="n">
         <v>2.16</v>
@@ -2145,7 +2145,7 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2157,16 +2157,16 @@
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
         <v>1.77</v>
@@ -2175,10 +2175,10 @@
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
         <v>16</v>
@@ -2190,7 +2190,7 @@
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB7" t="n">
         <v>15.5</v>
@@ -2232,7 +2232,7 @@
         <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -2259,19 +2259,19 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC7" t="n">
         <v>6.8</v>
@@ -2280,31 +2280,31 @@
         <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
         <v>13</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>130</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN7" t="n">
         <v>8.199999999999999</v>
@@ -2313,7 +2313,7 @@
         <v>5.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.9</v>
@@ -2322,7 +2322,7 @@
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT7" t="n">
         <v>5.6</v>
@@ -2331,13 +2331,13 @@
         <v>3.95</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW7" t="n">
         <v>4.3</v>
       </c>
       <c r="BX7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
         <v>4.9</v>
@@ -2346,11 +2346,11 @@
         <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.47</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
@@ -2432,7 +2432,7 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>950</v>
@@ -2495,7 +2495,7 @@
         <v>3.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
         <v>4.3</v>
@@ -2504,28 +2504,28 @@
         <v>2.98</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AY8" t="n">
         <v>3.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BC8" t="n">
         <v>3.6</v>
@@ -2534,13 +2534,13 @@
         <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2644,13 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="J9" t="n">
         <v>6.6</v>
       </c>
       <c r="K9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2665,25 +2665,25 @@
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q9" t="n">
         <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
         <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
@@ -2695,7 +2695,7 @@
         <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
         <v>6.8</v>
@@ -2806,13 +2806,13 @@
         <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL9" t="n">
         <v>170</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN9" t="n">
         <v>18</v>
@@ -2824,22 +2824,22 @@
         <v>130</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR9" t="n">
         <v>110</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BT9" t="n">
         <v>4</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BW9" t="n">
         <v>5</v>
@@ -2848,17 +2848,17 @@
         <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
         <v>1.25</v>
@@ -2901,10 +2901,10 @@
         <v>1.27</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>1.16</v>
@@ -2913,7 +2913,7 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>1.11</v>
@@ -2922,13 +2922,13 @@
         <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="T10" t="n">
         <v>1.79</v>
@@ -2949,7 +2949,7 @@
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
         <v>11.5</v>
@@ -2970,13 +2970,13 @@
         <v>150</v>
       </c>
       <c r="AG10" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
         <v>480</v>
@@ -3048,7 +3048,7 @@
         <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BH10" t="n">
         <v>7</v>
@@ -3081,7 +3081,7 @@
         <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BS10" t="n">
         <v>4.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
         <v>3.85</v>
@@ -3176,7 +3176,7 @@
         <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
         <v>1.28</v>
@@ -3215,7 +3215,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -3239,7 +3239,7 @@
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>140</v>
@@ -3248,7 +3248,7 @@
         <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>9.4</v>
@@ -3260,7 +3260,7 @@
         <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3284,10 +3284,10 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>44</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
@@ -3296,10 +3296,10 @@
         <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG11" t="n">
         <v>36</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3424,25 +3424,25 @@
         <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
@@ -3538,7 +3538,7 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB12" t="n">
         <v>10.5</v>
@@ -3547,7 +3547,7 @@
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
         <v>44</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.35</v>
       </c>
       <c r="H13" t="n">
         <v>10.5</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -3702,7 +3702,7 @@
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3798,7 +3798,7 @@
         <v>5.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD13" t="n">
         <v>8.800000000000001</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I14" t="n">
         <v>1.57</v>
@@ -3944,7 +3944,7 @@
         <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
         <v>1.7</v>
@@ -4013,64 +4013,64 @@
         <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AV14" t="n">
         <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>2.18</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6</v>
       </c>
-      <c r="BA14" t="n">
-        <v>21</v>
-      </c>
       <c r="BB14" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="BC14" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.93</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH14" t="n">
         <v>4.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
@@ -4088,7 +4088,7 @@
         <v>12.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
         <v>60</v>
@@ -4118,7 +4118,7 @@
         <v>24</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G16" t="n">
         <v>3.35</v>
@@ -4470,13 +4470,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z16" t="n">
         <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB16" t="n">
         <v>9</v>
@@ -4485,7 +4485,7 @@
         <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
@@ -4503,7 +4503,7 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
         <v>60</v>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
         <v>14.5</v>
@@ -4554,25 +4554,25 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH16" t="n">
         <v>2.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I17" t="n">
         <v>3.3</v>
@@ -4691,7 +4691,7 @@
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
@@ -4718,7 +4718,7 @@
         <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -4766,7 +4766,7 @@
         <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN17" t="n">
         <v>36</v>
@@ -4775,7 +4775,7 @@
         <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
         <v>7.4</v>
@@ -4838,7 +4838,7 @@
         <v>12</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL17" t="n">
         <v>180</v>
@@ -4853,7 +4853,7 @@
         <v>4.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ17" t="n">
         <v>4.1</v>
@@ -4868,7 +4868,7 @@
         <v>7.2</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV17" t="n">
         <v>32</v>
@@ -4877,10 +4877,10 @@
         <v>4.2</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>44</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
         <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="R18" t="n">
         <v>1.59</v>
@@ -5047,22 +5047,22 @@
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AX18" t="n">
         <v>6.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
         <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
         <v>7.8</v>
@@ -5071,13 +5071,13 @@
         <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BF18" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG18" t="n">
         <v>9</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.32</v>
@@ -5208,28 +5208,28 @@
         <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
@@ -5241,7 +5241,7 @@
         <v>34</v>
       </c>
       <c r="AB19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
         <v>8</v>
@@ -5253,7 +5253,7 @@
         <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG19" t="n">
         <v>15.5</v>
@@ -5265,13 +5265,13 @@
         <v>38</v>
       </c>
       <c r="AJ19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK19" t="n">
         <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>100</v>
@@ -5286,7 +5286,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
@@ -5337,7 +5337,7 @@
         <v>13.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI19" t="n">
         <v>2.82</v>
@@ -5346,13 +5346,13 @@
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BL19" t="n">
         <v>140</v>
       </c>
       <c r="BM19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN19" t="n">
         <v>8.6</v>
@@ -5364,41 +5364,41 @@
         <v>36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR19" t="n">
         <v>48</v>
       </c>
       <c r="BS19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV19" t="n">
         <v>18</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="BX19" t="n">
         <v>34</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ19" t="n">
         <v>29</v>
       </c>
       <c r="CA19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>7.2</v>
       </c>
       <c r="I20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>5.5</v>
@@ -5471,13 +5471,13 @@
         <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
         <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W20" t="n">
         <v>3.15</v>
@@ -5591,22 +5591,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BL20" t="n">
         <v>90</v>
       </c>
       <c r="BM20" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BN20" t="n">
         <v>5.1</v>
@@ -5618,41 +5618,41 @@
         <v>9.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BR20" t="n">
         <v>21</v>
       </c>
       <c r="BS20" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BT20" t="n">
         <v>13</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BV20" t="n">
         <v>55</v>
       </c>
       <c r="BW20" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BX20" t="n">
         <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
         <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
         <v>2.4</v>
@@ -5746,7 +5746,7 @@
         <v>46</v>
       </c>
       <c r="AA21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="n">
         <v>15.5</v>
@@ -5782,13 +5782,13 @@
         <v>30</v>
       </c>
       <c r="AM21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
         <v>7.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP21" t="n">
         <v>1.05</v>
@@ -5854,59 +5854,59 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL21" t="n">
         <v>90</v>
       </c>
       <c r="BM21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
         <v>13</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR21" t="n">
         <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT21" t="n">
         <v>9.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX21" t="n">
         <v>40</v>
       </c>
       <c r="BY21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BZ21" t="n">
         <v>16</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q23" t="n">
         <v>1.41</v>
@@ -6233,7 +6233,7 @@
         <v>2.08</v>
       </c>
       <c r="T23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U23" t="n">
         <v>2.82</v>
@@ -6362,13 +6362,13 @@
         <v>9.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL23" t="n">
         <v>75</v>
       </c>
       <c r="BM23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN23" t="n">
         <v>6.2</v>
@@ -6386,10 +6386,10 @@
         <v>23</v>
       </c>
       <c r="BS23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU23" t="n">
         <v>3.35</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6454,10 +6454,10 @@
         <v>2.34</v>
       </c>
       <c r="I24" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
         <v>3.85</v>
@@ -6475,25 +6475,25 @@
         <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R24" t="n">
         <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U24" t="n">
         <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W24" t="n">
         <v>1.44</v>
@@ -6538,7 +6538,7 @@
         <v>50</v>
       </c>
       <c r="AK24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -6547,7 +6547,7 @@
         <v>70</v>
       </c>
       <c r="AN24" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
         <v>16</v>
@@ -6613,7 +6613,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK24" t="n">
         <v>6.6</v>
@@ -6622,25 +6622,25 @@
         <v>110</v>
       </c>
       <c r="BM24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BR24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT24" t="n">
         <v>6.6</v>
@@ -6649,26 +6649,26 @@
         <v>4.8</v>
       </c>
       <c r="BV24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ24" t="n">
         <v>24</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H25" t="n">
         <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.26</v>
@@ -6729,28 +6729,28 @@
         <v>1.2</v>
       </c>
       <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.44</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
       </c>
       <c r="T25" t="n">
         <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X25" t="n">
         <v>950</v>
@@ -6759,52 +6759,52 @@
         <v>950</v>
       </c>
       <c r="Z25" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA25" t="n">
         <v>140</v>
       </c>
       <c r="AB25" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF25" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP25" t="n">
         <v>18.5</v>
@@ -6813,10 +6813,10 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
@@ -6828,10 +6828,10 @@
         <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -6840,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="BB25" t="n">
         <v>12.5</v>
@@ -6849,34 +6849,34 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ25" t="n">
         <v>11</v>
       </c>
       <c r="BK25" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BL25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM25" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BN25" t="n">
         <v>5.2</v>
@@ -6888,41 +6888,41 @@
         <v>12</v>
       </c>
       <c r="BQ25" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BR25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS25" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BT25" t="n">
         <v>10.5</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV25" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX25" t="n">
         <v>46</v>
       </c>
-      <c r="BW25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>48</v>
-      </c>
       <c r="BY25" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BZ25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
         <v>2.26</v>
       </c>
       <c r="I26" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J26" t="n">
         <v>3.85</v>
@@ -6995,7 +6995,7 @@
         <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U26" t="n">
         <v>2.52</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G27" t="n">
         <v>4.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -7485,16 +7485,16 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
         <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
         <v>1.24</v>
@@ -7503,16 +7503,16 @@
         <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
         <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
         <v>970</v>
@@ -7569,58 +7569,58 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.9</v>
+        <v>1.83</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AU28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD28" t="n">
         <v>3.2</v>
       </c>
-      <c r="AV28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW28" t="n">
+      <c r="BE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF28" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG28" t="n">
-        <v>4.8</v>
+        <v>1.86</v>
       </c>
       <c r="BH28" t="n">
         <v>3.35</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G29" t="n">
         <v>1.75</v>
       </c>
       <c r="H29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -7814,7 +7814,7 @@
         <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN29" t="n">
         <v>970</v>
@@ -7835,13 +7835,13 @@
         <v>5</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AW29" t="n">
         <v>6.8</v>
@@ -7850,13 +7850,13 @@
         <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AZ29" t="n">
         <v>5.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB29" t="n">
         <v>5.4</v>
@@ -7886,13 +7886,13 @@
         <v>12.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL29" t="n">
         <v>240</v>
       </c>
       <c r="BM29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN29" t="n">
         <v>4.2</v>
@@ -7904,41 +7904,41 @@
         <v>15</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR29" t="n">
         <v>36</v>
       </c>
       <c r="BS29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT29" t="n">
         <v>11</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV29" t="n">
         <v>75</v>
       </c>
       <c r="BW29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX29" t="n">
         <v>90</v>
       </c>
       <c r="BY29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ29" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CA29" t="n">
         <v>6.2</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -8014,7 +8014,7 @@
         <v>1.98</v>
       </c>
       <c r="U30" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
         <v>2.38</v>
@@ -8101,7 +8101,7 @@
         <v>16.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY30" t="n">
         <v>18.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -8223,58 +8223,58 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G31" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H31" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="I31" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K31" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="X31" t="n">
         <v>14.5</v>
@@ -8283,49 +8283,49 @@
         <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
         <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL31" t="n">
         <v>75</v>
       </c>
       <c r="AM31" t="n">
-        <v>510</v>
+        <v>560</v>
       </c>
       <c r="AN31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
@@ -8334,76 +8334,76 @@
         <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS31" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU31" t="n">
         <v>10.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BA31" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BD31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG31" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>10.5</v>
       </c>
       <c r="BH31" t="n">
         <v>3.75</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ31" t="n">
         <v>17</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL31" t="n">
         <v>410</v>
       </c>
       <c r="BM31" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BN31" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO31" t="n">
         <v>2.98</v>
@@ -8418,35 +8418,35 @@
         <v>36</v>
       </c>
       <c r="BS31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT31" t="n">
         <v>21</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV31" t="n">
         <v>230</v>
       </c>
       <c r="BW31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX31" t="n">
         <v>210</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BZ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA31" t="n">
         <v>4.7</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v>4.7</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.28</v>
@@ -8528,7 +8528,7 @@
         <v>2.84</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
         <v>30</v>
@@ -8537,7 +8537,7 @@
         <v>11.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
         <v>16.5</v>
@@ -8546,7 +8546,7 @@
         <v>950</v>
       </c>
       <c r="AC32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD32" t="n">
         <v>10.5</v>
@@ -8561,7 +8561,7 @@
         <v>32</v>
       </c>
       <c r="AH32" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
         <v>36</v>
@@ -8609,7 +8609,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY32" t="n">
         <v>19</v>
@@ -8618,22 +8618,22 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB32" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG32" t="n">
         <v>5.1</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -8737,10 +8737,10 @@
         <v>4.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I33" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8758,22 +8758,22 @@
         <v>6.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R33" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T33" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U33" t="n">
         <v>2.76</v>
@@ -8782,64 +8782,64 @@
         <v>2.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
         <v>24</v>
       </c>
       <c r="AB33" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AC33" t="n">
         <v>10.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE33" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AF33" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AG33" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI33" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AJ33" t="n">
         <v>80</v>
       </c>
       <c r="AK33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM33" t="n">
         <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO33" t="n">
         <v>8</v>
       </c>
       <c r="AP33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ33" t="n">
         <v>13.5</v>
@@ -8848,52 +8848,52 @@
         <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV33" t="n">
         <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX33" t="n">
         <v>22</v>
       </c>
       <c r="AY33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ33" t="n">
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BB33" t="n">
         <v>34</v>
       </c>
       <c r="BC33" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BD33" t="n">
         <v>22</v>
       </c>
       <c r="BE33" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BF33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BI33" t="n">
         <v>3.8</v>
@@ -8902,59 +8902,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BL33" t="n">
         <v>80</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BN33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO33" t="n">
         <v>6</v>
       </c>
       <c r="BP33" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR33" t="n">
         <v>34</v>
       </c>
       <c r="BS33" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BX33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA33" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G34" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="J34" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="K34" t="n">
         <v>5.4</v>
@@ -9015,34 +9015,34 @@
         <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R34" t="n">
         <v>1.75</v>
       </c>
       <c r="S34" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T34" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U34" t="n">
         <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z34" t="n">
         <v>13.5</v>
@@ -9051,10 +9051,10 @@
         <v>17</v>
       </c>
       <c r="AB34" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AC34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD34" t="n">
         <v>11</v>
@@ -9069,7 +9069,7 @@
         <v>950</v>
       </c>
       <c r="AH34" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI34" t="n">
         <v>26</v>
@@ -9078,7 +9078,7 @@
         <v>170</v>
       </c>
       <c r="AK34" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AL34" t="n">
         <v>60</v>
@@ -9093,7 +9093,7 @@
         <v>6.4</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ34" t="n">
         <v>10</v>
@@ -9105,7 +9105,7 @@
         <v>12.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU34" t="n">
         <v>11</v>
@@ -9129,22 +9129,22 @@
         <v>20</v>
       </c>
       <c r="BB34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC34" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC34" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD34" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH34" t="n">
         <v>5.9</v>
@@ -9156,13 +9156,13 @@
         <v>11.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BL34" t="n">
         <v>95</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BN34" t="n">
         <v>12.5</v>
@@ -9180,35 +9180,35 @@
         <v>48</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT34" t="n">
         <v>5.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BV34" t="n">
         <v>11</v>
       </c>
       <c r="BW34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BX34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY34" t="n">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="BZ34" t="n">
         <v>13</v>
       </c>
       <c r="CA34" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H35" t="n">
         <v>6.8</v>
@@ -9254,7 +9254,7 @@
         <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.37</v>
@@ -9272,10 +9272,10 @@
         <v>1.96</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S35" t="n">
         <v>3.2</v>
@@ -9284,13 +9284,13 @@
         <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V35" t="n">
         <v>1.12</v>
       </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="Z35" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AA35" t="n">
         <v>280</v>
@@ -9323,7 +9323,7 @@
         <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI35" t="n">
         <v>130</v>
@@ -9341,7 +9341,7 @@
         <v>170</v>
       </c>
       <c r="AN35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO35" t="n">
         <v>190</v>
@@ -9350,13 +9350,13 @@
         <v>12</v>
       </c>
       <c r="AQ35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT35" t="n">
         <v>6.8</v>
@@ -9368,7 +9368,7 @@
         <v>20</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX35" t="n">
         <v>6.8</v>
@@ -9377,10 +9377,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB35" t="n">
         <v>10</v>
@@ -9389,16 +9389,16 @@
         <v>12.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF35" t="n">
         <v>6.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH35" t="n">
         <v>4.1</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G36" t="n">
         <v>1.85</v>
@@ -9502,7 +9502,7 @@
         <v>4.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>4.1</v>
@@ -9517,16 +9517,16 @@
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R36" t="n">
         <v>1.5</v>
@@ -9535,7 +9535,7 @@
         <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U36" t="n">
         <v>2.3</v>
@@ -9547,7 +9547,7 @@
         <v>2.16</v>
       </c>
       <c r="X36" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="n">
         <v>21</v>
@@ -9559,7 +9559,7 @@
         <v>110</v>
       </c>
       <c r="AB36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
         <v>9.199999999999999</v>
@@ -9577,16 +9577,16 @@
         <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI36" t="n">
         <v>55</v>
       </c>
       <c r="AJ36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL36" t="n">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>10</v>
       </c>
       <c r="AO36" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP36" t="n">
         <v>17</v>
@@ -9610,19 +9610,19 @@
         <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV36" t="n">
         <v>16</v>
       </c>
       <c r="AW36" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -9637,13 +9637,13 @@
         <v>44</v>
       </c>
       <c r="BB36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC36" t="n">
         <v>16</v>
       </c>
       <c r="BD36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE36" t="n">
         <v>14</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -9762,10 +9762,10 @@
         <v>3.35</v>
       </c>
       <c r="K37" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9783,7 +9783,7 @@
         <v>2.06</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
         <v>3.8</v>
@@ -9798,7 +9798,7 @@
         <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X37" t="n">
         <v>970</v>
@@ -9813,10 +9813,10 @@
         <v>140</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD37" t="n">
         <v>950</v>
@@ -9828,7 +9828,7 @@
         <v>14</v>
       </c>
       <c r="AG37" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
         <v>950</v>
@@ -9849,7 +9849,7 @@
         <v>160</v>
       </c>
       <c r="AN37" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="n">
         <v>110</v>
@@ -9858,13 +9858,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT37" t="n">
         <v>6</v>
@@ -9873,10 +9873,10 @@
         <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX37" t="n">
         <v>9.800000000000001</v>
@@ -9885,28 +9885,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB37" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BC37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF37" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>13</v>
-      </c>
       <c r="BG37" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH37" t="n">
         <v>3.7</v>
@@ -9933,7 +9933,7 @@
         <v>3.5</v>
       </c>
       <c r="BP37" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="BQ37" t="n">
         <v>3.85</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J38" t="n">
         <v>3.45</v>
@@ -10028,7 +10028,7 @@
         <v>2.88</v>
       </c>
       <c r="O38" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="P38" t="n">
         <v>1.64</v>
@@ -10040,7 +10040,7 @@
         <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T38" t="n">
         <v>2.18</v>
@@ -10112,7 +10112,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR38" t="n">
         <v>5</v>
@@ -10121,10 +10121,10 @@
         <v>5.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
         <v>19.5</v>
@@ -10139,7 +10139,7 @@
         <v>8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
         <v>5.2</v>
@@ -10148,7 +10148,7 @@
         <v>16</v>
       </c>
       <c r="BC38" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD38" t="n">
         <v>5</v>
@@ -10157,7 +10157,7 @@
         <v>5.2</v>
       </c>
       <c r="BF38" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG38" t="n">
         <v>5.2</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -10255,25 +10255,25 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J39" t="n">
         <v>2.84</v>
       </c>
-      <c r="H39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.74</v>
-      </c>
       <c r="K39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L39" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
@@ -10282,49 +10282,49 @@
         <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P39" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S39" t="n">
         <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U39" t="n">
         <v>1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="X39" t="n">
         <v>970</v>
       </c>
       <c r="Y39" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB39" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC39" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD39" t="n">
         <v>970</v>
@@ -10363,46 +10363,46 @@
         <v>65</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW39" t="n">
+      <c r="BA39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC39" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>4.6</v>
       </c>
       <c r="BD39" t="n">
         <v>4.8</v>
@@ -10411,7 +10411,7 @@
         <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG39" t="n">
         <v>4.8</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -10509,58 +10509,58 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K40" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L40" t="n">
         <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="O40" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P40" t="n">
         <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W40" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X40" t="n">
         <v>970</v>
@@ -10569,7 +10569,7 @@
         <v>950</v>
       </c>
       <c r="Z40" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
@@ -10578,7 +10578,7 @@
         <v>7.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD40" t="n">
         <v>950</v>
@@ -10617,70 +10617,70 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AR40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV40" t="n">
+      <c r="BA40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC40" t="n">
         <v>4</v>
       </c>
-      <c r="AW40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BD40" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF40" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ40" t="n">
         <v>970</v>
       </c>
       <c r="BK40" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10689,19 +10689,19 @@
         <v>4.9</v>
       </c>
       <c r="BN40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO40" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BP40" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ40" t="n">
         <v>3.6</v>
       </c>
       <c r="BR40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS40" t="n">
         <v>4.4</v>
@@ -10710,7 +10710,7 @@
         <v>970</v>
       </c>
       <c r="BU40" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV40" t="n">
         <v>120</v>
@@ -10725,14 +10725,14 @@
         <v>4.8</v>
       </c>
       <c r="BZ40" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA40" t="n">
         <v>4.3</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G41" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I41" t="n">
         <v>1.74</v>
       </c>
       <c r="J41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K41" t="n">
         <v>4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.47</v>
@@ -10796,19 +10796,19 @@
         <v>1.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
         <v>4.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U41" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V41" t="n">
         <v>2.36</v>
@@ -10823,10 +10823,10 @@
         <v>7.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA41" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB41" t="n">
         <v>16.5</v>
@@ -10853,7 +10853,7 @@
         <v>44</v>
       </c>
       <c r="AJ41" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK41" t="n">
         <v>90</v>
@@ -10862,16 +10862,16 @@
         <v>90</v>
       </c>
       <c r="AM41" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN41" t="n">
         <v>160</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>150</v>
       </c>
       <c r="AO41" t="n">
         <v>12.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ41" t="n">
         <v>7</v>
@@ -10886,7 +10886,7 @@
         <v>15.5</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV41" t="n">
         <v>9.800000000000001</v>
@@ -10895,7 +10895,7 @@
         <v>18.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY41" t="n">
         <v>22</v>
@@ -10907,7 +10907,7 @@
         <v>40</v>
       </c>
       <c r="BB41" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BC41" t="n">
         <v>80</v>
@@ -10916,10 +10916,10 @@
         <v>85</v>
       </c>
       <c r="BE41" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="BF41" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BG41" t="n">
         <v>11.5</v>
@@ -10931,10 +10931,10 @@
         <v>2.9</v>
       </c>
       <c r="BJ41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BL41" t="n">
         <v>190</v>
@@ -10952,19 +10952,19 @@
         <v>60</v>
       </c>
       <c r="BQ41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BR41" t="n">
         <v>70</v>
       </c>
       <c r="BS41" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT41" t="n">
         <v>4.1</v>
       </c>
       <c r="BU41" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV41" t="n">
         <v>12</v>
@@ -10976,7 +10976,7 @@
         <v>32</v>
       </c>
       <c r="BY41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G42" t="n">
         <v>2.02</v>
       </c>
       <c r="H42" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J42" t="n">
         <v>3.35</v>
@@ -11035,19 +11035,19 @@
         <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M42" t="n">
         <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
         <v>1.43</v>
       </c>
       <c r="P42" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q42" t="n">
         <v>2.22</v>
@@ -11056,7 +11056,7 @@
         <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T42" t="n">
         <v>1.89</v>
@@ -11068,7 +11068,7 @@
         <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X42" t="n">
         <v>970</v>
@@ -11173,7 +11173,7 @@
         <v>2.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>2.78</v>
+        <v>7.2</v>
       </c>
       <c r="BG42" t="n">
         <v>2.18</v>
@@ -11200,7 +11200,7 @@
         <v>5</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP42" t="n">
         <v>17</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
         <v>1.37</v>
       </c>
       <c r="H43" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
         <v>14.5</v>
@@ -11295,7 +11295,7 @@
         <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
         <v>1.3</v>
@@ -11337,7 +11337,7 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC43" t="n">
         <v>14.5</v>
@@ -11373,7 +11373,7 @@
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
@@ -11382,55 +11382,55 @@
         <v>4.9</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR43" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="AT43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV43" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AW43" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AX43" t="n">
         <v>5.8</v>
       </c>
       <c r="AY43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB43" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>4.2</v>
       </c>
       <c r="BC43" t="n">
         <v>4.9</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BF43" t="n">
         <v>5.2</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="BH43" t="n">
         <v>4.1</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G44" t="n">
         <v>1.51</v>
@@ -11534,13 +11534,13 @@
         <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J44" t="n">
         <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L44" t="n">
         <v>1.38</v>
@@ -11552,7 +11552,7 @@
         <v>3.05</v>
       </c>
       <c r="O44" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P44" t="n">
         <v>1.71</v>
@@ -11567,7 +11567,7 @@
         <v>4.3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="U44" t="n">
         <v>1.58</v>
@@ -11579,46 +11579,46 @@
         <v>2.96</v>
       </c>
       <c r="X44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
         <v>24</v>
       </c>
       <c r="Z44" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AB44" t="n">
         <v>6.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE44" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AF44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG44" t="n">
         <v>11.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI44" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="n">
         <v>65</v>
@@ -11630,61 +11630,61 @@
         <v>11</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AP44" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR44" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AS44" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU44" t="n">
         <v>9.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
         <v>30</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB44" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE44" t="n">
         <v>10</v>
       </c>
-      <c r="BC44" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG44" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BH44" t="n">
         <v>3.6</v>
@@ -11726,7 +11726,7 @@
         <v>16.5</v>
       </c>
       <c r="BU44" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="BV44" t="n">
         <v>150</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -11779,13 +11779,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H45" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I45" t="n">
         <v>5.4</v>
@@ -11794,7 +11794,7 @@
         <v>3.4</v>
       </c>
       <c r="K45" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L45" t="n">
         <v>1.42</v>
@@ -11812,25 +11812,25 @@
         <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R45" t="n">
         <v>1.24</v>
       </c>
       <c r="S45" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T45" t="n">
         <v>2.04</v>
       </c>
       <c r="U45" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V45" t="n">
         <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>12</v>
@@ -11854,7 +11854,7 @@
         <v>21</v>
       </c>
       <c r="AE45" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF45" t="n">
         <v>11</v>
@@ -11917,19 +11917,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA45" t="n">
         <v>6</v>
       </c>
       <c r="BB45" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC45" t="n">
         <v>20</v>
       </c>
       <c r="BD45" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE45" t="n">
         <v>6</v>
@@ -11950,19 +11950,19 @@
         <v>13.5</v>
       </c>
       <c r="BK45" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL45" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="BM45" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN45" t="n">
         <v>5.2</v>
       </c>
       <c r="BO45" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP45" t="n">
         <v>18</v>
@@ -11977,7 +11977,7 @@
         <v>4.4</v>
       </c>
       <c r="BT45" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU45" t="n">
         <v>6</v>
@@ -11986,13 +11986,13 @@
         <v>60</v>
       </c>
       <c r="BW45" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX45" t="n">
         <v>80</v>
       </c>
       <c r="BY45" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ45" t="n">
         <v>42</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
         <v>4.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
@@ -12072,13 +12072,13 @@
         <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U46" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>1.21</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>2.44</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H47" t="n">
         <v>3.25</v>
@@ -12302,7 +12302,7 @@
         <v>3.1</v>
       </c>
       <c r="K47" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L47" t="n">
         <v>1.41</v>
@@ -12317,7 +12317,7 @@
         <v>1.44</v>
       </c>
       <c r="P47" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q47" t="n">
         <v>2.28</v>
@@ -12353,10 +12353,10 @@
         <v>65</v>
       </c>
       <c r="AB47" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD47" t="n">
         <v>17</v>
@@ -12368,7 +12368,7 @@
         <v>19</v>
       </c>
       <c r="AG47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH47" t="n">
         <v>24</v>
@@ -12389,7 +12389,7 @@
         <v>160</v>
       </c>
       <c r="AN47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO47" t="n">
         <v>55</v>
@@ -12398,13 +12398,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ47" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.8</v>
+        <v>19</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT47" t="n">
         <v>7.8</v>
@@ -12416,7 +12416,7 @@
         <v>12.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX47" t="n">
         <v>13.5</v>
@@ -12428,25 +12428,25 @@
         <v>17</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB47" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BC47" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF47" t="n">
         <v>22</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.1</v>
+        <v>36</v>
       </c>
       <c r="BH47" t="n">
         <v>3.45</v>
@@ -12458,7 +12458,7 @@
         <v>12.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="BL47" t="n">
         <v>190</v>
@@ -12470,7 +12470,7 @@
         <v>6.4</v>
       </c>
       <c r="BO47" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BP47" t="n">
         <v>25</v>
@@ -12488,7 +12488,7 @@
         <v>7.4</v>
       </c>
       <c r="BU47" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV47" t="n">
         <v>36</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -881,34 +881,34 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
         <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -917,10 +917,10 @@
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
@@ -947,10 +947,10 @@
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>34</v>
@@ -959,13 +959,13 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
         <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>12</v>
@@ -974,10 +974,10 @@
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -986,7 +986,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,25 +998,25 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>3.9</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
         <v>4.7</v>
@@ -1138,52 +1138,52 @@
         <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
         <v>2.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB3" t="n">
         <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>65</v>
@@ -1198,13 +1198,13 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>410</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -1213,19 +1213,19 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AO3" t="n">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="AP3" t="n">
         <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1237,10 +1237,10 @@
         <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1261,16 +1261,16 @@
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1282,13 +1282,13 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>80</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
@@ -1300,10 +1300,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BS3" t="n">
         <v>6.6</v>
@@ -1312,29 +1312,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
         <v>42</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1386,52 +1386,52 @@
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="U4" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AC4" t="n">
         <v>9.4</v>
@@ -1440,19 +1440,19 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
@@ -1464,85 +1464,85 @@
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>12</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BL4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
@@ -1554,13 +1554,13 @@
         <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR4" t="n">
         <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
@@ -1572,23 +1572,23 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX4" t="n">
         <v>26</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G5" t="n">
         <v>2.86</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.98</v>
-      </c>
       <c r="H5" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1643,7 +1643,7 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
@@ -1652,16 +1652,16 @@
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
         <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
         <v>2.26</v>
@@ -1670,7 +1670,7 @@
         <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
@@ -1679,16 +1679,16 @@
         <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
         <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
@@ -1697,10 +1697,10 @@
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
@@ -1712,16 +1712,16 @@
         <v>46</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
         <v>24</v>
@@ -1730,10 +1730,10 @@
         <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
         <v>32</v>
@@ -1745,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1760,22 +1760,22 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BG5" t="n">
         <v>20</v>
@@ -1784,19 +1784,19 @@
         <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1808,10 +1808,10 @@
         <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
         <v>6.4</v>
@@ -1820,16 +1820,16 @@
         <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV5" t="n">
         <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY5" t="n">
         <v>6.4</v>
@@ -1838,11 +1838,11 @@
         <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I6" t="n">
         <v>1.91</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
@@ -2160,19 +2160,19 @@
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.86</v>
@@ -2187,64 +2187,64 @@
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB7" t="n">
         <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>18</v>
       </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
       <c r="AI7" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
         <v>13</v>
@@ -2253,13 +2253,13 @@
         <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
         <v>13.5</v>
@@ -2268,43 +2268,43 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BG7" t="n">
         <v>13</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="BL7" t="n">
         <v>130</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BN7" t="n">
         <v>8.199999999999999</v>
@@ -2316,7 +2316,7 @@
         <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
@@ -2331,26 +2331,26 @@
         <v>3.95</v>
       </c>
       <c r="BV7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX7" t="n">
         <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ7" t="n">
         <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G8" t="n">
         <v>1.57</v>
@@ -2396,7 +2396,7 @@
         <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.38</v>
@@ -2435,7 +2435,7 @@
         <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
@@ -2450,7 +2450,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2471,13 +2471,13 @@
         <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2489,58 +2489,58 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
         <v>3.45</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I9" t="n">
         <v>1.28</v>
@@ -2650,7 +2650,7 @@
         <v>6.6</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2692,10 +2692,10 @@
         <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
         <v>10</v>
@@ -2704,16 +2704,16 @@
         <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>970</v>
       </c>
       <c r="AF9" t="n">
-        <v>180</v>
+        <v>540</v>
       </c>
       <c r="AG9" t="n">
         <v>950</v>
@@ -2722,7 +2722,7 @@
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2743,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.4</v>
@@ -2755,7 +2755,7 @@
         <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
@@ -2764,34 +2764,34 @@
         <v>9.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
         <v>3.1</v>
@@ -2803,7 +2803,7 @@
         <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="BK9" t="n">
         <v>4.3</v>
@@ -2812,25 +2812,25 @@
         <v>170</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN9" t="n">
         <v>18</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
         <v>130</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
         <v>110</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT9" t="n">
         <v>4</v>
@@ -2848,17 +2848,17 @@
         <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G10" t="n">
         <v>14</v>
@@ -2925,10 +2925,10 @@
         <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="T10" t="n">
         <v>1.79</v>
@@ -2949,13 +2949,13 @@
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
         <v>11.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AC10" t="n">
         <v>19</v>
@@ -2976,7 +2976,7 @@
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
         <v>480</v>
@@ -3027,7 +3027,7 @@
         <v>25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
         <v>25</v>
@@ -3036,7 +3036,7 @@
         <v>95</v>
       </c>
       <c r="BC10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BD10" t="n">
         <v>38</v>
@@ -3048,7 +3048,7 @@
         <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BH10" t="n">
         <v>7</v>
@@ -3081,7 +3081,7 @@
         <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BS10" t="n">
         <v>4.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
         <v>2.44</v>
@@ -3197,7 +3197,7 @@
         <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
         <v>13</v>
@@ -3206,7 +3206,7 @@
         <v>26</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
         <v>9.4</v>
@@ -3239,10 +3239,10 @@
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>25</v>
@@ -3260,7 +3260,7 @@
         <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3284,10 +3284,10 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
@@ -3296,7 +3296,7 @@
         <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA12" t="n">
         <v>340</v>
@@ -3484,7 +3484,7 @@
         <v>32</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AJ12" t="n">
         <v>13</v>
@@ -3556,7 +3556,7 @@
         <v>5.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -3675,40 +3675,40 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="Z13" t="n">
         <v>130</v>
@@ -3717,10 +3717,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
@@ -3729,10 +3729,10 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
@@ -3747,28 +3747,28 @@
         <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.96</v>
+        <v>4.2</v>
       </c>
       <c r="AT13" t="n">
         <v>9.800000000000001</v>
@@ -3777,40 +3777,40 @@
         <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>3.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="n">
         <v>5.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
         <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
@@ -3929,19 +3929,19 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
         <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
         <v>2.44</v>
@@ -3953,10 +3953,10 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>950</v>
@@ -3974,7 +3974,7 @@
         <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
@@ -3989,16 +3989,16 @@
         <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL14" t="n">
         <v>80</v>
@@ -4007,100 +4007,100 @@
         <v>95</v>
       </c>
       <c r="AN14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO14" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV14" t="n">
         <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="AY14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6</v>
-      </c>
       <c r="BB14" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="n">
         <v>4.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL14" t="n">
         <v>130</v>
       </c>
       <c r="BM14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BN14" t="n">
         <v>12.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT14" t="n">
         <v>4.4</v>
@@ -4112,13 +4112,13 @@
         <v>9.6</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX14" t="n">
         <v>24</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
@@ -4168,46 +4168,46 @@
         <v>2.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
         <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
         <v>1.47</v>
@@ -4216,70 +4216,70 @@
         <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
         <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
@@ -4288,10 +4288,10 @@
         <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -4300,40 +4300,40 @@
         <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG15" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BH15" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG15" t="n">
+      <c r="BI15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
         <v>3.55</v>
       </c>
       <c r="BL15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM15" t="n">
         <v>5.2</v>
@@ -4345,25 +4345,25 @@
         <v>5.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ15" t="n">
         <v>4.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS15" t="n">
         <v>4.7</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU15" t="n">
         <v>4.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW15" t="n">
         <v>4.2</v>
@@ -4372,17 +4372,17 @@
         <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA15" t="n">
         <v>4.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G16" t="n">
         <v>3.35</v>
       </c>
       <c r="H16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I16" t="n">
         <v>3.15</v>
@@ -4431,7 +4431,7 @@
         <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
@@ -4467,7 +4467,7 @@
         <v>1.42</v>
       </c>
       <c r="X16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y16" t="n">
         <v>8.6</v>
@@ -4482,16 +4482,16 @@
         <v>9</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
         <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
         <v>17</v>
@@ -4500,22 +4500,22 @@
         <v>27</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ16" t="n">
         <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL16" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX16" t="n">
         <v>14.5</v>
@@ -4554,25 +4554,25 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="n">
         <v>2.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
         <v>2.82</v>
@@ -4691,7 +4691,7 @@
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
@@ -4721,31 +4721,31 @@
         <v>1.54</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
         <v>950</v>
@@ -4754,25 +4754,25 @@
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
         <v>8</v>
@@ -4781,10 +4781,10 @@
         <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4796,7 +4796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -4805,61 +4805,61 @@
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH17" t="n">
         <v>3.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BL17" t="n">
         <v>180</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ17" t="n">
         <v>4.1</v>
       </c>
       <c r="BR17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS17" t="n">
         <v>4.4</v>
@@ -4871,7 +4871,7 @@
         <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW17" t="n">
         <v>4.2</v>
@@ -4880,17 +4880,17 @@
         <v>55</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>44</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -4921,37 +4921,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G18" t="n">
         <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="n">
         <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q18" t="n">
         <v>1.48</v>
@@ -4969,7 +4969,7 @@
         <v>2.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W18" t="n">
         <v>1.37</v>
@@ -4981,13 +4981,13 @@
         <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
         <v>29</v>
       </c>
       <c r="AB18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="n">
         <v>9.800000000000001</v>
@@ -4999,7 +4999,7 @@
         <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG18" t="n">
         <v>15.5</v>
@@ -5020,13 +5020,13 @@
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP18" t="n">
         <v>18.5</v>
@@ -5083,7 +5083,7 @@
         <v>9</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BI18" t="n">
         <v>3.45</v>
@@ -5092,31 +5092,31 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BL18" t="n">
         <v>90</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BT18" t="n">
         <v>6.4</v>
@@ -5125,26 +5125,26 @@
         <v>4.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BX18" t="n">
         <v>27</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5175,28 +5175,28 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G19" t="n">
         <v>3.7</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H19" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.65</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
         <v>4.1</v>
@@ -5223,16 +5223,16 @@
         <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
         <v>14.5</v>
@@ -5244,7 +5244,7 @@
         <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5253,7 +5253,7 @@
         <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
         <v>15.5</v>
@@ -5262,10 +5262,10 @@
         <v>17.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AK19" t="n">
         <v>44</v>
@@ -5274,10 +5274,10 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
         <v>15</v>
@@ -5286,7 +5286,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
@@ -5319,13 +5319,13 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BC19" t="n">
         <v>36</v>
       </c>
       <c r="BD19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE19" t="n">
         <v>36</v>
@@ -5337,25 +5337,25 @@
         <v>13.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BL19" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO19" t="n">
         <v>5.3</v>
@@ -5364,41 +5364,41 @@
         <v>36</v>
       </c>
       <c r="BQ19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS19" t="n">
         <v>4.2</v>
       </c>
-      <c r="BR19" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BT19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BX19" t="n">
         <v>34</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ19" t="n">
         <v>29</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>1.46</v>
       </c>
       <c r="H20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I20" t="n">
         <v>8</v>
@@ -5444,7 +5444,7 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>1.2</v>
@@ -5456,7 +5456,7 @@
         <v>7.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
         <v>3.15</v>
@@ -5489,7 +5489,7 @@
         <v>42</v>
       </c>
       <c r="Z20" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA20" t="n">
         <v>210</v>
@@ -5501,10 +5501,10 @@
         <v>14</v>
       </c>
       <c r="AD20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="AF20" t="n">
         <v>12.5</v>
@@ -5513,10 +5513,10 @@
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AJ20" t="n">
         <v>14</v>
@@ -5525,28 +5525,28 @@
         <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AN20" t="n">
         <v>4.3</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>13</v>
@@ -5558,7 +5558,7 @@
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -5570,7 +5570,7 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -5582,13 +5582,13 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
         <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="n">
         <v>5.3</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
         <v>4.9</v>
@@ -5731,76 +5731,76 @@
         <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z21" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AA21" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
         <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AF21" t="n">
         <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
         <v>7.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.05</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>17.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -5824,7 +5824,7 @@
         <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
         <v>15</v>
@@ -5836,13 +5836,13 @@
         <v>19.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF21" t="n">
         <v>5.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="BH21" t="n">
         <v>5.1</v>
@@ -5854,59 +5854,59 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL21" t="n">
         <v>90</v>
       </c>
       <c r="BM21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
         <v>13</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR21" t="n">
         <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT21" t="n">
         <v>9.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV21" t="n">
         <v>36</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BX21" t="n">
         <v>40</v>
       </c>
       <c r="BY21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ21" t="n">
         <v>16</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>2.84</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H22" t="n">
         <v>2.36</v>
@@ -5949,7 +5949,7 @@
         <v>2.52</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
         <v>4.5</v>
@@ -5988,7 +5988,7 @@
         <v>1.66</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
         <v>950</v>
@@ -5997,46 +5997,46 @@
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
         <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>970</v>
@@ -6045,7 +6045,7 @@
         <v>11</v>
       </c>
       <c r="AP22" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
         <v>14</v>
@@ -6054,7 +6054,7 @@
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT22" t="n">
         <v>15.5</v>
@@ -6078,19 +6078,19 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
         <v>10.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G23" t="n">
         <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I23" t="n">
         <v>4.1</v>
@@ -6206,7 +6206,7 @@
         <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6224,28 +6224,28 @@
         <v>2.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S23" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T23" t="n">
         <v>1.46</v>
       </c>
       <c r="U23" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
         <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
         <v>29</v>
@@ -6254,7 +6254,7 @@
         <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB23" t="n">
         <v>19</v>
@@ -6290,7 +6290,7 @@
         <v>24</v>
       </c>
       <c r="AM23" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
         <v>7.8</v>
@@ -6305,10 +6305,10 @@
         <v>6.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6344,7 +6344,7 @@
         <v>17.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF23" t="n">
         <v>6.2</v>
@@ -6362,7 +6362,7 @@
         <v>9.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL23" t="n">
         <v>75</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="H24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I24" t="n">
         <v>2.34</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.44</v>
       </c>
       <c r="J24" t="n">
         <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>1.28</v>
@@ -6487,82 +6487,82 @@
         <v>2.76</v>
       </c>
       <c r="T24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
         <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
         <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL24" t="n">
         <v>50</v>
       </c>
-      <c r="AK24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>40</v>
-      </c>
       <c r="AM24" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN24" t="n">
         <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP24" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
         <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -6574,7 +6574,7 @@
         <v>8.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
         <v>16</v>
@@ -6586,7 +6586,7 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.05</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>36</v>
@@ -6598,7 +6598,7 @@
         <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.05</v>
+        <v>7.8</v>
       </c>
       <c r="BF24" t="n">
         <v>19.5</v>
@@ -6613,7 +6613,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK24" t="n">
         <v>6.6</v>
@@ -6622,53 +6622,53 @@
         <v>110</v>
       </c>
       <c r="BM24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT24" t="n">
         <v>6.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ24" t="n">
         <v>24</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J25" t="n">
         <v>4.4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>1.26</v>
@@ -6726,46 +6726,46 @@
         <v>5.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="S25" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
         <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
         <v>950</v>
       </c>
       <c r="Y25" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Z25" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
         <v>11</v>
@@ -6774,7 +6774,7 @@
         <v>950</v>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AF25" t="n">
         <v>12.5</v>
@@ -6783,28 +6783,28 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AJ25" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO25" t="n">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AP25" t="n">
         <v>18.5</v>
@@ -6813,13 +6813,13 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU25" t="n">
         <v>8.4</v>
@@ -6828,7 +6828,7 @@
         <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -6840,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>12.5</v>
@@ -6849,22 +6849,22 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BF25" t="n">
         <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH25" t="n">
         <v>4.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ25" t="n">
         <v>11</v>
@@ -6876,7 +6876,7 @@
         <v>100</v>
       </c>
       <c r="BM25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN25" t="n">
         <v>5.2</v>
@@ -6894,7 +6894,7 @@
         <v>24</v>
       </c>
       <c r="BS25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT25" t="n">
         <v>10.5</v>
@@ -6906,7 +6906,7 @@
         <v>44</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX25" t="n">
         <v>46</v>
@@ -6915,14 +6915,14 @@
         <v>5.9</v>
       </c>
       <c r="BZ25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA25" t="n">
         <v>4.7</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -6953,25 +6953,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="I26" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J26" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
         <v>1.04</v>
@@ -6986,7 +6986,7 @@
         <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R26" t="n">
         <v>1.56</v>
@@ -6995,70 +6995,70 @@
         <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U26" t="n">
         <v>2.52</v>
       </c>
       <c r="V26" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
       </c>
       <c r="AF26" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="AK26" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AM26" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AO26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
         <v>17</v>
@@ -7079,7 +7079,7 @@
         <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
@@ -7088,7 +7088,7 @@
         <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
@@ -7097,7 +7097,7 @@
         <v>20</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
         <v>22</v>
@@ -7130,53 +7130,53 @@
         <v>95</v>
       </c>
       <c r="BM26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BN26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP26" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BQ26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BR26" t="n">
         <v>36</v>
       </c>
       <c r="BS26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV26" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW26" t="n">
         <v>3.65</v>
       </c>
       <c r="BX26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BZ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA26" t="n">
         <v>3.75</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>3.65</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="I27" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="J27" t="n">
         <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>1.19</v>
@@ -7255,22 +7255,22 @@
         <v>2.76</v>
       </c>
       <c r="V27" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AA27" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AB27" t="n">
         <v>950</v>
@@ -7279,34 +7279,34 @@
         <v>12.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AK27" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL27" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
         <v>23</v>
@@ -7315,37 +7315,37 @@
         <v>7</v>
       </c>
       <c r="AP27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX27" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AY27" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="BA27" t="n">
         <v>6.8</v>
@@ -7354,13 +7354,13 @@
         <v>8.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
         <v>6.6</v>
@@ -7372,7 +7372,7 @@
         <v>6.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7467,16 +7467,16 @@
         <v>2.22</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I28" t="n">
         <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -7494,7 +7494,7 @@
         <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
         <v>1.24</v>
@@ -7509,118 +7509,118 @@
         <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W28" t="n">
         <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD28" t="n">
         <v>950</v>
       </c>
       <c r="AE28" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH28" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU28" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AV28" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.3</v>
+        <v>2.86</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.86</v>
+        <v>2.92</v>
       </c>
       <c r="BH28" t="n">
         <v>3.35</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G29" t="n">
         <v>1.75</v>
@@ -7760,7 +7760,7 @@
         <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V29" t="n">
         <v>1.16</v>
@@ -7769,19 +7769,19 @@
         <v>2.32</v>
       </c>
       <c r="X29" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z29" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC29" t="n">
         <v>9.6</v>
@@ -7790,49 +7790,49 @@
         <v>950</v>
       </c>
       <c r="AE29" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI29" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN29" t="n">
         <v>55</v>
       </c>
-      <c r="AM29" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>970</v>
-      </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AT29" t="n">
         <v>5.8</v>
@@ -7844,31 +7844,31 @@
         <v>19.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BF29" t="n">
         <v>12</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I30" t="n">
         <v>1.72</v>
@@ -7987,7 +7987,7 @@
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -7999,7 +7999,7 @@
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
@@ -8026,52 +8026,52 @@
         <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE30" t="n">
         <v>19.5</v>
       </c>
-      <c r="AC30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>970</v>
-      </c>
       <c r="AF30" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AG30" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AH30" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AI30" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AK30" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="AL30" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AN30" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AO30" t="n">
         <v>12</v>
@@ -8089,19 +8089,19 @@
         <v>14.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU30" t="n">
         <v>8</v>
       </c>
       <c r="AV30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY30" t="n">
         <v>18.5</v>
@@ -8110,22 +8110,22 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG30" t="n">
         <v>10</v>
@@ -8143,7 +8143,7 @@
         <v>3.95</v>
       </c>
       <c r="BL30" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BM30" t="n">
         <v>5.6</v>
@@ -8152,7 +8152,7 @@
         <v>11</v>
       </c>
       <c r="BO30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP30" t="n">
         <v>65</v>
@@ -8164,13 +8164,13 @@
         <v>75</v>
       </c>
       <c r="BS30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT30" t="n">
         <v>4.7</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BV30" t="n">
         <v>13.5</v>
@@ -8185,14 +8185,14 @@
         <v>4.9</v>
       </c>
       <c r="BZ30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -8226,19 +8226,19 @@
         <v>1.29</v>
       </c>
       <c r="G31" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H31" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.42</v>
@@ -8247,43 +8247,43 @@
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
         <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
         <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X31" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Z31" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
         <v>6.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
@@ -8310,22 +8310,22 @@
         <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK31" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL31" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AM31" t="n">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="AN31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
@@ -8340,7 +8340,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT31" t="n">
         <v>5.5</v>
@@ -8349,40 +8349,40 @@
         <v>10.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA31" t="n">
         <v>9.4</v>
       </c>
-      <c r="AX31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ31" t="n">
+      <c r="BB31" t="n">
         <v>8</v>
       </c>
-      <c r="BA31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC31" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF31" t="n">
         <v>6.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH31" t="n">
         <v>3.75</v>
@@ -8412,7 +8412,7 @@
         <v>8.4</v>
       </c>
       <c r="BQ31" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="BR31" t="n">
         <v>36</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -8480,10 +8480,10 @@
         <v>6.4</v>
       </c>
       <c r="G32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H32" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="I32" t="n">
         <v>1.55</v>
@@ -8525,7 +8525,7 @@
         <v>2.14</v>
       </c>
       <c r="V32" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="W32" t="n">
         <v>1.15</v>
@@ -8543,7 +8543,7 @@
         <v>16.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AC32" t="n">
         <v>12</v>
@@ -8555,31 +8555,31 @@
         <v>18</v>
       </c>
       <c r="AF32" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AG32" t="n">
         <v>32</v>
       </c>
       <c r="AH32" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AI32" t="n">
         <v>36</v>
       </c>
       <c r="AJ32" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK32" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AL32" t="n">
-        <v>75</v>
+        <v>390</v>
       </c>
       <c r="AM32" t="n">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="AN32" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AO32" t="n">
         <v>6.8</v>
@@ -8618,22 +8618,22 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BB32" t="n">
         <v>7</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD32" t="n">
         <v>6.6</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG32" t="n">
         <v>5.1</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8761,7 +8761,7 @@
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1.52</v>
@@ -8776,13 +8776,13 @@
         <v>1.52</v>
       </c>
       <c r="U33" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V33" t="n">
         <v>2.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X33" t="n">
         <v>28</v>
@@ -8791,13 +8791,13 @@
         <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
         <v>24</v>
       </c>
       <c r="AB33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC33" t="n">
         <v>10.5</v>
@@ -8812,22 +8812,22 @@
         <v>36</v>
       </c>
       <c r="AG33" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ33" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="n">
         <v>55</v>
@@ -8839,10 +8839,10 @@
         <v>8</v>
       </c>
       <c r="AP33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR33" t="n">
         <v>14</v>
@@ -8863,7 +8863,7 @@
         <v>15.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AY33" t="n">
         <v>15</v>
@@ -8872,7 +8872,7 @@
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BB33" t="n">
         <v>34</v>
@@ -8881,7 +8881,7 @@
         <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BE33" t="n">
         <v>44</v>
@@ -8893,7 +8893,7 @@
         <v>7.2</v>
       </c>
       <c r="BH33" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BI33" t="n">
         <v>3.8</v>
@@ -8902,13 +8902,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BL33" t="n">
         <v>80</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BN33" t="n">
         <v>8.800000000000001</v>
@@ -8920,13 +8920,13 @@
         <v>29</v>
       </c>
       <c r="BQ33" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR33" t="n">
         <v>34</v>
       </c>
       <c r="BS33" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BT33" t="n">
         <v>6</v>
@@ -8938,23 +8938,23 @@
         <v>14.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BX33" t="n">
         <v>24</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BZ33" t="n">
         <v>15.5</v>
       </c>
       <c r="CA33" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -8988,19 +8988,19 @@
         <v>6.2</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="I34" t="n">
         <v>1.55</v>
       </c>
       <c r="J34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K34" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L34" t="n">
         <v>1.2</v>
@@ -9015,7 +9015,7 @@
         <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
@@ -9036,16 +9036,16 @@
         <v>2.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
         <v>17</v>
@@ -9063,7 +9063,7 @@
         <v>15</v>
       </c>
       <c r="AF34" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="AG34" t="n">
         <v>950</v>
@@ -9072,28 +9072,28 @@
         <v>19.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AJ34" t="n">
         <v>170</v>
       </c>
       <c r="AK34" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AL34" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="AM34" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="AN34" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AO34" t="n">
         <v>6.4</v>
       </c>
       <c r="AP34" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>10</v>
@@ -9105,7 +9105,7 @@
         <v>12.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU34" t="n">
         <v>11</v>
@@ -9129,19 +9129,19 @@
         <v>20</v>
       </c>
       <c r="BB34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC34" t="n">
         <v>7</v>
       </c>
-      <c r="BC34" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG34" t="n">
         <v>4.6</v>
@@ -9186,7 +9186,7 @@
         <v>5.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BV34" t="n">
         <v>11</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H35" t="n">
         <v>6.8</v>
@@ -9251,13 +9251,13 @@
         <v>9.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>4.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -9266,7 +9266,7 @@
         <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P35" t="n">
         <v>1.96</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="Z35" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AA35" t="n">
         <v>280</v>
@@ -9308,10 +9308,10 @@
         <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE35" t="n">
         <v>140</v>
@@ -9320,7 +9320,7 @@
         <v>10.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH35" t="n">
         <v>28</v>
@@ -9353,10 +9353,10 @@
         <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT35" t="n">
         <v>6.8</v>
@@ -9368,7 +9368,7 @@
         <v>20</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX35" t="n">
         <v>6.8</v>
@@ -9380,7 +9380,7 @@
         <v>19.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB35" t="n">
         <v>10</v>
@@ -9389,34 +9389,34 @@
         <v>12.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF35" t="n">
         <v>6.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH35" t="n">
         <v>4.1</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ35" t="n">
         <v>13.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BL35" t="n">
         <v>190</v>
       </c>
       <c r="BM35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN35" t="n">
         <v>4.7</v>
@@ -9428,10 +9428,10 @@
         <v>12</v>
       </c>
       <c r="BQ35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BR35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS35" t="n">
         <v>4.2</v>
@@ -9440,13 +9440,13 @@
         <v>12.5</v>
       </c>
       <c r="BU35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV35" t="n">
         <v>80</v>
       </c>
       <c r="BW35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX35" t="n">
         <v>85</v>
@@ -9455,14 +9455,14 @@
         <v>4.6</v>
       </c>
       <c r="BZ35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA35" t="n">
         <v>4</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>1.83</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H36" t="n">
         <v>4.6</v>
@@ -9535,34 +9535,34 @@
         <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U36" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
         <v>2.16</v>
       </c>
       <c r="X36" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y36" t="n">
         <v>21</v>
       </c>
       <c r="Z36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA36" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB36" t="n">
         <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD36" t="n">
         <v>18.5</v>
@@ -9586,7 +9586,7 @@
         <v>20</v>
       </c>
       <c r="AK36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL36" t="n">
         <v>28</v>
@@ -9604,19 +9604,19 @@
         <v>17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR36" t="n">
         <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV36" t="n">
         <v>16</v>
@@ -9634,10 +9634,10 @@
         <v>15.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC36" t="n">
         <v>16</v>
@@ -9646,13 +9646,13 @@
         <v>26</v>
       </c>
       <c r="BE36" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BF36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH36" t="n">
         <v>4.4</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G37" t="n">
         <v>2.06</v>
@@ -9762,10 +9762,10 @@
         <v>3.35</v>
       </c>
       <c r="K37" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9801,16 +9801,16 @@
         <v>1.96</v>
       </c>
       <c r="X37" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y37" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z37" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA37" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB37" t="n">
         <v>9.800000000000001</v>
@@ -9819,52 +9819,52 @@
         <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE37" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF37" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH37" t="n">
         <v>950</v>
       </c>
       <c r="AI37" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ37" t="n">
-        <v>28</v>
+        <v>900</v>
       </c>
       <c r="AK37" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL37" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM37" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN37" t="n">
         <v>20</v>
       </c>
       <c r="AO37" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP37" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT37" t="n">
         <v>6</v>
@@ -9873,10 +9873,10 @@
         <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AX37" t="n">
         <v>9.800000000000001</v>
@@ -9885,28 +9885,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BC37" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BH37" t="n">
         <v>3.7</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -10001,19 +10001,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G38" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
         <v>3.9</v>
@@ -10022,19 +10022,19 @@
         <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O38" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="P38" t="n">
         <v>1.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R38" t="n">
         <v>1.23</v>
@@ -10043,7 +10043,7 @@
         <v>4.6</v>
       </c>
       <c r="T38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
         <v>1.73</v>
@@ -10052,10 +10052,10 @@
         <v>1.16</v>
       </c>
       <c r="W38" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="X38" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y38" t="n">
         <v>19</v>
@@ -10064,7 +10064,7 @@
         <v>60</v>
       </c>
       <c r="AA38" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AB38" t="n">
         <v>7.4</v>
@@ -10076,7 +10076,7 @@
         <v>30</v>
       </c>
       <c r="AE38" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AF38" t="n">
         <v>10.5</v>
@@ -10088,7 +10088,7 @@
         <v>32</v>
       </c>
       <c r="AI38" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ38" t="n">
         <v>21</v>
@@ -10097,70 +10097,70 @@
         <v>26</v>
       </c>
       <c r="AL38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM38" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AN38" t="n">
         <v>18.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AP38" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV38" t="n">
         <v>19.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX38" t="n">
         <v>7.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BA38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD38" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB38" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>5</v>
-      </c>
       <c r="BE38" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF38" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH38" t="n">
         <v>3.3</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -10258,19 +10258,19 @@
         <v>2.44</v>
       </c>
       <c r="G39" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I39" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K39" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.51</v>
@@ -10279,7 +10279,7 @@
         <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
         <v>1.45</v>
@@ -10306,19 +10306,19 @@
         <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X39" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y39" t="n">
         <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA39" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AB39" t="n">
         <v>10</v>
@@ -10330,7 +10330,7 @@
         <v>970</v>
       </c>
       <c r="AE39" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF39" t="n">
         <v>970</v>
@@ -10342,25 +10342,25 @@
         <v>950</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ39" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AK39" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL39" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN39" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO39" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP39" t="n">
         <v>7.8</v>
@@ -10369,13 +10369,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AU39" t="n">
         <v>5.6</v>
@@ -10384,37 +10384,37 @@
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AY39" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BB39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD39" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE39" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH39" t="n">
         <v>3.25</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -10509,19 +10509,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G40" t="n">
         <v>1.62</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I40" t="n">
         <v>11.5</v>
       </c>
       <c r="J40" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K40" t="n">
         <v>4.5</v>
@@ -10563,13 +10563,13 @@
         <v>2.6</v>
       </c>
       <c r="X40" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y40" t="n">
         <v>950</v>
       </c>
       <c r="Z40" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
@@ -10599,46 +10599,46 @@
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AK40" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AL40" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT40" t="n">
         <v>4.7</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX40" t="n">
         <v>5.9</v>
@@ -10647,28 +10647,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB40" t="n">
         <v>10</v>
       </c>
       <c r="BC40" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF40" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH40" t="n">
         <v>3.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -10772,7 +10772,7 @@
         <v>1.72</v>
       </c>
       <c r="I41" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="J41" t="n">
         <v>3.95</v>
@@ -10781,34 +10781,34 @@
         <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M41" t="n">
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="T41" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V41" t="n">
         <v>2.36</v>
@@ -10820,25 +10820,25 @@
         <v>12.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA41" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB41" t="n">
         <v>16.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD41" t="n">
         <v>10</v>
       </c>
       <c r="AE41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF41" t="n">
         <v>44</v>
@@ -10847,46 +10847,46 @@
         <v>24</v>
       </c>
       <c r="AH41" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI41" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ41" t="n">
         <v>190</v>
       </c>
       <c r="AK41" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL41" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM41" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AO41" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU41" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>8.4</v>
       </c>
       <c r="AV41" t="n">
         <v>9.800000000000001</v>
@@ -10895,16 +10895,16 @@
         <v>18.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY41" t="n">
         <v>22</v>
       </c>
       <c r="AZ41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB41" t="n">
         <v>140</v>
@@ -10913,7 +10913,7 @@
         <v>80</v>
       </c>
       <c r="BD41" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BE41" t="n">
         <v>110</v>
@@ -10922,19 +10922,19 @@
         <v>120</v>
       </c>
       <c r="BG41" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BJ41" t="n">
         <v>11.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL41" t="n">
         <v>190</v>
@@ -10949,16 +10949,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BP41" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BQ41" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BR41" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BS41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BT41" t="n">
         <v>4.1</v>
@@ -10973,7 +10973,7 @@
         <v>10.5</v>
       </c>
       <c r="BX41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY41" t="n">
         <v>11</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -11017,28 +11017,28 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G42" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H42" t="n">
         <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K42" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
         <v>1.42</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N42" t="n">
         <v>3.05</v>
@@ -11050,7 +11050,7 @@
         <v>1.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R42" t="n">
         <v>1.26</v>
@@ -11059,94 +11059,94 @@
         <v>4.3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U42" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V42" t="n">
         <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" t="n">
         <v>970</v>
       </c>
       <c r="Z42" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA42" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
         <v>970</v>
       </c>
       <c r="AC42" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD42" t="n">
         <v>950</v>
       </c>
       <c r="AE42" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF42" t="n">
         <v>970</v>
       </c>
       <c r="AG42" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH42" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI42" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AJ42" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AK42" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AL42" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM42" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO42" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ42" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AT42" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AX42" t="n">
         <v>9.199999999999999</v>
@@ -11155,28 +11155,28 @@
         <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="BC42" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="BH42" t="n">
         <v>3.35</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G43" t="n">
         <v>1.37</v>
@@ -11280,13 +11280,13 @@
         <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J43" t="n">
         <v>5.1</v>
       </c>
       <c r="K43" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
         <v>1.32</v>
@@ -11295,34 +11295,34 @@
         <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O43" t="n">
         <v>1.3</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
         <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V43" t="n">
         <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="X43" t="n">
         <v>970</v>
@@ -11403,7 +11403,7 @@
         <v>3.45</v>
       </c>
       <c r="AX43" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY43" t="n">
         <v>4.4</v>
@@ -11448,7 +11448,7 @@
         <v>260</v>
       </c>
       <c r="BM43" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN43" t="n">
         <v>3.95</v>
@@ -11466,7 +11466,7 @@
         <v>34</v>
       </c>
       <c r="BS43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT43" t="n">
         <v>17.5</v>
@@ -11475,26 +11475,26 @@
         <v>4.5</v>
       </c>
       <c r="BV43" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BW43" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX43" t="n">
         <v>140</v>
       </c>
       <c r="BY43" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ43" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA43" t="n">
         <v>4.4</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -11528,16 +11528,16 @@
         <v>1.46</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="I44" t="n">
         <v>11.5</v>
       </c>
       <c r="J44" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K44" t="n">
         <v>4.7</v>
@@ -11549,7 +11549,7 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.41</v>
@@ -11576,7 +11576,7 @@
         <v>1.1</v>
       </c>
       <c r="W44" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X44" t="n">
         <v>12</v>
@@ -11588,7 +11588,7 @@
         <v>95</v>
       </c>
       <c r="AA44" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AB44" t="n">
         <v>6.4</v>
@@ -11606,7 +11606,7 @@
         <v>7.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH44" t="n">
         <v>38</v>
@@ -11618,31 +11618,31 @@
         <v>12.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL44" t="n">
         <v>65</v>
       </c>
       <c r="AM44" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="AN44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO44" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AP44" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR44" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT44" t="n">
         <v>5.5</v>
@@ -11654,7 +11654,7 @@
         <v>32</v>
       </c>
       <c r="AW44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX44" t="n">
         <v>6.4</v>
@@ -11666,7 +11666,7 @@
         <v>30</v>
       </c>
       <c r="BA44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB44" t="n">
         <v>11</v>
@@ -11675,28 +11675,28 @@
         <v>17.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE44" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG44" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH44" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ44" t="n">
         <v>17</v>
       </c>
       <c r="BK44" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BL44" t="n">
         <v>340</v>
@@ -11711,7 +11711,7 @@
         <v>2.82</v>
       </c>
       <c r="BP44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ44" t="n">
         <v>3.5</v>
@@ -11726,29 +11726,29 @@
         <v>16.5</v>
       </c>
       <c r="BU44" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="BV44" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BW44" t="n">
         <v>4.9</v>
       </c>
       <c r="BX44" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BY44" t="n">
         <v>4.9</v>
       </c>
       <c r="BZ44" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA44" t="n">
         <v>4.3</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H45" t="n">
         <v>4.7</v>
@@ -11794,7 +11794,7 @@
         <v>3.4</v>
       </c>
       <c r="K45" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L45" t="n">
         <v>1.42</v>
@@ -11812,7 +11812,7 @@
         <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R45" t="n">
         <v>1.24</v>
@@ -11830,7 +11830,7 @@
         <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X45" t="n">
         <v>12</v>
@@ -11917,7 +11917,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA45" t="n">
         <v>6</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>1.76</v>
       </c>
       <c r="G46" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H46" t="n">
         <v>5</v>
@@ -12048,7 +12048,7 @@
         <v>3.7</v>
       </c>
       <c r="K46" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L46" t="n">
         <v>1.35</v>
@@ -12084,7 +12084,7 @@
         <v>1.21</v>
       </c>
       <c r="W46" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X46" t="n">
         <v>17</v>
@@ -12114,7 +12114,7 @@
         <v>12.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH46" t="n">
         <v>24</v>
@@ -12147,10 +12147,10 @@
         <v>15</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT46" t="n">
         <v>7.4</v>
@@ -12162,7 +12162,7 @@
         <v>17.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX46" t="n">
         <v>9.199999999999999</v>
@@ -12174,7 +12174,7 @@
         <v>17.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB46" t="n">
         <v>16</v>
@@ -12183,16 +12183,16 @@
         <v>16</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF46" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH46" t="n">
         <v>3.85</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G47" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H47" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I47" t="n">
         <v>3.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K47" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
         <v>1.41</v>
@@ -12311,22 +12311,22 @@
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
         <v>1.44</v>
       </c>
       <c r="P47" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q47" t="n">
         <v>2.28</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S47" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T47" t="n">
         <v>1.92</v>
@@ -12338,7 +12338,7 @@
         <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X47" t="n">
         <v>13</v>
@@ -12383,7 +12383,7 @@
         <v>38</v>
       </c>
       <c r="AL47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM47" t="n">
         <v>160</v>
@@ -12404,7 +12404,7 @@
         <v>19</v>
       </c>
       <c r="AS47" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT47" t="n">
         <v>7.8</v>
@@ -12416,7 +12416,7 @@
         <v>12.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX47" t="n">
         <v>13.5</v>
@@ -12428,16 +12428,16 @@
         <v>17</v>
       </c>
       <c r="BA47" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB47" t="n">
         <v>5.9</v>
       </c>
       <c r="BC47" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE47" t="n">
         <v>6.4</v>
@@ -12458,49 +12458,49 @@
         <v>12.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL47" t="n">
         <v>190</v>
       </c>
       <c r="BM47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN47" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO47" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BP47" t="n">
         <v>25</v>
       </c>
       <c r="BQ47" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS47" t="n">
         <v>4.4</v>
       </c>
       <c r="BT47" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU47" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV47" t="n">
         <v>36</v>
       </c>
       <c r="BW47" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX47" t="n">
         <v>55</v>
       </c>
       <c r="BY47" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ47" t="n">
         <v>46</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
         <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
@@ -881,85 +881,85 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.78</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
         <v>36</v>
@@ -968,25 +968,25 @@
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,89 +998,89 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO2" t="n">
         <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
         <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BW2" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY2" t="n">
         <v>36</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1138,94 +1138,94 @@
         <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
         <v>2.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
         <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V3" t="n">
         <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z3" t="n">
         <v>60</v>
       </c>
-      <c r="Z3" t="n">
-        <v>70</v>
-      </c>
       <c r="AA3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
         <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>230</v>
+        <v>44</v>
       </c>
       <c r="AP3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AR3" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1240,37 +1240,37 @@
         <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB3" t="n">
         <v>15</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1285,7 +1285,7 @@
         <v>5</v>
       </c>
       <c r="BL3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BM3" t="n">
         <v>9.199999999999999</v>
@@ -1300,7 +1300,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR3" t="n">
         <v>18.5</v>
@@ -1324,7 +1324,7 @@
         <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
         <v>2.7</v>
@@ -1404,7 +1404,7 @@
         <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
         <v>1.49</v>
@@ -1425,25 +1425,25 @@
         <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="n">
         <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG4" t="n">
         <v>14.5</v>
@@ -1452,7 +1452,7 @@
         <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
@@ -1461,7 +1461,7 @@
         <v>44</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
         <v>60</v>
@@ -1479,10 +1479,10 @@
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>17.5</v>
@@ -1497,28 +1497,28 @@
         <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY4" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BF4" t="n">
         <v>15.5</v>
@@ -1530,7 +1530,7 @@
         <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
@@ -1572,23 +1572,23 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX4" t="n">
         <v>26</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA4" t="n">
         <v>4.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1619,55 +1619,55 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
         <v>1.54</v>
@@ -1679,7 +1679,7 @@
         <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
         <v>44</v>
@@ -1688,7 +1688,7 @@
         <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
@@ -1697,7 +1697,7 @@
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
@@ -1709,7 +1709,7 @@
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK5" t="n">
         <v>32</v>
@@ -1724,22 +1724,22 @@
         <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
@@ -1748,25 +1748,25 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY5" t="n">
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>25</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BD5" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1873,217 +1873,217 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB6" t="n">
         <v>24</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>20</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="AK6" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.35</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.55</v>
+        <v>18.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.7</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="BM6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
         <v>4.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY6" t="n">
         <v>4.3</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
         <v>3.8</v>
@@ -2139,37 +2139,37 @@
         <v>2.16</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
         <v>2.2</v>
@@ -2181,19 +2181,19 @@
         <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -2202,13 +2202,13 @@
         <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
@@ -2217,7 +2217,7 @@
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AK7" t="n">
         <v>110</v>
@@ -2232,7 +2232,7 @@
         <v>210</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -2241,7 +2241,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
         <v>17</v>
@@ -2256,7 +2256,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>18</v>
@@ -2268,7 +2268,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
         <v>34</v>
@@ -2286,43 +2286,43 @@
         <v>25</v>
       </c>
       <c r="BG7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BL7" t="n">
         <v>130</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO7" t="n">
         <v>5.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT7" t="n">
         <v>5.6</v>
@@ -2334,23 +2334,23 @@
         <v>17.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>28</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
@@ -2396,7 +2396,7 @@
         <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.38</v>
@@ -2414,13 +2414,13 @@
         <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -2435,7 +2435,7 @@
         <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
@@ -2450,7 +2450,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2489,58 +2489,58 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AV8" t="n">
         <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BD8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>4.5</v>
@@ -2692,7 +2692,7 @@
         <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
         <v>14.5</v>
@@ -2704,10 +2704,10 @@
         <v>950</v>
       </c>
       <c r="AC9" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE9" t="n">
         <v>970</v>
@@ -2755,7 +2755,7 @@
         <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
@@ -2767,31 +2767,31 @@
         <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>7.2</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG9" t="n">
         <v>3.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2901,10 +2901,10 @@
         <v>1.27</v>
       </c>
       <c r="J10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
         <v>1.16</v>
@@ -2913,25 +2913,25 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
         <v>1.35</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
         <v>1.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
         <v>2.16</v>
@@ -2958,10 +2958,10 @@
         <v>65</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>13</v>
@@ -2970,13 +2970,13 @@
         <v>150</v>
       </c>
       <c r="AG10" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
         <v>480</v>
@@ -2985,16 +2985,16 @@
         <v>180</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN10" t="n">
         <v>150</v>
       </c>
       <c r="AO10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AP10" t="n">
         <v>27</v>
@@ -3009,19 +3009,19 @@
         <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AU10" t="n">
         <v>16.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
         <v>11.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AY10" t="n">
         <v>25</v>
@@ -3033,10 +3033,10 @@
         <v>25</v>
       </c>
       <c r="BB10" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BC10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BD10" t="n">
         <v>38</v>
@@ -3048,7 +3048,7 @@
         <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BH10" t="n">
         <v>7</v>
@@ -3060,7 +3060,7 @@
         <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL10" t="n">
         <v>120</v>
@@ -3069,7 +3069,7 @@
         <v>4.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BO10" t="n">
         <v>3.75</v>
@@ -3078,7 +3078,7 @@
         <v>95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR10" t="n">
         <v>75</v>
@@ -3102,17 +3102,17 @@
         <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>8.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3176,13 +3176,13 @@
         <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
         <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
         <v>1.84</v>
@@ -3203,13 +3203,13 @@
         <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
         <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
@@ -3221,7 +3221,7 @@
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -3230,19 +3230,19 @@
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
         <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>25</v>
@@ -3260,7 +3260,7 @@
         <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3284,10 +3284,10 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
@@ -3296,7 +3296,7 @@
         <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3475,7 +3475,7 @@
         <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -3562,65 +3562,65 @@
         <v>4.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="BL12" t="n">
         <v>180</v>
       </c>
       <c r="BM12" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BO12" t="n">
         <v>3.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="BR12" t="n">
         <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BV12" t="n">
         <v>95</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
         <v>90</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>1.29</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="H13" t="n">
         <v>10.5</v>
       </c>
       <c r="I13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -3669,10 +3669,10 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
         <v>6.2</v>
@@ -3702,7 +3702,7 @@
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3759,13 +3759,13 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS13" t="n">
         <v>4.2</v>
@@ -3774,43 +3774,43 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
         <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC13" t="n">
         <v>6</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
         <v>3.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="n">
         <v>5.4</v>
@@ -3840,7 +3840,7 @@
         <v>8.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="BR13" t="n">
         <v>24</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1.56</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
         <v>5.3</v>
@@ -3953,19 +3953,19 @@
         <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
         <v>970</v>
@@ -3983,13 +3983,13 @@
         <v>970</v>
       </c>
       <c r="AF14" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AG14" t="n">
         <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -3998,10 +3998,10 @@
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="n">
         <v>95</v>
@@ -4013,22 +4013,22 @@
         <v>6.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS14" t="n">
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV14" t="n">
         <v>7.6</v>
@@ -4037,31 +4037,31 @@
         <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
         <v>6.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
         <v>4.7</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
         <v>2.52</v>
@@ -4201,13 +4201,13 @@
         <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
         <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>1.47</v>
@@ -4267,7 +4267,7 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>8.4</v>
@@ -4276,10 +4276,10 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX15" t="n">
         <v>7</v>
@@ -4300,22 +4300,22 @@
         <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>7.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG15" t="n">
         <v>5.3</v>
@@ -4330,7 +4330,7 @@
         <v>9.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL15" t="n">
         <v>80</v>
@@ -4363,7 +4363,7 @@
         <v>4.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW15" t="n">
         <v>4.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
         <v>14.5</v>
@@ -4560,7 +4560,7 @@
         <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>7</v>
@@ -4569,7 +4569,7 @@
         <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
         <v>8.4</v>
@@ -4590,7 +4590,7 @@
         <v>250</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BN16" t="n">
         <v>6.8</v>
@@ -4623,7 +4623,7 @@
         <v>5.1</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY16" t="n">
         <v>5.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4667,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J17" t="n">
         <v>2.94</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
         <v>1.77</v>
@@ -4718,10 +4718,10 @@
         <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
         <v>19.5</v>
@@ -4733,7 +4733,7 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>13</v>
@@ -4757,7 +4757,7 @@
         <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>500</v>
@@ -4775,16 +4775,16 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4796,7 +4796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -4808,89 +4808,89 @@
         <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>2.74</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
         <v>7.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL17" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="BV17" t="n">
         <v>34</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX17" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>55</v>
       </c>
-      <c r="BY17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>44</v>
-      </c>
       <c r="CA17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4930,10 +4930,10 @@
         <v>2.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
@@ -4942,7 +4942,7 @@
         <v>1.23</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
         <v>5.2</v>
@@ -4951,19 +4951,19 @@
         <v>1.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
         <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="U18" t="n">
         <v>2.56</v>
@@ -4978,10 +4978,10 @@
         <v>28</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA18" t="n">
         <v>29</v>
@@ -4990,28 +4990,28 @@
         <v>20</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="n">
         <v>29</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
       </c>
       <c r="AI18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK18" t="n">
         <v>36</v>
@@ -5020,13 +5020,13 @@
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
         <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP18" t="n">
         <v>18.5</v>
@@ -5053,7 +5053,7 @@
         <v>17.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -5062,10 +5062,10 @@
         <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
@@ -5092,13 +5092,13 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BL18" t="n">
         <v>90</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BN18" t="n">
         <v>8.4</v>
@@ -5110,13 +5110,13 @@
         <v>28</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BT18" t="n">
         <v>6.4</v>
@@ -5125,7 +5125,7 @@
         <v>4.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BW18" t="n">
         <v>3.65</v>
@@ -5134,17 +5134,17 @@
         <v>27</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5187,64 +5187,64 @@
         <v>2.24</v>
       </c>
       <c r="J19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.39</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W19" t="n">
         <v>1.37</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
         <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AB19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5253,52 +5253,52 @@
         <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL19" t="n">
         <v>500</v>
       </c>
-      <c r="AK19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>55</v>
-      </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
         <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.6</v>
       </c>
       <c r="AR19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -5331,31 +5331,31 @@
         <v>36</v>
       </c>
       <c r="BF19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BL19" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO19" t="n">
         <v>5.3</v>
@@ -5364,13 +5364,13 @@
         <v>36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BR19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BT19" t="n">
         <v>5.9</v>
@@ -5379,26 +5379,26 @@
         <v>3.85</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BX19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BZ19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5432,13 +5432,13 @@
         <v>1.43</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
         <v>7.4</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>5.5</v>
@@ -5480,7 +5480,7 @@
         <v>1.14</v>
       </c>
       <c r="W20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X20" t="n">
         <v>40</v>
@@ -5540,7 +5540,7 @@
         <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
         <v>12</v>
@@ -5585,13 +5585,13 @@
         <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
         <v>11.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BI20" t="n">
         <v>4.2</v>
@@ -5600,13 +5600,13 @@
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BL20" t="n">
         <v>90</v>
       </c>
       <c r="BM20" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BN20" t="n">
         <v>5.1</v>
@@ -5618,41 +5618,41 @@
         <v>9.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BR20" t="n">
         <v>21</v>
       </c>
       <c r="BS20" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BT20" t="n">
         <v>13</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BV20" t="n">
         <v>55</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BX20" t="n">
         <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ20" t="n">
         <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>1.85</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
         <v>4.8</v>
@@ -5698,7 +5698,7 @@
         <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.24</v>
@@ -5728,7 +5728,7 @@
         <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V21" t="n">
         <v>1.26</v>
@@ -5770,7 +5770,7 @@
         <v>17.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ21" t="n">
         <v>21</v>
@@ -5800,7 +5800,7 @@
         <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5842,7 +5842,7 @@
         <v>5.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="n">
         <v>5.1</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H22" t="n">
         <v>2.36</v>
       </c>
       <c r="I22" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
         <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
@@ -5985,25 +5985,25 @@
         <v>2.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X22" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB22" t="n">
         <v>500</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>950</v>
       </c>
       <c r="AC22" t="n">
         <v>11.5</v>
@@ -6018,10 +6018,10 @@
         <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
         <v>500</v>
@@ -6033,19 +6033,19 @@
         <v>500</v>
       </c>
       <c r="AL22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN22" t="n">
         <v>500</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>970</v>
       </c>
       <c r="AO22" t="n">
         <v>11</v>
       </c>
       <c r="AP22" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>14</v>
@@ -6078,16 +6078,16 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
         <v>7.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BE22" t="n">
         <v>7.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
         <v>4.1</v>
@@ -6221,7 +6221,7 @@
         <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q23" t="n">
         <v>1.39</v>
@@ -6263,7 +6263,7 @@
         <v>12</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
@@ -6272,7 +6272,7 @@
         <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>15.5</v>
@@ -6281,7 +6281,7 @@
         <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>18</v>
@@ -6293,22 +6293,22 @@
         <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO23" t="n">
         <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6317,10 +6317,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AX23" t="n">
         <v>12</v>
@@ -6332,7 +6332,7 @@
         <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -6344,7 +6344,7 @@
         <v>17.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF23" t="n">
         <v>6.2</v>
@@ -6356,7 +6356,7 @@
         <v>5.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.6</v>
@@ -6368,7 +6368,7 @@
         <v>75</v>
       </c>
       <c r="BM23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BN23" t="n">
         <v>6.2</v>
@@ -6386,13 +6386,13 @@
         <v>23</v>
       </c>
       <c r="BS23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="BV23" t="n">
         <v>28</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6448,100 +6448,100 @@
         <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA24" t="n">
         <v>32</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI24" t="n">
         <v>75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AK24" t="n">
         <v>75</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AM24" t="n">
         <v>500</v>
@@ -6553,19 +6553,19 @@
         <v>15</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
         <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
         <v>6.6</v>
@@ -6574,19 +6574,19 @@
         <v>8.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX24" t="n">
         <v>16</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BB24" t="n">
         <v>36</v>
@@ -6610,13 +6610,13 @@
         <v>4.6</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.6</v>
+        <v>3.25</v>
       </c>
       <c r="BL24" t="n">
         <v>110</v>
@@ -6625,31 +6625,31 @@
         <v>4.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS24" t="n">
         <v>4.1</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV24" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW24" t="n">
         <v>3.7</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H25" t="n">
         <v>5.5</v>
@@ -6723,7 +6723,7 @@
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
@@ -6738,7 +6738,7 @@
         <v>1.67</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T25" t="n">
         <v>1.6</v>
@@ -6750,10 +6750,10 @@
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X25" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="Y25" t="n">
         <v>42</v>
@@ -6882,7 +6882,7 @@
         <v>5.2</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP25" t="n">
         <v>12</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G26" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I26" t="n">
         <v>2.18</v>
       </c>
-      <c r="I26" t="n">
-        <v>2.32</v>
-      </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -6983,16 +6983,16 @@
         <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T26" t="n">
         <v>1.59</v>
@@ -7001,43 +7001,43 @@
         <v>2.52</v>
       </c>
       <c r="V26" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Y26" t="n">
         <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AB26" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
         <v>70</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
@@ -7049,16 +7049,16 @@
         <v>500</v>
       </c>
       <c r="AL26" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
         <v>17</v>
@@ -7073,13 +7073,13 @@
         <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
         <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
@@ -7097,10 +7097,10 @@
         <v>20</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BD26" t="n">
         <v>25</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>3.65</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H27" t="n">
         <v>1.87</v>
@@ -7372,7 +7372,7 @@
         <v>6.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>2.22</v>
       </c>
       <c r="H28" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
         <v>5.1</v>
@@ -7491,7 +7491,7 @@
         <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
         <v>2.12</v>
@@ -7503,7 +7503,7 @@
         <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
         <v>1.86</v>
@@ -7515,10 +7515,10 @@
         <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="Z28" t="n">
         <v>500</v>
@@ -7527,7 +7527,7 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>42</v>
@@ -7539,13 +7539,13 @@
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AH28" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -7554,7 +7554,7 @@
         <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AL28" t="n">
         <v>500</v>
@@ -7575,10 +7575,10 @@
         <v>6.2</v>
       </c>
       <c r="AR28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS28" t="n">
         <v>4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.8</v>
       </c>
       <c r="AT28" t="n">
         <v>4.4</v>
@@ -7587,40 +7587,40 @@
         <v>4.9</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="AX28" t="n">
         <v>6.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AZ28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD28" t="n">
         <v>3.75</v>
       </c>
-      <c r="BA28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BE28" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="BF28" t="n">
         <v>5.7</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.35</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G29" t="n">
         <v>1.75</v>
@@ -7760,7 +7760,7 @@
         <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V29" t="n">
         <v>1.16</v>
@@ -7784,7 +7784,7 @@
         <v>6.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
@@ -7793,7 +7793,7 @@
         <v>700</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AG29" t="n">
         <v>17.5</v>
@@ -7874,7 +7874,7 @@
         <v>12</v>
       </c>
       <c r="BG29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="n">
         <v>3.25</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7981,13 +7981,13 @@
         <v>1.72</v>
       </c>
       <c r="J30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K30" t="n">
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -8119,7 +8119,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE30" t="n">
         <v>10</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8226,16 +8226,16 @@
         <v>1.29</v>
       </c>
       <c r="G31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K31" t="n">
         <v>5.8</v>
@@ -8244,28 +8244,28 @@
         <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
         <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="U31" t="n">
         <v>1.47</v>
@@ -8274,13 +8274,13 @@
         <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="Z31" t="n">
         <v>230</v>
@@ -8289,7 +8289,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC31" t="n">
         <v>13.5</v>
@@ -8301,88 +8301,88 @@
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AG31" t="n">
         <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="AI31" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
         <v>380</v>
       </c>
       <c r="AM31" t="n">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="AN31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ31" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AY31" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
       </c>
       <c r="BD31" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF31" t="n">
         <v>6.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH31" t="n">
         <v>3.75</v>
@@ -8391,62 +8391,62 @@
         <v>2.66</v>
       </c>
       <c r="BJ31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL31" t="n">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="BM31" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN31" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BO31" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BP31" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BQ31" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BR31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS31" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BT31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="BV31" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="BW31" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BX31" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="BY31" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ31" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CA31" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G32" t="n">
         <v>7.6</v>
       </c>
       <c r="H32" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I32" t="n">
         <v>1.55</v>
@@ -8609,7 +8609,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY32" t="n">
         <v>19</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8761,34 +8761,34 @@
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q33" t="n">
         <v>1.52</v>
       </c>
       <c r="R33" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S33" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T33" t="n">
         <v>1.52</v>
       </c>
       <c r="U33" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V33" t="n">
         <v>2.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z33" t="n">
         <v>16</v>
@@ -8812,13 +8812,13 @@
         <v>36</v>
       </c>
       <c r="AG33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH33" t="n">
         <v>14.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ33" t="n">
         <v>75</v>
@@ -8839,7 +8839,7 @@
         <v>8</v>
       </c>
       <c r="AP33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ33" t="n">
         <v>14</v>
@@ -8857,7 +8857,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
         <v>15.5</v>
@@ -8887,7 +8887,7 @@
         <v>44</v>
       </c>
       <c r="BF33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG33" t="n">
         <v>7.2</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8985,13 +8985,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G34" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I34" t="n">
         <v>1.55</v>
@@ -9000,13 +9000,13 @@
         <v>4.8</v>
       </c>
       <c r="K34" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
         <v>6.2</v>
@@ -9015,40 +9015,40 @@
         <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
       </c>
       <c r="R34" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U34" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V34" t="n">
         <v>2.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
         <v>75</v>
       </c>
       <c r="Y34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB34" t="n">
         <v>36</v>
@@ -9063,7 +9063,7 @@
         <v>15</v>
       </c>
       <c r="AF34" t="n">
-        <v>420</v>
+        <v>130</v>
       </c>
       <c r="AG34" t="n">
         <v>950</v>
@@ -9078,7 +9078,7 @@
         <v>170</v>
       </c>
       <c r="AK34" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="AL34" t="n">
         <v>300</v>
@@ -9090,7 +9090,7 @@
         <v>150</v>
       </c>
       <c r="AO34" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AP34" t="n">
         <v>14.5</v>
@@ -9105,10 +9105,10 @@
         <v>12.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AU34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV34" t="n">
         <v>9.199999999999999</v>
@@ -9129,25 +9129,25 @@
         <v>20</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BE34" t="n">
         <v>28</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BG34" t="n">
         <v>4.6</v>
       </c>
       <c r="BH34" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BI34" t="n">
         <v>3.85</v>
@@ -9156,59 +9156,59 @@
         <v>11.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BL34" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN34" t="n">
         <v>12.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BP34" t="n">
         <v>55</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR34" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BT34" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BU34" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BV34" t="n">
         <v>11</v>
       </c>
       <c r="BW34" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BX34" t="n">
         <v>22</v>
       </c>
       <c r="BY34" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BZ34" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G35" t="n">
         <v>1.61</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="Z35" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AA35" t="n">
         <v>280</v>
@@ -9353,10 +9353,10 @@
         <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT35" t="n">
         <v>6.8</v>
@@ -9389,7 +9389,7 @@
         <v>12.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE35" t="n">
         <v>5.4</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>1.83</v>
       </c>
       <c r="G36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H36" t="n">
         <v>4.6</v>
@@ -9505,10 +9505,10 @@
         <v>4.8</v>
       </c>
       <c r="J36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L36" t="n">
         <v>1.34</v>
@@ -9529,25 +9529,25 @@
         <v>1.74</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T36" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U36" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X36" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y36" t="n">
         <v>21</v>
@@ -9556,19 +9556,19 @@
         <v>36</v>
       </c>
       <c r="AA36" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC36" t="n">
         <v>9.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE36" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF36" t="n">
         <v>12.5</v>
@@ -9595,28 +9595,28 @@
         <v>85</v>
       </c>
       <c r="AN36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO36" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP36" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR36" t="n">
         <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV36" t="n">
         <v>16</v>
@@ -9625,19 +9625,19 @@
         <v>44</v>
       </c>
       <c r="AX36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
         <v>15.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BB36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC36" t="n">
         <v>16</v>
@@ -9658,19 +9658,19 @@
         <v>4.4</v>
       </c>
       <c r="BI36" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BL36" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM36" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BN36" t="n">
         <v>5.4</v>
@@ -9682,41 +9682,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BR36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA36" t="n">
         <v>4.2</v>
       </c>
-      <c r="BT36" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BV36" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BX36" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>4</v>
-      </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
         <v>3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9804,7 +9804,7 @@
         <v>22</v>
       </c>
       <c r="Y37" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z37" t="n">
         <v>500</v>
@@ -9816,7 +9816,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD37" t="n">
         <v>970</v>
@@ -9825,7 +9825,7 @@
         <v>500</v>
       </c>
       <c r="AF37" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AG37" t="n">
         <v>36</v>
@@ -9858,22 +9858,22 @@
         <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU37" t="n">
         <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AW37" t="n">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>7.8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA37" t="n">
         <v>7</v>
@@ -9897,7 +9897,7 @@
         <v>6.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE37" t="n">
         <v>7.4</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="G38" t="n">
         <v>1.77</v>
@@ -10115,7 +10115,7 @@
         <v>12.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS38" t="n">
         <v>5.5</v>
@@ -10127,10 +10127,10 @@
         <v>7.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX38" t="n">
         <v>7.2</v>
@@ -10142,7 +10142,7 @@
         <v>15.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB38" t="n">
         <v>14</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         <v>3.2</v>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J39" t="n">
         <v>3.05</v>
@@ -10309,7 +10309,7 @@
         <v>1.58</v>
       </c>
       <c r="X39" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="n">
         <v>12.5</v>
@@ -10318,7 +10318,7 @@
         <v>500</v>
       </c>
       <c r="AA39" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB39" t="n">
         <v>10</v>
@@ -10339,13 +10339,13 @@
         <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
       </c>
       <c r="AJ39" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK39" t="n">
         <v>500</v>
@@ -10369,13 +10369,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR39" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AU39" t="n">
         <v>5.6</v>
@@ -10384,37 +10384,37 @@
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AY39" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF39" t="n">
         <v>5.3</v>
       </c>
-      <c r="BA39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG39" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BH39" t="n">
         <v>3.25</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -10512,19 +10512,19 @@
         <v>1.54</v>
       </c>
       <c r="G40" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H40" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I40" t="n">
         <v>11.5</v>
       </c>
       <c r="J40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L40" t="n">
         <v>1.39</v>
@@ -10533,7 +10533,7 @@
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>1.41</v>
@@ -10557,13 +10557,13 @@
         <v>1.63</v>
       </c>
       <c r="V40" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W40" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X40" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="n">
         <v>950</v>
@@ -10575,7 +10575,7 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AC40" t="n">
         <v>11.5</v>
@@ -10599,7 +10599,7 @@
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="AK40" t="n">
         <v>60</v>
@@ -10611,7 +10611,7 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -10620,10 +10620,10 @@
         <v>5.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AR40" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AS40" t="n">
         <v>5.2</v>
@@ -10635,7 +10635,7 @@
         <v>5.1</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AW40" t="n">
         <v>5.1</v>
@@ -10647,7 +10647,7 @@
         <v>7.8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA40" t="n">
         <v>5.1</v>
@@ -10656,10 +10656,10 @@
         <v>10</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE40" t="n">
         <v>5.2</v>
@@ -10668,7 +10668,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH40" t="n">
         <v>3.5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -10790,10 +10790,10 @@
         <v>3.55</v>
       </c>
       <c r="O41" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P41" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q41" t="n">
         <v>2.1</v>
@@ -10802,13 +10802,13 @@
         <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T41" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V41" t="n">
         <v>2.36</v>
@@ -10826,34 +10826,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA41" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB41" t="n">
         <v>16.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD41" t="n">
         <v>10</v>
       </c>
       <c r="AE41" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF41" t="n">
         <v>44</v>
       </c>
       <c r="AG41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH41" t="n">
         <v>23</v>
       </c>
       <c r="AI41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ41" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AK41" t="n">
         <v>85</v>
@@ -10865,7 +10865,7 @@
         <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO41" t="n">
         <v>11.5</v>
@@ -10925,10 +10925,10 @@
         <v>10.5</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ41" t="n">
         <v>11.5</v>
@@ -10952,13 +10952,13 @@
         <v>70</v>
       </c>
       <c r="BQ41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BR41" t="n">
         <v>80</v>
       </c>
       <c r="BS41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT41" t="n">
         <v>4.1</v>
@@ -10976,7 +10976,7 @@
         <v>30</v>
       </c>
       <c r="BY41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -11017,19 +11017,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="G42" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="H42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
         <v>3.8</v>
@@ -11041,37 +11041,37 @@
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P42" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="R42" t="n">
         <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U42" t="n">
         <v>1.75</v>
       </c>
       <c r="V42" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="X42" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="n">
         <v>970</v>
@@ -11083,7 +11083,7 @@
         <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC42" t="n">
         <v>14</v>
@@ -11095,7 +11095,7 @@
         <v>700</v>
       </c>
       <c r="AF42" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG42" t="n">
         <v>36</v>
@@ -11110,7 +11110,7 @@
         <v>900</v>
       </c>
       <c r="AK42" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL42" t="n">
         <v>500</v>
@@ -11119,70 +11119,70 @@
         <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO42" t="n">
         <v>700</v>
       </c>
       <c r="AP42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX42" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AY42" t="n">
         <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="BC42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH42" t="n">
         <v>3.4</v>
       </c>
-      <c r="BE42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BI42" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ42" t="n">
         <v>12.5</v>
@@ -11197,50 +11197,50 @@
         <v>5.8</v>
       </c>
       <c r="BN42" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ42" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR42" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BU42" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW42" t="n">
         <v>5.4</v>
       </c>
       <c r="BX42" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY42" t="n">
         <v>5.5</v>
       </c>
       <c r="BZ42" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -11262,239 +11262,239 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="G43" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="J43" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="L43" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="U43" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W43" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="X43" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y43" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z43" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AD43" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF43" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AG43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH43" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI43" t="n">
         <v>230</v>
       </c>
       <c r="AJ43" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK43" t="n">
         <v>970</v>
       </c>
       <c r="AL43" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN43" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP43" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="AR43" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AT43" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AU43" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>340</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS43" t="n">
         <v>4.6</v>
       </c>
-      <c r="AV43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB43" t="n">
+      <c r="BT43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>160</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>160</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA43" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ43" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>260</v>
-      </c>
-      <c r="BM43" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN43" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO43" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ43" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR43" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS43" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BT43" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BU43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV43" t="n">
-        <v>150</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>140</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BZ43" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="CA43" t="n">
-        <v>4.4</v>
-      </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -11516,239 +11516,239 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="G44" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="H44" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="I44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X44" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>11.5</v>
-      </c>
-      <c r="J44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S44" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>520</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>12.5</v>
       </c>
       <c r="AK44" t="n">
         <v>970</v>
       </c>
       <c r="AL44" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM44" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AO44" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AR44" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS44" t="n">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="AW44" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AZ44" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="BA44" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>260</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BT44" t="n">
         <v>17.5</v>
       </c>
-      <c r="BD44" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ44" t="n">
-        <v>17</v>
-      </c>
-      <c r="BK44" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>340</v>
-      </c>
-      <c r="BM44" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BP44" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BR44" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS44" t="n">
+      <c r="BU44" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT44" t="n">
+      <c r="BV44" t="n">
+        <v>150</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>140</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BZ44" t="n">
         <v>16.5</v>
       </c>
-      <c r="BU44" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV44" t="n">
-        <v>160</v>
-      </c>
-      <c r="BW44" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BX44" t="n">
-        <v>160</v>
-      </c>
-      <c r="BY44" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BZ44" t="n">
-        <v>26</v>
-      </c>
       <c r="CA44" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
         <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R45" t="n">
         <v>1.24</v>
@@ -11821,10 +11821,10 @@
         <v>4.4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U45" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="V45" t="n">
         <v>1.23</v>
@@ -11833,10 +11833,10 @@
         <v>2.02</v>
       </c>
       <c r="X45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z45" t="n">
         <v>38</v>
@@ -11845,10 +11845,10 @@
         <v>170</v>
       </c>
       <c r="AB45" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD45" t="n">
         <v>21</v>
@@ -11860,28 +11860,28 @@
         <v>11</v>
       </c>
       <c r="AG45" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI45" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ45" t="n">
         <v>25</v>
       </c>
       <c r="AK45" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL45" t="n">
         <v>55</v>
       </c>
       <c r="AM45" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO45" t="n">
         <v>130</v>
@@ -11896,7 +11896,7 @@
         <v>30</v>
       </c>
       <c r="AS45" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -11908,7 +11908,7 @@
         <v>17.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX45" t="n">
         <v>9.199999999999999</v>
@@ -11920,7 +11920,7 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB45" t="n">
         <v>19</v>
@@ -11932,13 +11932,13 @@
         <v>42</v>
       </c>
       <c r="BE45" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF45" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH45" t="n">
         <v>3.4</v>
@@ -11950,16 +11950,16 @@
         <v>13.5</v>
       </c>
       <c r="BK45" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL45" t="n">
         <v>230</v>
       </c>
       <c r="BM45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO45" t="n">
         <v>3.4</v>
@@ -11968,13 +11968,13 @@
         <v>18</v>
       </c>
       <c r="BQ45" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR45" t="n">
         <v>42</v>
       </c>
       <c r="BS45" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT45" t="n">
         <v>9.800000000000001</v>
@@ -11986,23 +11986,23 @@
         <v>60</v>
       </c>
       <c r="BW45" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX45" t="n">
         <v>80</v>
       </c>
       <c r="BY45" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ45" t="n">
         <v>42</v>
       </c>
       <c r="CA45" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -12036,49 +12036,49 @@
         <v>1.76</v>
       </c>
       <c r="G46" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I46" t="n">
         <v>5.8</v>
       </c>
       <c r="J46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S46" t="n">
         <v>3.7</v>
       </c>
-      <c r="K46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T46" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="V46" t="n">
         <v>1.21</v>
@@ -12087,19 +12087,19 @@
         <v>2.16</v>
       </c>
       <c r="X46" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y46" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA46" t="n">
         <v>160</v>
       </c>
       <c r="AB46" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC46" t="n">
         <v>9.199999999999999</v>
@@ -12111,7 +12111,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG46" t="n">
         <v>10</v>
@@ -12138,34 +12138,34 @@
         <v>13.5</v>
       </c>
       <c r="AO46" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP46" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ46" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS46" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AT46" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV46" t="n">
         <v>17.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX46" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY46" t="n">
         <v>8.800000000000001</v>
@@ -12174,7 +12174,7 @@
         <v>17.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB46" t="n">
         <v>16</v>
@@ -12183,22 +12183,22 @@
         <v>16</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF46" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH46" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BJ46" t="n">
         <v>12</v>
@@ -12207,7 +12207,7 @@
         <v>3.95</v>
       </c>
       <c r="BL46" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM46" t="n">
         <v>5.7</v>
@@ -12216,16 +12216,16 @@
         <v>4.9</v>
       </c>
       <c r="BO46" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP46" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS46" t="n">
         <v>5</v>
@@ -12234,29 +12234,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU46" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV46" t="n">
         <v>55</v>
       </c>
       <c r="BW46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX46" t="n">
         <v>60</v>
       </c>
       <c r="BY46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ46" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="CA46" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
         <v>1.92</v>
       </c>
       <c r="U47" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V47" t="n">
         <v>1.4</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -857,115 +857,115 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.65</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>25</v>
       </c>
       <c r="AA2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE2" t="n">
         <v>70</v>
       </c>
-      <c r="AB2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>40</v>
-      </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -974,113 +974,113 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="BE2" t="n">
         <v>38</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>970</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
         <v>36</v>
       </c>
       <c r="BZ2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.25</v>
@@ -1144,49 +1144,49 @@
         <v>2.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
         <v>30</v>
       </c>
       <c r="Y3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
         <v>55</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>13.5</v>
@@ -1195,13 +1195,13 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>340</v>
+        <v>480</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK3" t="n">
         <v>15</v>
@@ -1210,131 +1210,131 @@
         <v>24</v>
       </c>
       <c r="AM3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS3" t="n">
         <v>70</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>42</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
         <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI3" t="n">
         <v>4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>75</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>18.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1395,40 +1395,40 @@
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="n">
         <v>28</v>
@@ -1437,19 +1437,19 @@
         <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1458,7 +1458,7 @@
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
@@ -1467,64 +1467,64 @@
         <v>60</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
         <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC4" t="n">
         <v>22</v>
       </c>
-      <c r="BB4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>23</v>
-      </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH4" t="n">
         <v>4.9</v>
@@ -1536,59 +1536,59 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BL4" t="n">
         <v>70</v>
       </c>
       <c r="BM4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
         <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
         <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>17</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1643,7 +1643,7 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
@@ -1652,7 +1652,7 @@
         <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
@@ -1682,7 +1682,7 @@
         <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
         <v>12.5</v>
@@ -1703,7 +1703,7 @@
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1724,22 +1724,22 @@
         <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
         <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
@@ -1748,101 +1748,101 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>16.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
         <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>140</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>34</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>6.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.55</v>
@@ -1891,13 +1891,13 @@
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.34</v>
@@ -1915,13 +1915,13 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
@@ -1930,28 +1930,28 @@
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
         <v>24</v>
       </c>
       <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AG6" t="n">
         <v>34</v>
@@ -1960,25 +1960,25 @@
         <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AK6" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -1999,13 +1999,13 @@
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW6" t="n">
         <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -2014,22 +2014,22 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
         <v>9.199999999999999</v>
@@ -2047,10 +2047,10 @@
         <v>3.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BM6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN6" t="n">
         <v>12.5</v>
@@ -2065,7 +2065,7 @@
         <v>4.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
         <v>4.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G7" t="n">
         <v>3.8</v>
@@ -2142,37 +2142,37 @@
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
         <v>1.86</v>
@@ -2181,13 +2181,13 @@
         <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
         <v>90</v>
@@ -2211,13 +2211,13 @@
         <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
         <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>110</v>
@@ -2229,25 +2229,25 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>210</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>17</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
         <v>7.4</v>
@@ -2259,16 +2259,16 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AY7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
         <v>34</v>
@@ -2289,68 +2289,68 @@
         <v>14</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU7" t="n">
         <v>3.95</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA7" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2384,28 +2384,28 @@
         <v>1.46</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -2417,13 +2417,13 @@
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
@@ -2432,112 +2432,112 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AS8" t="n">
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE8" t="n">
         <v>3.15</v>
       </c>
-      <c r="AU8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
         <v>4.2</v>
@@ -2546,55 +2546,55 @@
         <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
         <v>970</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BP8" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BR8" t="n">
         <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT8" t="n">
         <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV8" t="n">
         <v>90</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BX8" t="n">
         <v>95</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I9" t="n">
         <v>1.28</v>
@@ -2653,7 +2653,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2665,10 +2665,10 @@
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
         <v>1.68</v>
@@ -2695,10 +2695,10 @@
         <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB9" t="n">
         <v>950</v>
@@ -2740,125 +2740,125 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
         <v>7.6</v>
       </c>
       <c r="AX9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY9" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>170</v>
       </c>
       <c r="BM9" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BP9" t="n">
         <v>130</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BR9" t="n">
         <v>110</v>
       </c>
       <c r="BS9" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BX9" t="n">
         <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H10" t="n">
         <v>1.25</v>
       </c>
       <c r="I10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="J10" t="n">
         <v>7.4</v>
@@ -2907,46 +2907,46 @@
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O10" t="n">
         <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
         <v>11.5</v>
@@ -2958,7 +2958,7 @@
         <v>65</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
         <v>12</v>
@@ -2973,13 +2973,13 @@
         <v>110</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AI10" t="n">
         <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="AK10" t="n">
         <v>180</v>
@@ -2991,16 +2991,16 @@
         <v>380</v>
       </c>
       <c r="AN10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AP10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -3009,110 +3009,110 @@
         <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AU10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
         <v>50</v>
       </c>
       <c r="AY10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="BC10" t="n">
         <v>48</v>
       </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BE10" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BH10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>90</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU10" t="n">
         <v>3.45</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>95</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>75</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.4</v>
       </c>
       <c r="BV10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BW10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CA10" t="n">
         <v>5.1</v>
       </c>
-      <c r="BX10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>5.3</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
         <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
         <v>3.95</v>
@@ -3218,7 +3218,7 @@
         <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
         <v>14.5</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3284,7 +3284,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
         <v>18</v>
@@ -3311,37 +3311,37 @@
         <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BL11" t="n">
         <v>160</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BO11" t="n">
         <v>4.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
         <v>5.1</v>
@@ -3350,23 +3350,23 @@
         <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BX11" t="n">
         <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ11" t="n">
         <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
         <v>5.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.34</v>
@@ -3427,7 +3427,7 @@
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
         <v>1.74</v>
@@ -3436,19 +3436,19 @@
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -3460,16 +3460,16 @@
         <v>420</v>
       </c>
       <c r="AA12" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
         <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AE12" t="n">
         <v>160</v>
@@ -3478,7 +3478,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>32</v>
@@ -3502,19 +3502,19 @@
         <v>6.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AS12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AT12" t="n">
         <v>7.8</v>
@@ -3523,10 +3523,10 @@
         <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3535,10 +3535,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BB12" t="n">
         <v>10.5</v>
@@ -3547,16 +3547,16 @@
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF12" t="n">
         <v>5.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
@@ -3565,62 +3565,62 @@
         <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL12" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN12" t="n">
         <v>3.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP12" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR12" t="n">
         <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT12" t="n">
         <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3657,10 +3657,10 @@
         <v>1.33</v>
       </c>
       <c r="H13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -3669,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
@@ -3693,7 +3693,7 @@
         <v>2.14</v>
       </c>
       <c r="T13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -3702,13 +3702,13 @@
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
         <v>130</v>
@@ -3723,7 +3723,7 @@
         <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -3774,25 +3774,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
         <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
         <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
         <v>5.3</v>
@@ -3804,10 +3804,10 @@
         <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BG13" t="n">
         <v>9.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
         <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
         <v>2.16</v>
@@ -3989,7 +3989,7 @@
         <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -4022,19 +4022,19 @@
         <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="AT14" t="n">
         <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>6.2</v>
@@ -4043,7 +4043,7 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
         <v>7.2</v>
@@ -4061,7 +4061,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
         <v>4.7</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
@@ -4183,7 +4183,7 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
@@ -4201,7 +4201,7 @@
         <v>2.32</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
         <v>2.46</v>
@@ -4267,7 +4267,7 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>8.4</v>
@@ -4276,10 +4276,10 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
@@ -4288,10 +4288,10 @@
         <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -4300,25 +4300,25 @@
         <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH15" t="n">
         <v>5.1</v>
@@ -4330,16 +4330,16 @@
         <v>9.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL15" t="n">
         <v>80</v>
       </c>
       <c r="BM15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO15" t="n">
         <v>5.3</v>
@@ -4348,13 +4348,13 @@
         <v>24</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR15" t="n">
         <v>30</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT15" t="n">
         <v>6.6</v>
@@ -4366,7 +4366,7 @@
         <v>17.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX15" t="n">
         <v>26</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -4413,34 +4413,34 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.15</v>
       </c>
-      <c r="J16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
         <v>2.44</v>
       </c>
       <c r="O16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P16" t="n">
         <v>1.48</v>
@@ -4452,25 +4452,25 @@
         <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
         <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y16" t="n">
         <v>8.4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>8.6</v>
       </c>
       <c r="Z16" t="n">
         <v>21</v>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX16" t="n">
         <v>14.5</v>
@@ -4554,40 +4554,40 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
         <v>8.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL16" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="BM16" t="n">
         <v>6</v>
@@ -4596,10 +4596,10 @@
         <v>6.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ16" t="n">
         <v>5.2</v>
@@ -4614,7 +4614,7 @@
         <v>6.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
@@ -4623,7 +4623,7 @@
         <v>5.1</v>
       </c>
       <c r="BX16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>5.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -4673,37 +4673,37 @@
         <v>2.9</v>
       </c>
       <c r="H17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="n">
         <v>2.92</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.94</v>
       </c>
       <c r="K17" t="n">
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="O17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.51</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
         <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -4724,7 +4724,7 @@
         <v>19</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
@@ -4733,7 +4733,7 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
         <v>13</v>
@@ -4781,10 +4781,10 @@
         <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4796,13 +4796,13 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>10.5</v>
@@ -4811,16 +4811,16 @@
         <v>9.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.74</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="BF17" t="n">
         <v>6.2</v>
@@ -4829,25 +4829,25 @@
         <v>7.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO17" t="n">
         <v>4.2</v>
@@ -4856,41 +4856,41 @@
         <v>30</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
         <v>55</v>
       </c>
       <c r="BS17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT17" t="n">
         <v>7</v>
       </c>
       <c r="BU17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BV17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BX17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>60</v>
       </c>
-      <c r="BY17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>55</v>
-      </c>
       <c r="CA17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G18" t="n">
         <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I18" t="n">
         <v>2.18</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
@@ -4966,10 +4966,10 @@
         <v>1.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W18" t="n">
         <v>1.37</v>
@@ -4984,10 +4984,10 @@
         <v>17.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -4999,7 +4999,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG18" t="n">
         <v>17</v>
@@ -5065,7 +5065,7 @@
         <v>13</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>3.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I19" t="n">
         <v>2.24</v>
@@ -5199,13 +5199,13 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
         <v>1.93</v>
@@ -5214,16 +5214,16 @@
         <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.37</v>
@@ -5232,19 +5232,19 @@
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
         <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5256,13 +5256,13 @@
         <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AJ19" t="n">
         <v>70</v>
@@ -5271,16 +5271,16 @@
         <v>42</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AP19" t="n">
         <v>13</v>
@@ -5316,7 +5316,7 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
         <v>55</v>
@@ -5331,7 +5331,7 @@
         <v>36</v>
       </c>
       <c r="BF19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG19" t="n">
         <v>14.5</v>
@@ -5376,7 +5376,7 @@
         <v>5.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV19" t="n">
         <v>19</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>7.4</v>
       </c>
       <c r="I20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.2</v>
@@ -5468,13 +5468,13 @@
         <v>1.87</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T20" t="n">
         <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V20" t="n">
         <v>1.14</v>
@@ -5483,37 +5483,37 @@
         <v>3.2</v>
       </c>
       <c r="X20" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y20" t="n">
         <v>40</v>
       </c>
-      <c r="Y20" t="n">
-        <v>42</v>
-      </c>
       <c r="Z20" t="n">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AA20" t="n">
         <v>210</v>
       </c>
       <c r="AB20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
         <v>14</v>
       </c>
       <c r="AD20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
         <v>400</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
         <v>320</v>
@@ -5540,13 +5540,13 @@
         <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
         <v>13</v>
@@ -5558,7 +5558,7 @@
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -5570,7 +5570,7 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -5582,16 +5582,16 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BI20" t="n">
         <v>4.2</v>
@@ -5600,13 +5600,13 @@
         <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BL20" t="n">
         <v>90</v>
       </c>
       <c r="BM20" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BN20" t="n">
         <v>5.1</v>
@@ -5618,41 +5618,41 @@
         <v>9.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BR20" t="n">
         <v>21</v>
       </c>
       <c r="BS20" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BT20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BV20" t="n">
         <v>55</v>
       </c>
       <c r="BW20" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BX20" t="n">
         <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BZ20" t="n">
         <v>11</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>1.77</v>
       </c>
       <c r="G21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H21" t="n">
         <v>4.5</v>
@@ -5701,7 +5701,7 @@
         <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5737,10 +5737,10 @@
         <v>2.18</v>
       </c>
       <c r="X21" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="Y21" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="Z21" t="n">
         <v>95</v>
@@ -5749,7 +5749,7 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
@@ -5761,7 +5761,7 @@
         <v>190</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
@@ -5770,7 +5770,7 @@
         <v>17.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AJ21" t="n">
         <v>21</v>
@@ -5797,10 +5797,10 @@
         <v>17.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -5824,7 +5824,7 @@
         <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
         <v>15</v>
@@ -5836,16 +5836,16 @@
         <v>19.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
         <v>5.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI21" t="n">
         <v>3.6</v>
@@ -5857,10 +5857,10 @@
         <v>3.65</v>
       </c>
       <c r="BL21" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN21" t="n">
         <v>5.5</v>
@@ -5887,10 +5887,10 @@
         <v>3.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX21" t="n">
         <v>40</v>
@@ -5899,14 +5899,14 @@
         <v>4.9</v>
       </c>
       <c r="BZ21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA21" t="n">
         <v>4.1</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
         <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
@@ -5988,7 +5988,7 @@
         <v>1.68</v>
       </c>
       <c r="W22" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
         <v>75</v>
@@ -6081,7 +6081,7 @@
         <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
         <v>13</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
         <v>2.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
         <v>2.02</v>
@@ -6299,16 +6299,16 @@
         <v>22</v>
       </c>
       <c r="AP23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS23" t="n">
         <v>9</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6320,7 +6320,7 @@
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX23" t="n">
         <v>12</v>
@@ -6332,7 +6332,7 @@
         <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -6374,13 +6374,13 @@
         <v>6.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP23" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="BR23" t="n">
         <v>23</v>
@@ -6410,11 +6410,11 @@
         <v>14.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -6457,19 +6457,19 @@
         <v>2.32</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
@@ -6529,7 +6529,7 @@
         <v>15.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
         <v>75</v>
@@ -6571,13 +6571,13 @@
         <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
         <v>16.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
         <v>12.5</v>
@@ -6586,7 +6586,7 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB24" t="n">
         <v>36</v>
@@ -6598,10 +6598,10 @@
         <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
         <v>11</v>
@@ -6628,7 +6628,7 @@
         <v>8</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP24" t="n">
         <v>30</v>
@@ -6646,7 +6646,7 @@
         <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV24" t="n">
         <v>18.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -6702,22 +6702,22 @@
         <v>1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H25" t="n">
         <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
@@ -6732,31 +6732,31 @@
         <v>2.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R25" t="n">
         <v>1.67</v>
       </c>
       <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.36</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.34</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X25" t="n">
         <v>50</v>
       </c>
       <c r="Y25" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Z25" t="n">
         <v>500</v>
@@ -6789,7 +6789,7 @@
         <v>700</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
         <v>29</v>
@@ -6804,31 +6804,31 @@
         <v>6.6</v>
       </c>
       <c r="AO25" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AP25" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV25" t="n">
         <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -6837,19 +6837,19 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>12.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BE25" t="n">
         <v>20</v>
@@ -6858,25 +6858,25 @@
         <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BI25" t="n">
         <v>3.55</v>
       </c>
       <c r="BJ25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BL25" t="n">
         <v>100</v>
       </c>
       <c r="BM25" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BN25" t="n">
         <v>5.2</v>
@@ -6888,41 +6888,41 @@
         <v>12</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BR25" t="n">
         <v>24</v>
       </c>
       <c r="BS25" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BT25" t="n">
         <v>10.5</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BV25" t="n">
         <v>44</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BX25" t="n">
         <v>46</v>
       </c>
       <c r="BY25" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BZ25" t="n">
         <v>15.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -6959,10 +6959,10 @@
         <v>3.65</v>
       </c>
       <c r="H26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>3.75</v>
@@ -6983,28 +6983,28 @@
         <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
         <v>1.61</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="U26" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V26" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
         <v>50</v>
@@ -7013,10 +7013,10 @@
         <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB26" t="n">
         <v>30</v>
@@ -7034,7 +7034,7 @@
         <v>70</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
@@ -7085,34 +7085,34 @@
         <v>15.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE26" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>40</v>
       </c>
       <c r="BF26" t="n">
         <v>14.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH26" t="n">
         <v>5</v>
@@ -7124,7 +7124,7 @@
         <v>10.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BL26" t="n">
         <v>95</v>
@@ -7136,7 +7136,7 @@
         <v>8.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP26" t="n">
         <v>29</v>
@@ -7157,7 +7157,7 @@
         <v>4.1</v>
       </c>
       <c r="BV26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW26" t="n">
         <v>3.65</v>
@@ -7172,11 +7172,11 @@
         <v>20</v>
       </c>
       <c r="CA26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
         <v>3.95</v>
@@ -7216,7 +7216,7 @@
         <v>1.87</v>
       </c>
       <c r="I27" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J27" t="n">
         <v>4.4</v>
@@ -7255,7 +7255,7 @@
         <v>2.76</v>
       </c>
       <c r="V27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W27" t="n">
         <v>1.33</v>
@@ -7315,7 +7315,7 @@
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
         <v>14.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7461,64 +7461,64 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="H28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.7</v>
       </c>
-      <c r="I28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.74</v>
-      </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
         <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
         <v>500</v>
@@ -7527,25 +7527,25 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
         <v>42</v>
       </c>
       <c r="AD28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="AH28" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -7554,7 +7554,7 @@
         <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
         <v>500</v>
@@ -7569,112 +7569,112 @@
         <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AT28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU28" t="n">
         <v>4.4</v>
       </c>
-      <c r="AU28" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AV28" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AX28" t="n">
         <v>6.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="BE28" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="BF28" t="n">
         <v>5.7</v>
       </c>
       <c r="BG28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO28" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>2.82</v>
       </c>
       <c r="BP28" t="n">
         <v>970</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR28" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BS28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BT28" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV28" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BW28" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX28" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BY28" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7718,10 +7718,10 @@
         <v>1.69</v>
       </c>
       <c r="G29" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -7739,37 +7739,37 @@
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V29" t="n">
         <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="Y29" t="n">
         <v>32</v>
@@ -7781,10 +7781,10 @@
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
@@ -7793,7 +7793,7 @@
         <v>700</v>
       </c>
       <c r="AF29" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
         <v>17.5</v>
@@ -7805,7 +7805,7 @@
         <v>700</v>
       </c>
       <c r="AJ29" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AK29" t="n">
         <v>65</v>
@@ -7823,31 +7823,31 @@
         <v>700</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
@@ -7856,7 +7856,7 @@
         <v>13</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
         <v>8.4</v>
@@ -7865,19 +7865,19 @@
         <v>11.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
         <v>12</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI29" t="n">
         <v>2.44</v>
@@ -7886,13 +7886,13 @@
         <v>12.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL29" t="n">
         <v>240</v>
       </c>
       <c r="BM29" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN29" t="n">
         <v>4.2</v>
@@ -7901,44 +7901,44 @@
         <v>3.65</v>
       </c>
       <c r="BP29" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR29" t="n">
         <v>36</v>
       </c>
       <c r="BS29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BX29" t="n">
         <v>90</v>
       </c>
       <c r="BY29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ29" t="n">
         <v>32</v>
       </c>
       <c r="CA29" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7975,19 +7975,19 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="I30" t="n">
         <v>1.72</v>
       </c>
       <c r="J30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K30" t="n">
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -8026,7 +8026,7 @@
         <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z30" t="n">
         <v>9.800000000000001</v>
@@ -8041,13 +8041,13 @@
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>19.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AG30" t="n">
         <v>44</v>
@@ -8056,7 +8056,7 @@
         <v>40</v>
       </c>
       <c r="AI30" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AJ30" t="n">
         <v>900</v>
@@ -8101,7 +8101,7 @@
         <v>15.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY30" t="n">
         <v>18.5</v>
@@ -8110,22 +8110,22 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD30" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG30" t="n">
         <v>10</v>
@@ -8170,7 +8170,7 @@
         <v>4.7</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BV30" t="n">
         <v>13.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -8223,52 +8223,52 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H31" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="I31" t="n">
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="K31" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="V31" t="n">
         <v>1.05</v>
@@ -8277,10 +8277,10 @@
         <v>3.85</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Y31" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="Z31" t="n">
         <v>230</v>
@@ -8289,7 +8289,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AC31" t="n">
         <v>13.5</v>
@@ -8301,58 +8301,58 @@
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AJ31" t="n">
         <v>9.4</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
         <v>380</v>
       </c>
       <c r="AM31" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ31" t="n">
         <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU31" t="n">
         <v>11</v>
       </c>
       <c r="AV31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX31" t="n">
         <v>5.1</v>
@@ -8361,61 +8361,61 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="BA31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
       </c>
       <c r="BD31" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ31" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL31" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="BM31" t="n">
         <v>7.6</v>
       </c>
       <c r="BN31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BO31" t="n">
         <v>2.92</v>
       </c>
       <c r="BP31" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ31" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BR31" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS31" t="n">
         <v>6.4</v>
@@ -8424,29 +8424,29 @@
         <v>23</v>
       </c>
       <c r="BU31" t="n">
-        <v>13.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV31" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="BW31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX31" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="BY31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ31" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="CA31" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -8486,43 +8486,43 @@
         <v>1.48</v>
       </c>
       <c r="I32" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J32" t="n">
         <v>4.7</v>
       </c>
       <c r="K32" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.28</v>
       </c>
       <c r="M32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.19</v>
       </c>
       <c r="P32" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R32" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S32" t="n">
         <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U32" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V32" t="n">
         <v>2.82</v>
@@ -8555,7 +8555,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="AG32" t="n">
         <v>32</v>
@@ -8567,7 +8567,7 @@
         <v>36</v>
       </c>
       <c r="AJ32" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK32" t="n">
         <v>480</v>
@@ -8609,7 +8609,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY32" t="n">
         <v>19</v>
@@ -8621,19 +8621,19 @@
         <v>14.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BG32" t="n">
         <v>5.1</v>
@@ -8642,7 +8642,7 @@
         <v>5.2</v>
       </c>
       <c r="BI32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ32" t="n">
         <v>12</v>
@@ -8654,7 +8654,7 @@
         <v>120</v>
       </c>
       <c r="BM32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN32" t="n">
         <v>12.5</v>
@@ -8666,7 +8666,7 @@
         <v>55</v>
       </c>
       <c r="BQ32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR32" t="n">
         <v>60</v>
@@ -8678,13 +8678,13 @@
         <v>5.1</v>
       </c>
       <c r="BU32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV32" t="n">
         <v>11</v>
       </c>
       <c r="BW32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BX32" t="n">
         <v>25</v>
@@ -8693,14 +8693,14 @@
         <v>4</v>
       </c>
       <c r="BZ32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA32" t="n">
         <v>3.6</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>1.93</v>
       </c>
       <c r="I33" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="J33" t="n">
         <v>4.1</v>
@@ -8749,7 +8749,7 @@
         <v>4.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
@@ -8758,16 +8758,16 @@
         <v>6.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1.52</v>
       </c>
       <c r="R33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S33" t="n">
         <v>2.28</v>
@@ -8779,16 +8779,16 @@
         <v>2.76</v>
       </c>
       <c r="V33" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W33" t="n">
         <v>1.31</v>
       </c>
       <c r="X33" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Y33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z33" t="n">
         <v>16</v>
@@ -8812,22 +8812,22 @@
         <v>36</v>
       </c>
       <c r="AG33" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH33" t="n">
         <v>14.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ33" t="n">
         <v>75</v>
       </c>
       <c r="AK33" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="n">
         <v>55</v>
@@ -8896,65 +8896,65 @@
         <v>5.3</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BL33" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BN33" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BO33" t="n">
         <v>6</v>
       </c>
       <c r="BP33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR33" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BS33" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BT33" t="n">
         <v>6</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV33" t="n">
         <v>14.5</v>
       </c>
       <c r="BW33" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BX33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BZ33" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA33" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>6.4</v>
       </c>
       <c r="G34" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H34" t="n">
         <v>1.52</v>
@@ -8997,73 +8997,73 @@
         <v>1.55</v>
       </c>
       <c r="J34" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K34" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P34" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="R34" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="S34" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="T34" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U34" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="V34" t="n">
         <v>2.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
         <v>75</v>
       </c>
       <c r="Y34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AC34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE34" t="n">
         <v>15</v>
       </c>
       <c r="AF34" t="n">
-        <v>130</v>
+        <v>420</v>
       </c>
       <c r="AG34" t="n">
         <v>950</v>
@@ -9072,7 +9072,7 @@
         <v>19.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AJ34" t="n">
         <v>170</v>
@@ -9090,28 +9090,28 @@
         <v>150</v>
       </c>
       <c r="AO34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AP34" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>10</v>
       </c>
       <c r="AR34" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS34" t="n">
         <v>12.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW34" t="n">
         <v>12</v>
@@ -9120,7 +9120,7 @@
         <v>42</v>
       </c>
       <c r="AY34" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ34" t="n">
         <v>16</v>
@@ -9129,10 +9129,10 @@
         <v>20</v>
       </c>
       <c r="BB34" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BD34" t="n">
         <v>25</v>
@@ -9141,74 +9141,74 @@
         <v>28</v>
       </c>
       <c r="BF34" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH34" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BJ34" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BL34" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="BM34" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BN34" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BO34" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP34" t="n">
+        <v>46</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR34" t="n">
         <v>55</v>
       </c>
-      <c r="BQ34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>44</v>
-      </c>
       <c r="BS34" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT34" t="n">
         <v>4.7</v>
       </c>
       <c r="BU34" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BV34" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BW34" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BX34" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BZ34" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -9239,13 +9239,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
         <v>1.61</v>
       </c>
       <c r="H35" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I35" t="n">
         <v>9.4</v>
@@ -9308,7 +9308,7 @@
         <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD35" t="n">
         <v>32</v>
@@ -9353,10 +9353,10 @@
         <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT35" t="n">
         <v>6.8</v>
@@ -9368,7 +9368,7 @@
         <v>20</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX35" t="n">
         <v>6.8</v>
@@ -9380,7 +9380,7 @@
         <v>19.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB35" t="n">
         <v>10</v>
@@ -9389,16 +9389,16 @@
         <v>12.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF35" t="n">
         <v>6.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH35" t="n">
         <v>4.1</v>
@@ -9410,13 +9410,13 @@
         <v>13.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL35" t="n">
         <v>190</v>
       </c>
       <c r="BM35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN35" t="n">
         <v>4.7</v>
@@ -9425,7 +9425,7 @@
         <v>3.15</v>
       </c>
       <c r="BP35" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ35" t="n">
         <v>3.45</v>
@@ -9440,7 +9440,7 @@
         <v>12.5</v>
       </c>
       <c r="BU35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV35" t="n">
         <v>80</v>
@@ -9452,17 +9452,17 @@
         <v>85</v>
       </c>
       <c r="BY35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ35" t="n">
         <v>24</v>
       </c>
       <c r="CA35" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -9493,16 +9493,16 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G36" t="n">
         <v>1.83</v>
       </c>
-      <c r="G36" t="n">
-        <v>1.87</v>
-      </c>
       <c r="H36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
@@ -9517,19 +9517,19 @@
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
         <v>1.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S36" t="n">
         <v>2.82</v>
@@ -9538,25 +9538,25 @@
         <v>1.71</v>
       </c>
       <c r="U36" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB36" t="n">
         <v>11.5</v>
@@ -9565,10 +9565,10 @@
         <v>9.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF36" t="n">
         <v>12.5</v>
@@ -9577,16 +9577,16 @@
         <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI36" t="n">
         <v>55</v>
       </c>
       <c r="AJ36" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL36" t="n">
         <v>28</v>
@@ -9595,52 +9595,52 @@
         <v>85</v>
       </c>
       <c r="AN36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO36" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS36" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>16</v>
       </c>
       <c r="AT36" t="n">
         <v>10</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX36" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ36" t="n">
         <v>15.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB36" t="n">
         <v>18</v>
       </c>
       <c r="BC36" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD36" t="n">
         <v>26</v>
@@ -9649,7 +9649,7 @@
         <v>42</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG36" t="n">
         <v>38</v>
@@ -9664,59 +9664,59 @@
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL36" t="n">
         <v>120</v>
       </c>
       <c r="BM36" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BN36" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO36" t="n">
         <v>4</v>
       </c>
       <c r="BP36" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BR36" t="n">
         <v>28</v>
       </c>
       <c r="BS36" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BT36" t="n">
         <v>9.6</v>
       </c>
       <c r="BU36" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BV36" t="n">
         <v>42</v>
       </c>
       <c r="BW36" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BX36" t="n">
         <v>44</v>
       </c>
       <c r="BY36" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BZ36" t="n">
         <v>21</v>
       </c>
       <c r="CA36" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
         <v>3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9777,7 +9777,7 @@
         <v>1.36</v>
       </c>
       <c r="P37" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q37" t="n">
         <v>2.06</v>
@@ -9858,13 +9858,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR37" t="n">
         <v>6.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT37" t="n">
         <v>7</v>
@@ -9876,7 +9876,7 @@
         <v>6.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
         <v>9.800000000000001</v>
@@ -9888,25 +9888,25 @@
         <v>6.2</v>
       </c>
       <c r="BA37" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC37" t="n">
         <v>6.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF37" t="n">
         <v>5.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH37" t="n">
         <v>3.7</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G38" t="n">
         <v>1.77</v>
@@ -10016,7 +10016,7 @@
         <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L38" t="n">
         <v>1.5</v>
@@ -10067,10 +10067,10 @@
         <v>900</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD38" t="n">
         <v>30</v>
@@ -10079,7 +10079,7 @@
         <v>700</v>
       </c>
       <c r="AF38" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG38" t="n">
         <v>12</v>
@@ -10115,22 +10115,22 @@
         <v>12.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AT38" t="n">
         <v>5.1</v>
       </c>
       <c r="AU38" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV38" t="n">
         <v>15.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX38" t="n">
         <v>7.2</v>
@@ -10142,7 +10142,7 @@
         <v>15.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB38" t="n">
         <v>14</v>
@@ -10151,16 +10151,16 @@
         <v>19</v>
       </c>
       <c r="BD38" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF38" t="n">
         <v>13.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BH38" t="n">
         <v>3.3</v>
@@ -10184,7 +10184,7 @@
         <v>4.6</v>
       </c>
       <c r="BO38" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BP38" t="n">
         <v>14.5</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>2.44</v>
       </c>
       <c r="G39" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H39" t="n">
         <v>3.2</v>
@@ -10279,7 +10279,7 @@
         <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>1.45</v>
@@ -10291,7 +10291,7 @@
         <v>2.32</v>
       </c>
       <c r="R39" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S39" t="n">
         <v>4.1</v>
@@ -10306,7 +10306,7 @@
         <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X39" t="n">
         <v>20</v>
@@ -10369,10 +10369,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AT39" t="n">
         <v>6.6</v>
@@ -10384,7 +10384,7 @@
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX39" t="n">
         <v>5</v>
@@ -10393,28 +10393,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="n">
         <v>3.25</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -10512,22 +10512,22 @@
         <v>1.54</v>
       </c>
       <c r="G40" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H40" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I40" t="n">
         <v>11.5</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K40" t="n">
         <v>4.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M40" t="n">
         <v>1.09</v>
@@ -10545,7 +10545,7 @@
         <v>2.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
         <v>4.2</v>
@@ -10560,10 +10560,10 @@
         <v>1.1</v>
       </c>
       <c r="W40" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="X40" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="Y40" t="n">
         <v>950</v>
@@ -10575,7 +10575,7 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC40" t="n">
         <v>11.5</v>
@@ -10590,7 +10590,7 @@
         <v>9.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AH40" t="n">
         <v>950</v>
@@ -10599,19 +10599,19 @@
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AK40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL40" t="n">
         <v>500</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN40" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -10620,13 +10620,13 @@
         <v>5.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT40" t="n">
         <v>4.7</v>
@@ -10635,10 +10635,10 @@
         <v>5.1</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX40" t="n">
         <v>5.9</v>
@@ -10647,40 +10647,40 @@
         <v>7.8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB40" t="n">
         <v>10</v>
       </c>
       <c r="BC40" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF40" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG40" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BH40" t="n">
         <v>3.5</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ40" t="n">
         <v>970</v>
       </c>
       <c r="BK40" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -10763,16 +10763,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G41" t="n">
         <v>5.9</v>
       </c>
-      <c r="G41" t="n">
-        <v>6</v>
-      </c>
       <c r="H41" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I41" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="J41" t="n">
         <v>3.95</v>
@@ -10784,34 +10784,34 @@
         <v>1.46</v>
       </c>
       <c r="M41" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.37</v>
       </c>
       <c r="P41" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R41" t="n">
         <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U41" t="n">
         <v>1.92</v>
       </c>
       <c r="V41" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="W41" t="n">
         <v>1.2</v>
@@ -10826,19 +10826,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA41" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AB41" t="n">
         <v>16.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD41" t="n">
         <v>10</v>
       </c>
       <c r="AE41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF41" t="n">
         <v>44</v>
@@ -10859,7 +10859,7 @@
         <v>85</v>
       </c>
       <c r="AL41" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM41" t="n">
         <v>120</v>
@@ -10871,7 +10871,7 @@
         <v>11.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ41" t="n">
         <v>7.4</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
         <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
@@ -11035,7 +11035,7 @@
         <v>3.8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
@@ -11056,13 +11056,13 @@
         <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T42" t="n">
         <v>1.89</v>
       </c>
       <c r="U42" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="V42" t="n">
         <v>1.21</v>
@@ -11119,34 +11119,34 @@
         <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="AO42" t="n">
         <v>700</v>
       </c>
       <c r="AP42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ42" t="n">
         <v>7.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AT42" t="n">
         <v>6.4</v>
       </c>
       <c r="AU42" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AW42" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX42" t="n">
         <v>6</v>
@@ -11155,28 +11155,28 @@
         <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="BA42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC42" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB42" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG42" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH42" t="n">
         <v>3.4</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G43" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="H43" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
         <v>11.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K43" t="n">
         <v>4.7</v>
@@ -11322,7 +11322,7 @@
         <v>1.1</v>
       </c>
       <c r="W43" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
         <v>12</v>
@@ -11346,7 +11346,7 @@
         <v>42</v>
       </c>
       <c r="AE43" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AF43" t="n">
         <v>7.4</v>
@@ -11355,7 +11355,7 @@
         <v>11</v>
       </c>
       <c r="AH43" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI43" t="n">
         <v>230</v>
@@ -11370,7 +11370,7 @@
         <v>65</v>
       </c>
       <c r="AM43" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN43" t="n">
         <v>10.5</v>
@@ -11385,10 +11385,10 @@
         <v>21</v>
       </c>
       <c r="AR43" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AS43" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT43" t="n">
         <v>5.5</v>
@@ -11415,19 +11415,19 @@
         <v>11.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC43" t="n">
         <v>17.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BE43" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF43" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG43" t="n">
         <v>12</v>
@@ -11445,10 +11445,10 @@
         <v>4</v>
       </c>
       <c r="BL43" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="BM43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BN43" t="n">
         <v>4.1</v>
@@ -11460,41 +11460,41 @@
         <v>11</v>
       </c>
       <c r="BQ43" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BR43" t="n">
         <v>42</v>
       </c>
       <c r="BS43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT43" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU43" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV43" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BW43" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BX43" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BY43" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ43" t="n">
         <v>26</v>
       </c>
       <c r="CA43" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -11525,16 +11525,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G44" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H44" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
         <v>5.3</v>
@@ -11549,49 +11549,49 @@
         <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O44" t="n">
         <v>1.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="R44" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U44" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V44" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W44" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="X44" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y44" t="n">
         <v>950</v>
       </c>
       <c r="Z44" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AA44" t="n">
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AC44" t="n">
         <v>14.5</v>
@@ -11612,13 +11612,13 @@
         <v>950</v>
       </c>
       <c r="AI44" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AJ44" t="n">
         <v>11.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL44" t="n">
         <v>60</v>
@@ -11627,64 +11627,64 @@
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AT44" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX44" t="n">
         <v>6.2</v>
       </c>
-      <c r="AW44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AY44" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA44" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BB44" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="BC44" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="BE44" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BF44" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BH44" t="n">
         <v>4.1</v>
@@ -11693,22 +11693,22 @@
         <v>3</v>
       </c>
       <c r="BJ44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BK44" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL44" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="BM44" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN44" t="n">
         <v>3.95</v>
       </c>
       <c r="BO44" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BP44" t="n">
         <v>8.800000000000001</v>
@@ -11717,38 +11717,38 @@
         <v>6</v>
       </c>
       <c r="BR44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS44" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV44" t="n">
         <v>150</v>
       </c>
       <c r="BW44" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX44" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY44" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BZ44" t="n">
         <v>16.5</v>
       </c>
       <c r="CA44" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -11782,13 +11782,13 @@
         <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H45" t="n">
         <v>4.7</v>
       </c>
       <c r="I45" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J45" t="n">
         <v>3.4</v>
@@ -11803,10 +11803,10 @@
         <v>1.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O45" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P45" t="n">
         <v>1.65</v>
@@ -11830,7 +11830,7 @@
         <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X45" t="n">
         <v>11</v>
@@ -11842,10 +11842,10 @@
         <v>38</v>
       </c>
       <c r="AA45" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB45" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC45" t="n">
         <v>8.6</v>
@@ -11854,7 +11854,7 @@
         <v>21</v>
       </c>
       <c r="AE45" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF45" t="n">
         <v>11</v>
@@ -11890,13 +11890,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ45" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR45" t="n">
         <v>30</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT45" t="n">
         <v>6.4</v>
@@ -11905,13 +11905,13 @@
         <v>7.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW45" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AX45" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY45" t="n">
         <v>9.199999999999999</v>
@@ -11920,7 +11920,7 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB45" t="n">
         <v>19</v>
@@ -11932,13 +11932,13 @@
         <v>42</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF45" t="n">
         <v>16.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH45" t="n">
         <v>3.4</v>
@@ -11959,7 +11959,7 @@
         <v>4.9</v>
       </c>
       <c r="BN45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO45" t="n">
         <v>3.4</v>
@@ -11968,16 +11968,16 @@
         <v>18</v>
       </c>
       <c r="BQ45" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR45" t="n">
         <v>42</v>
       </c>
       <c r="BS45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT45" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU45" t="n">
         <v>6</v>
@@ -11998,11 +11998,11 @@
         <v>42</v>
       </c>
       <c r="CA45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G46" t="n">
         <v>1.85</v>
@@ -12045,10 +12045,10 @@
         <v>5.8</v>
       </c>
       <c r="J46" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L46" t="n">
         <v>1.37</v>
@@ -12060,25 +12060,25 @@
         <v>3.35</v>
       </c>
       <c r="O46" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P46" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S46" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T46" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
         <v>1.21</v>
@@ -12153,7 +12153,7 @@
         <v>7.8</v>
       </c>
       <c r="AT46" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU46" t="n">
         <v>7.2</v>
@@ -12240,10 +12240,10 @@
         <v>55</v>
       </c>
       <c r="BW46" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX46" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY46" t="n">
         <v>5.4</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>2.42</v>
       </c>
       <c r="G47" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H47" t="n">
         <v>3.3</v>
@@ -12305,7 +12305,7 @@
         <v>3.4</v>
       </c>
       <c r="L47" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
         <v>1.1</v>
@@ -12314,13 +12314,13 @@
         <v>3.05</v>
       </c>
       <c r="O47" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P47" t="n">
         <v>1.69</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R47" t="n">
         <v>1.26</v>
@@ -12338,7 +12338,7 @@
         <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X47" t="n">
         <v>13</v>
@@ -12356,16 +12356,16 @@
         <v>10</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD47" t="n">
         <v>17</v>
       </c>
       <c r="AE47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF47" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AG47" t="n">
         <v>12</v>
@@ -12377,7 +12377,7 @@
         <v>65</v>
       </c>
       <c r="AJ47" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AK47" t="n">
         <v>38</v>
@@ -12401,10 +12401,10 @@
         <v>9.6</v>
       </c>
       <c r="AR47" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT47" t="n">
         <v>7.8</v>
@@ -12416,46 +12416,46 @@
         <v>12.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX47" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY47" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ47" t="n">
         <v>17</v>
       </c>
       <c r="BA47" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB47" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC47" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC47" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD47" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF47" t="n">
         <v>22</v>
       </c>
       <c r="BG47" t="n">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="BH47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK47" t="n">
         <v>3.5</v>
@@ -12473,7 +12473,7 @@
         <v>4</v>
       </c>
       <c r="BP47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ47" t="n">
         <v>4.1</v>
@@ -12503,14 +12503,14 @@
         <v>4.5</v>
       </c>
       <c r="BZ47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA47" t="n">
         <v>4.4</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
         <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>2.68</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG2" t="n">
         <v>120</v>
       </c>
-      <c r="AF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="BH2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP2" t="n">
         <v>11</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="BQ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>27</v>
       </c>
-      <c r="AI2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>95</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>190</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>960</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>75</v>
-      </c>
       <c r="CA2" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1102,239 +1102,239 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="H3" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AA3" t="n">
-        <v>350</v>
+        <v>660</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AE3" t="n">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI3" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>470</v>
+      </c>
+      <c r="AP3" t="n">
         <v>14</v>
       </c>
-      <c r="AK3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>370</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AR3" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE3" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>1.78</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>2.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>2.02</v>
       </c>
       <c r="BZ3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>2.68</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI4" t="n">
         <v>2.7</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="BJ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>140</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
         <v>15</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="BQ4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>990</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>34</v>
       </c>
-      <c r="Z4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>860</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>360</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>770</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>20</v>
-      </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.6</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AS5" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW5" t="n">
         <v>60</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB5" t="n">
         <v>17.5</v>
       </c>
-      <c r="BB5" t="n">
-        <v>20</v>
-      </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="BF5" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>13</v>
-      </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="CA5" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1864,493 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="X6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP6" t="n">
         <v>14</v>
       </c>
-      <c r="Y6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT6" t="n">
         <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>11</v>
-      </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BZ6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Cusco FC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>2.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.68</v>
+        <v>36</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>1.79</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AV2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AW2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>28</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>50</v>
       </c>
-      <c r="BB2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>150</v>
-      </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>1.61</v>
       </c>
       <c r="BG2" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1097,1006 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>1.57</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.8</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
         <v>2.02</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.54</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>2.66</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO3" t="n">
         <v>32</v>
       </c>
-      <c r="Z3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>660</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL3" t="n">
+      <c r="AP3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD3" t="n">
         <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>470</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>48</v>
       </c>
       <c r="BE3" t="n">
         <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>75</v>
       </c>
       <c r="BG3" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.78</v>
+        <v>3.95</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>180</v>
+        <v>3.95</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.56</v>
+        <v>3.95</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>1.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.68</v>
+        <v>3.95</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LDU</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Lanus</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>140</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>990</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-05-20 21:39:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sporting Cristal</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-05-20 21:39:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Cusco FC</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>75</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>13</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
